--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25046773-3F5A-4AB9-856F-791D71EE4B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726485BE-8332-4828-BB4A-EE2DA53B6EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19300" windowHeight="13770" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封标" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="124">
   <si>
     <t>​​画面描述 (分镜)​​</t>
   </si>
@@ -55,24 +55,9 @@
     <t>​​备注 (动作/道具/剪辑点)​​</t>
   </si>
   <si>
-    <t>乐曲BGM</t>
-  </si>
-  <si>
-    <t>频道名/LOGO展示</t>
-  </si>
-  <si>
-    <t>TODO</t>
-  </si>
-  <si>
     <t>时长</t>
   </si>
   <si>
-    <t>钢尺君/杯鸽等演奏片段</t>
-  </si>
-  <si>
-    <t>演示曲目待定</t>
-  </si>
-  <si>
     <t>相应的画面（快放）</t>
   </si>
   <si>
@@ -88,13 +73,6 @@
     <t>3d打印延迟摄影</t>
   </si>
   <si>
-    <t>取出模型</t>
-  </si>
-  <si>
-    <t>组装过程特写：
-以安装卡扣，拧螺丝为主</t>
-  </si>
-  <si>
     <t>成品展示：使用旋转展示台</t>
   </si>
   <si>
@@ -109,18 +87,6 @@
   </si>
   <si>
     <t>此前录制的慢放视频（使用类似进度条的东西，显示每部分时间占用）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>先设计一个原型机验证可行性
-使用丝杆步进电机来精确控制钢尺移动
-使用2个舵机分别压住钢尺与弹拨钢尺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>继承上面的图
-麦克风--&gt;开发板-(usb线)-&gt;mic--&gt;电脑
-                                    -&gt;midi--&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -215,20 +181,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>开头5秒黄金时间，必须炸裂</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚刚演奏的是小星星，不过好像听不太出来？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目《赛博朋克2077》，配合一些2077的特效
-添加字幕：“BGM由钢尺演奏”
-标题：“赛博钢尺2025”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>早年在b站看大佬用钢尺演奏太酷了！我也要！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -242,15 +194,6 @@
   </si>
   <si>
     <t>哆啦A梦掏出：钢尺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>那就…上！科！技！
-“自动演奏的钢尺”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>加加鸽</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -321,16 +264,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>​弹钢尺的画面不变
-范大将军片段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>我一个程序员，让我弹钢尺，他能弹么？弹不了！
-“没那个能力知道吧”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>大舵机图片
 不同的器件 + 雷达图（三个维度）动效</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -344,13 +277,6 @@
     <t>口播出镜
 慢速演奏（正常）
 快速（无法压住钢尺，节奏乱掉）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>我：那怎么办呢？
-刘华强：那，吸铁石
-我：钢尺嘛，可以用电磁铁来吸住他
-我：还挺牢固的</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -366,15 +292,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>其次是音不准的问题
-偏差有x.x%，如果偏差超过3%（50音分）就是明显跑调了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>因此，需要添加一个麦克风，使用程序控制拨动钢尺的不同长度，对麦克风采集到的音频进行傅里叶变换，得到频率。最终就可以拟合出一个高精度的频率-步进(step)曲线</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>口播出镜
 麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -385,20 +302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>最后，使用面包板，各种连线实在太乱了
-移动的时候不小心还会碰掉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>开发板乱糟糟的连线
-拿起连断线</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>那么，应该画一个电路板，把元件整合起来</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>连线图
 外面一个框浮现</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -418,24 +321,6 @@
   </si>
   <si>
     <t>王刚出菜BGM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>为了更方便复刻，就只使用成品模块</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>几个焊接特写（焊接排母、安装元件）
-成品效果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>何同学5G下载BGM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>方案可行！！！
-不过这样的效果还差点意思，还有很多问题！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -463,12 +348,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>不同力度弹奏midi键盘演示强弱
-原声--&gt;效果器（片头cyberpunk 2077 预告BGM演奏）
-口播出镜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>除了最基本的演奏，由于有mic，还可以对声音进行一些处理：
 比如对强弱的支持
 你还可以添加一些效果器，比如给这首曲子加上过载效果
@@ -519,16 +398,129 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>用高速摄影机播放分析一下弹奏的耗时：
+    <t>一个转场动画</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢琴一个八度的排列，12个音
+切换到特写键盘do与升do
+指示&lt;50音分偏差
+指示&gt;50音分偏差</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>原理图--&gt;pcb--&gt;2D渲染图</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>感谢嘉立创免费打样，让我白嫖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>再加上钢尺作为贝斯，让它们组一个文具乐队！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不过上面的文具乐队还没有实现，如果这类视频观众老爷们喜欢，点个关注！！
+后续UP主会持续更新的！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全曲太长了，节选一部分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>何同学5G下载BGM
+《rap god》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目《赛博朋克2077》，配合一些2077的特效
+添加字幕：“BGM由钢尺演奏”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《spoiler》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢尺君演奏片段</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过渡到:
+Cyberuler 2025 ——加加鸽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>先试试最简单的小星星
+刚刚演奏的是小星星，不过好像听不太出来？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（可以先用记号笔标注一下）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我一个程序员，让我弹钢尺，我能弹么？弹不了！
+“没那个能力知道吧”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>弹钢尺的画面不变
+范大将军片段（画中画）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么办呢？那就…上！科！技！
+“自动演奏的钢尺”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>先设计一个原型机验证可行性
+使用丝杆步进电机来精确控制钢尺移动
+使用一个舵机压住钢尺，另一个舵机弹拨钢尺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>方案可行！！！
+不过这样的效果还差点意思，还有很多问题要解决！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用高速摄影机播放分析一下：
 抬起舵机--&gt;移动钢尺--&gt;舵机按下--&gt;舵机拨动
-其中舵机抬起与落下耗时最多，需要着重优化</t>
+这四个步骤中，舵机抬起与落下耗时最多，需要着重优化</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>首先想到的就是加快按压钢尺的动作，更换更快速的舵机
-压住钢尺，要有足够的下压力，并且体积不能太大
-但发现：速度快、力量大、体积小是一个</t>
+      <t>那，首先想到的就是：可以更换一个更快速的舵机，减少耗时
+当然也可以是其他电机：但要有足够的下压力，并且体积不能太大
+这就会发现：速度快、力量大、体积小是一个</t>
     </r>
     <r>
       <rPr>
@@ -557,63 +549,104 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>一个转场动画</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>如何提高音准呢？此前调音是在桌面拨动钢尺测试了几个基准长度的音高频率，拟合出频率-长度函数。演奏的时候通过目标频率换算出具体长度。但这样人工测量非常耗时，而且并不准确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢琴一个八度的排列，12个音
-切换到特写键盘do与升do
-指示&lt;50音分偏差
-指示&gt;50音分偏差</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是因为我们常见的音乐都是使用十二平均律，将一个八度平均分成十二份。一份就是一个半音，也就是100音分。假设我弹奏一个do，如果偏差小于50音分，它更接近do，可能有些不准但还可以听出来是do。但如果偏差超过50音分，那它就更接近升do了，也就是跑调了。</t>
+    <t>我：那怎么办呢？
+刘华强：那，吸铁石
+我：谁说一定要用舵机呢！钢尺嘛，可以用电磁铁来吸住他
+我：看！还挺牢固的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解决了速度问题，下一个要解决的就是音不准的问题
+偏差有x.x%，如果偏差超过3%（50音分）就是明显跑调了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是因为我们常见的音乐都是使用十二平均律，将一个八度平均分成十二份,一份就是一个半音，一个半音音程等于100音分。假设我弹奏一个do，如果偏差小于50音分，它更接近do，可能有些不准但还可以听出来是do。但如果偏差超过50音分，那它就更接近升do了，也就是跑调了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何提高音准呢？
+此前调音是在桌面拨动钢尺，用手机测出几个基准长度的音高，而后拟合出频率-长度函数。演奏的时候通过目标频率换算出具体长度。但这样人工测量非常耗时，而且并不准确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因此，需要添加一个麦克风，在不同长度的位置拨动钢尺，用麦克风采集音频并进行傅里叶变换，得到对应长度的频率。最终就可以拟合出一个高精度的频率-步进(step)曲线</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>既然为了调音增加了麦克风硬件，那为什么不物尽其用呢？
-esp32s3开发板刚好有usb接口，可以集成一个usb麦克风，用来录音，获得更好的录音音质。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>还有一个问题，如何存储乐谱呢？
-原型机用串口发送一个音符演奏一个音符，谱子格式是自定义的：
-比如，("5#.", 1)：即表示高音升Sol，时长为一拍
+esp32s3开发板刚好有usb接口，可以集成一个usb麦克风，连接电脑用来录音，获得更好的录音音质。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>还有一个问题，就是，乐谱的存储与传输
+原型机的谱子格式是自定义的：
+比如，("5#.", 1)：即表示高音升Sol，时长为一拍，用串口发送一个音符演奏一个音符
 这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>主流的电子乐器都支持midi，所以决定使用usb midi进行音符传输，这样直接使用编曲软件存midi即可</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>原理图--&gt;pcb--&gt;2D渲染图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>感谢嘉立创免费打样，让我白嫖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>结束</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>再加上钢尺作为贝斯，让它们组一个文具乐队！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不过上面的文具乐队还没有实现，如果这类视频观众老爷们喜欢，点个关注！！
-后续UP主会持续更新的！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>全曲太长了，节选一部分</t>
+    <t>10:19-10:32 https://www.bilibili.com/video/BV187411r7hp/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>midi图示
+nokia tune播放视频
+5针、usb、RTS等物理接口
+麦克风--&gt;开发板-(usb线)-&gt;mic--&gt;电脑
+                                    -&gt;midi--&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哎！不知道你有没有听过一种技术叫MIDI，它即可以传输音符，又可以存储乐谱。
+功能机时代的诺基亚铃声，你一定听过
+它就是midi
+midi可以使用多种接口进行传输，比如usb接口。而刚好我们的开发板上就有usb接口。使用usb midi就是最好的选择了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发板乱糟糟的连线
+人+影视飓风的扭转特效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最后，使用面包板，各种连线实在太乱了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>画一个电路板，把它们整合起来</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>为了更方便复刻，都是使用的成品模块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>几个焊接特写：焊接排母、安装元件（插入卡点）
+成品效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>组装过程特写（按照装机区的那种风格）
+以安装器件，拧螺丝为主</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取出模型--&gt;拿到工作台--&gt;掰下来</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果没有midi键盘，也可用手机的虚拟MIDI键盘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手机midi键盘演示：do re mi fa。。。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同力度弹奏midi键盘演示强弱
+原声--&gt;效果器（片头cyberpunk 2077 预告BGM演奏）
+口播出镜（拿着读最后一句台词）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -621,7 +654,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="等线"/>
@@ -672,6 +705,20 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="MS Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="5">
@@ -790,7 +837,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -875,6 +922,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -892,6 +942,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1169,31 +1222,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FBFDF2-C68F-43FE-8FE4-06F462270704}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="22" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="22" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1204,26 +1257,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5"/>
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="8.25" style="6" customWidth="1"/>
     <col min="3" max="3" width="8.25" style="27" customWidth="1"/>
-    <col min="4" max="5" width="62.875" style="6" customWidth="1"/>
+    <col min="4" max="5" width="62.83203125" style="6" customWidth="1"/>
     <col min="6" max="6" width="26.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.375" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="9.125" style="3"/>
+    <col min="7" max="7" width="25.33203125" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="9.08203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1238,7 +1291,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="66">
+    <row r="2" spans="1:7" ht="49.5">
       <c r="A2" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
@@ -1246,19 +1299,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="33">
       <c r="A3" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
@@ -1267,16 +1317,13 @@
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>6</v>
+        <v>94</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1287,30 +1334,33 @@
         <f>B3+A3</f>
         <v>1.7361111111111109E-4</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>42</v>
+      <c r="C4" s="29" t="s">
+        <v>33</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="B5" s="5">
-        <f t="shared" ref="B5:B54" si="0">B4+A4</f>
+        <f t="shared" ref="B5:B56" si="0">B4+A4</f>
         <v>2.8935185185185184E-4</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="6" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>47</v>
+        <v>95</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1321,13 +1371,13 @@
         <f t="shared" si="0"/>
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="30"/>
       <c r="D6" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33">
@@ -1338,12 +1388,12 @@
         <f t="shared" si="0"/>
         <v>4.1666666666666664E-4</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="6" t="s">
-        <v>69</v>
+      <c r="C7" s="30"/>
+      <c r="D7" s="28" t="s">
+        <v>98</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="33">
@@ -1354,12 +1404,12 @@
         <f t="shared" si="0"/>
         <v>5.0925925925925921E-4</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="9" customFormat="1" ht="49.5">
@@ -1370,14 +1420,14 @@
         <f>B8+A8</f>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -1390,15 +1440,15 @@
         <f t="shared" si="0"/>
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="C10" s="29"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="17" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G10" s="17"/>
     </row>
@@ -1410,17 +1460,15 @@
         <f>B10+A10</f>
         <v>8.1018518518518516E-4</v>
       </c>
-      <c r="C11" s="30"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="6" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F11" s="10"/>
-      <c r="G11" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="33">
       <c r="A12" s="4">
@@ -1430,14 +1478,14 @@
         <f t="shared" si="0"/>
         <v>9.4907407407407408E-4</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>67</v>
+      <c r="C12" s="32" t="s">
+        <v>53</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
@@ -1450,15 +1498,15 @@
         <f t="shared" si="0"/>
         <v>1.0185185185185184E-3</v>
       </c>
-      <c r="C13" s="33"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="13" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G13" s="14"/>
     </row>
@@ -1470,12 +1518,12 @@
         <f t="shared" si="0"/>
         <v>1.2037037037037036E-3</v>
       </c>
-      <c r="C14" s="33"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="14" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
@@ -1488,12 +1536,12 @@
         <f t="shared" si="0"/>
         <v>1.435185185185185E-3</v>
       </c>
-      <c r="C15" s="33"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="13" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
@@ -1506,15 +1554,15 @@
         <f t="shared" si="0"/>
         <v>1.7824074074074072E-3</v>
       </c>
-      <c r="C16" s="33"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="13" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G16" s="13"/>
     </row>
@@ -1526,12 +1574,12 @@
         <f t="shared" si="0"/>
         <v>1.8981481481481479E-3</v>
       </c>
-      <c r="C17" s="33"/>
+      <c r="C17" s="34"/>
       <c r="D17" s="13" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
@@ -1544,9 +1592,9 @@
         <f t="shared" ref="B18:B22" si="1">B17+A17</f>
         <v>1.9907407407407404E-3</v>
       </c>
-      <c r="C18" s="33"/>
+      <c r="C18" s="34"/>
       <c r="D18" s="21" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="13"/>
@@ -1560,12 +1608,12 @@
         <f t="shared" si="0"/>
         <v>2.0023148148148144E-3</v>
       </c>
-      <c r="C19" s="33"/>
+      <c r="C19" s="34"/>
       <c r="D19" s="6" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
@@ -1578,17 +1626,17 @@
         <f t="shared" si="1"/>
         <v>2.1180555555555553E-3</v>
       </c>
-      <c r="C20" s="33"/>
+      <c r="C20" s="34"/>
       <c r="D20" s="6" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" ht="49.5">
+    <row r="21" spans="1:7" ht="66">
       <c r="A21" s="4">
         <v>2.8935185185185189E-4</v>
       </c>
@@ -1596,12 +1644,12 @@
         <f t="shared" si="0"/>
         <v>2.5231481481481481E-3</v>
       </c>
-      <c r="C21" s="33"/>
+      <c r="C21" s="34"/>
       <c r="D21" s="6" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="49.5">
@@ -1612,215 +1660,210 @@
         <f t="shared" si="1"/>
         <v>2.8124999999999999E-3</v>
       </c>
-      <c r="C22" s="33"/>
+      <c r="C22" s="34"/>
       <c r="D22" s="10" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="19" customFormat="1" ht="49.5">
-      <c r="A23" s="4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:7" s="19" customFormat="1" ht="49.5">
+      <c r="A24" s="4">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="B23" s="5">
-        <f t="shared" si="0"/>
+      <c r="B24" s="5">
+        <f>B22+A22</f>
         <v>3.1018518518518517E-3</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-    </row>
-    <row r="24" spans="1:7" s="19" customFormat="1">
-      <c r="A24" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="B24" s="5">
-        <f t="shared" si="0"/>
-        <v>3.2754629629629627E-3</v>
-      </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" s="24"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>109</v>
+      </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
     </row>
-    <row r="25" spans="1:7" ht="66">
+    <row r="25" spans="1:7" s="19" customFormat="1">
       <c r="A25" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="B25" s="5">
+        <f t="shared" si="0"/>
+        <v>3.2754629629629627E-3</v>
+      </c>
+      <c r="C25" s="34"/>
+      <c r="D25" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="24"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:7" ht="82.5">
+      <c r="A26" s="4">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B26" s="5">
         <f t="shared" si="0"/>
         <v>3.2870370370370367E-3</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:7" ht="49.5">
-      <c r="A26" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="B26" s="5">
+      <c r="C26" s="34"/>
+      <c r="D26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+    </row>
+    <row r="27" spans="1:7" ht="99">
+      <c r="A27" s="4">
+        <v>4.6296296296296293E-4</v>
+      </c>
+      <c r="B27" s="5">
         <f t="shared" si="0"/>
         <v>3.518518518518518E-3</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="4">
+      <c r="C27" s="34"/>
+      <c r="D27" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="B27" s="5">
-        <f t="shared" si="0"/>
-        <v>3.634259259259259E-3</v>
-      </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="12"/>
-    </row>
-    <row r="28" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A28" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
       <c r="B28" s="5">
         <f t="shared" si="0"/>
-        <v>3.645833333333333E-3</v>
-      </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="13" t="s">
+        <v>3.9814814814814808E-3</v>
+      </c>
+      <c r="C28" s="34"/>
+      <c r="D28" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" spans="1:7" s="16" customFormat="1" ht="33">
       <c r="A29" s="4">
-        <v>5.7870370370370366E-5</v>
+        <v>1.1574074074074073E-4</v>
       </c>
       <c r="B29" s="5">
         <f t="shared" si="0"/>
-        <v>3.7615740740740739E-3</v>
-      </c>
-      <c r="C29" s="32"/>
+        <v>3.9930555555555552E-3</v>
+      </c>
+      <c r="C29" s="34"/>
       <c r="D29" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>114</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="1:7" s="16" customFormat="1" ht="33">
       <c r="A30" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="B30" s="5">
         <f t="shared" si="0"/>
-        <v>3.8194444444444443E-3</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>26</v>
+        <v>4.1087962962962962E-3</v>
+      </c>
+      <c r="C30" s="33"/>
+      <c r="D30" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="21" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4">
-        <v>6.9444444444444444E-5</v>
+        <v>5.7870370370370366E-5</v>
       </c>
       <c r="B31" s="5">
         <f t="shared" si="0"/>
-        <v>3.8773148148148148E-3</v>
-      </c>
-      <c r="C31" s="33"/>
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>31</v>
+      </c>
       <c r="D31" s="6" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="4">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="B32" s="5">
+        <f t="shared" si="0"/>
+        <v>4.2245370370370371E-3</v>
+      </c>
+      <c r="C32" s="34"/>
+      <c r="D32" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="B32" s="5">
-        <f t="shared" si="0"/>
-        <v>3.9467592592592592E-3</v>
-      </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="33">
-      <c r="A33" s="4">
+      <c r="B33" s="5">
+        <f t="shared" si="0"/>
+        <v>4.2939814814814811E-3</v>
+      </c>
+      <c r="C33" s="34"/>
+      <c r="D33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="33">
+      <c r="A34" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B33" s="5">
-        <f t="shared" si="0"/>
-        <v>4.0046296296296297E-3</v>
-      </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
       <c r="B34" s="5">
         <f t="shared" si="0"/>
-        <v>4.1203703703703706E-3</v>
-      </c>
-      <c r="C34" s="33"/>
+        <v>4.3518518518518515E-3</v>
+      </c>
+      <c r="C34" s="34"/>
       <c r="D34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="F34" s="7"/>
     </row>
@@ -1830,11 +1873,14 @@
       </c>
       <c r="B35" s="5">
         <f t="shared" si="0"/>
-        <v>4.178240740740741E-3</v>
-      </c>
-      <c r="C35" s="33"/>
+        <v>4.4675925925925924E-3</v>
+      </c>
+      <c r="C35" s="34"/>
       <c r="D35" s="6" t="s">
-        <v>14</v>
+        <v>8</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="F35" s="7"/>
     </row>
@@ -1844,314 +1890,340 @@
       </c>
       <c r="B36" s="5">
         <f t="shared" si="0"/>
-        <v>4.2361111111111115E-3</v>
-      </c>
-      <c r="C36" s="33"/>
+        <v>4.5254629629629629E-3</v>
+      </c>
+      <c r="C36" s="34"/>
       <c r="D36" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:7" ht="33">
+    <row r="37" spans="1:7">
       <c r="A37" s="4">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="B37" s="5">
+        <f t="shared" si="0"/>
+        <v>4.5833333333333334E-3</v>
+      </c>
+      <c r="C37" s="34"/>
+      <c r="D37" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="33">
+      <c r="A38" s="4">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="B37" s="5">
-        <f t="shared" si="0"/>
-        <v>4.293981481481482E-3</v>
-      </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
       <c r="B38" s="5">
         <f t="shared" si="0"/>
-        <v>4.4675925925925933E-3</v>
-      </c>
-      <c r="C38" s="33"/>
+        <v>4.6412037037037038E-3</v>
+      </c>
+      <c r="C38" s="34"/>
       <c r="D38" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>88</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="F38" s="7"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4">
-        <v>3.4722222222222222E-5</v>
+        <v>5.7870370370370366E-5</v>
       </c>
       <c r="B39" s="5">
         <f t="shared" si="0"/>
-        <v>4.5254629629629638E-3</v>
-      </c>
-      <c r="C39" s="33"/>
+        <v>4.8148148148148152E-3</v>
+      </c>
+      <c r="C39" s="34"/>
       <c r="D39" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F39" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="B40" s="5">
+        <f t="shared" si="0"/>
+        <v>4.8726851851851856E-3</v>
+      </c>
+      <c r="C40" s="34"/>
+      <c r="D40" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="B40" s="5">
-        <f t="shared" si="0"/>
-        <v>4.5601851851851862E-3</v>
-      </c>
-      <c r="C40" s="32"/>
-      <c r="D40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="66">
-      <c r="A41" s="4">
+      <c r="B41" s="5">
+        <f t="shared" si="0"/>
+        <v>4.9074074074074081E-3</v>
+      </c>
+      <c r="C41" s="33"/>
+      <c r="D41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="66">
+      <c r="A42" s="4">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="B41" s="5">
-        <f t="shared" si="0"/>
-        <v>4.6064814814814822E-3</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="4">
+      <c r="B42" s="5">
+        <f t="shared" si="0"/>
+        <v>4.9537037037037041E-3</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4">
         <v>2.3148148148148147E-5</v>
       </c>
-      <c r="B42" s="5">
-        <f t="shared" si="0"/>
-        <v>5.069444444444445E-3</v>
-      </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="82.5">
-      <c r="A43" s="4">
+      <c r="B43" s="5">
+        <f t="shared" si="0"/>
+        <v>5.4166666666666669E-3</v>
+      </c>
+      <c r="C43" s="34"/>
+      <c r="D43" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="82.5">
+      <c r="A44" s="4">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="B43" s="5">
-        <f t="shared" si="0"/>
-        <v>5.092592592592593E-3</v>
-      </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G43" s="7"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="4">
+      <c r="B44" s="5">
+        <f t="shared" si="0"/>
+        <v>5.4398148148148149E-3</v>
+      </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G44" s="7"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="B44" s="5">
-        <f t="shared" si="0"/>
-        <v>5.4976851851851853E-3</v>
-      </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="45" spans="1:7" ht="66">
-      <c r="A45" s="4">
+      <c r="B45" s="5">
+        <f t="shared" si="0"/>
+        <v>5.8449074074074072E-3</v>
+      </c>
+      <c r="C45" s="34"/>
+      <c r="D45" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G46" s="7"/>
+    </row>
+    <row r="47" spans="1:7" ht="66">
+      <c r="A47" s="4">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="B45" s="5">
-        <f t="shared" si="0"/>
-        <v>5.5092592592592598E-3</v>
-      </c>
-      <c r="C45" s="32"/>
-      <c r="D45" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="4">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="B46" s="5">
+      <c r="B47" s="5">
         <f>B45+A45</f>
-        <v>5.9143518518518521E-3</v>
-      </c>
-      <c r="C46" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="4">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="B47" s="5">
-        <f t="shared" si="0"/>
-        <v>5.9490740740740745E-3</v>
+        <v>5.8564814814814816E-3</v>
       </c>
       <c r="C47" s="33"/>
       <c r="D47" s="6" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="4">
-        <v>5.7870370370370366E-5</v>
+        <v>3.4722222222222222E-5</v>
       </c>
       <c r="B48" s="5">
-        <f t="shared" si="0"/>
-        <v>5.9953703703703705E-3</v>
-      </c>
-      <c r="C48" s="33"/>
+        <f>B47+A47</f>
+        <v>6.2615740740740739E-3</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>29</v>
+      </c>
       <c r="D48" s="6" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="33">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="4">
-        <v>6.9444444444444444E-5</v>
+        <v>4.6296296296296294E-5</v>
       </c>
       <c r="B49" s="5">
         <f t="shared" si="0"/>
-        <v>6.053240740740741E-3</v>
-      </c>
-      <c r="C49" s="33"/>
+        <v>6.2962962962962964E-3</v>
+      </c>
+      <c r="C49" s="34"/>
       <c r="D49" s="6" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="4">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="B50" s="5">
+        <f t="shared" si="0"/>
+        <v>6.3425925925925924E-3</v>
+      </c>
+      <c r="C50" s="34"/>
+      <c r="D50" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="33">
+      <c r="A51" s="4">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="B50" s="5">
-        <f t="shared" si="0"/>
-        <v>6.122685185185185E-3</v>
-      </c>
-      <c r="C50" s="32"/>
-      <c r="D50" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="49.5">
-      <c r="A51" s="4">
+      <c r="B51" s="5">
+        <f t="shared" si="0"/>
+        <v>6.4004629629629628E-3</v>
+      </c>
+      <c r="C51" s="34"/>
+      <c r="D51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="4">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="B52" s="5">
+        <f t="shared" si="0"/>
+        <v>6.4699074074074069E-3</v>
+      </c>
+      <c r="C52" s="33"/>
+      <c r="D52" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="49.5">
+      <c r="A53" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B51" s="5">
-        <f t="shared" si="0"/>
-        <v>6.192129629629629E-3</v>
-      </c>
-      <c r="C51" s="23"/>
-      <c r="E51" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="33">
-      <c r="A52" s="4">
+      <c r="B53" s="5">
+        <f t="shared" si="0"/>
+        <v>6.5393518518518509E-3</v>
+      </c>
+      <c r="C53" s="23"/>
+      <c r="E53" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="33">
+      <c r="A54" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B52" s="5">
-        <f t="shared" si="0"/>
-        <v>6.3078703703703699E-3</v>
-      </c>
-      <c r="C52" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="132">
-      <c r="A53" s="4">
+      <c r="B54" s="5">
+        <f t="shared" si="0"/>
+        <v>6.6550925925925918E-3</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="132">
+      <c r="A55" s="4">
         <v>1.5046296296296294E-3</v>
       </c>
-      <c r="B53" s="5">
-        <f t="shared" si="0"/>
-        <v>6.4236111111111108E-3</v>
-      </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="B54" s="5">
-        <f t="shared" si="0"/>
-        <v>7.9282407407407409E-3</v>
-      </c>
-      <c r="C54" s="27" t="s">
-        <v>120</v>
+      <c r="B55" s="5">
+        <f t="shared" si="0"/>
+        <v>6.7708333333333327E-3</v>
+      </c>
+      <c r="C55" s="33"/>
+      <c r="D55" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="B56" s="5">
+        <f t="shared" si="0"/>
+        <v>8.2754629629629619E-3</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="C30:C40"/>
-    <mergeCell ref="C12:C29"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C42:C47"/>
+    <mergeCell ref="C31:C41"/>
+    <mergeCell ref="C12:C30"/>
     <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="C48:C52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2161,7 +2233,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{543450A5-C08D-4873-BAC4-1F306BA55BCC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726485BE-8332-4828-BB4A-EE2DA53B6EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D36613-7CBA-4B03-8002-86AF23254340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="封标" sheetId="4" r:id="rId1"/>
     <sheet name="完整版" sheetId="1" r:id="rId2"/>
     <sheet name="简洁版" sheetId="3" r:id="rId3"/>
+    <sheet name="素材引用" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="138">
   <si>
     <t>​​画面描述 (分镜)​​</t>
   </si>
@@ -58,9 +59,6 @@
     <t>时长</t>
   </si>
   <si>
-    <t>相应的画面（快放）</t>
-  </si>
-  <si>
     <t>响指</t>
   </si>
   <si>
@@ -87,11 +85,6 @@
   </si>
   <si>
     <t>此前录制的慢放视频（使用类似进度条的东西，显示每部分时间占用）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>开干！！！
-建模--&gt;打印--&gt;组装与连线--&gt;撸代码</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -162,10 +155,6 @@
   </si>
   <si>
     <t>原型机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>引入</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -281,13 +270,6 @@
   </si>
   <si>
     <t>口播出镜
-《华强买瓜》——吸铁石
-电磁铁吸住钢尺特写（尝试拨动，如果不行就静态展示）
-solidworks中4电磁铁+钢尺模型图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
 弹奏一个音+手机fft，浮现文字：误差xxx</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -434,11 +416,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>何同学5G下载BGM
-《rap god》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>成果展示，使用动态镜头视角（平移/缩放切换），演奏曲目《赛博朋克2077》，配合一些2077的特效
 添加字幕：“BGM由钢尺演奏”</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -449,25 +426,6 @@
   </si>
   <si>
     <t>钢尺君演奏片段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>过渡到:
-Cyberuler 2025 ——加加鸽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>先试试最简单的小星星
-刚刚演奏的是小星星，不过好像听不太出来？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>（可以先用记号笔标注一下）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>我一个程序员，让我弹钢尺，我能弹么？弹不了！
-“没那个能力知道吧”</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -495,17 +453,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>怎么办呢？那就…上！科！技！
-“自动演奏的钢尺”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>先设计一个原型机验证可行性
-使用丝杆步进电机来精确控制钢尺移动
-使用一个舵机压住钢尺，另一个舵机弹拨钢尺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>方案可行！！！
 不过这样的效果还差点意思，还有很多问题要解决！</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -514,6 +461,143 @@
     <t>用高速摄影机播放分析一下：
 抬起舵机--&gt;移动钢尺--&gt;舵机按下--&gt;舵机拨动
 这四个步骤中，舵机抬起与落下耗时最多，需要着重优化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解决了速度问题，下一个要解决的就是音不准的问题
+偏差有x.x%，如果偏差超过3%（50音分）就是明显跑调了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是因为我们常见的音乐都是使用十二平均律，将一个八度平均分成十二份,一份就是一个半音，一个半音音程等于100音分。假设我弹奏一个do，如果偏差小于50音分，它更接近do，可能有些不准但还可以听出来是do。但如果偏差超过50音分，那它就更接近升do了，也就是跑调了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何提高音准呢？
+此前调音是在桌面拨动钢尺，用手机测出几个基准长度的音高，而后拟合出频率-长度函数。演奏的时候通过目标频率换算出具体长度。但这样人工测量非常耗时，而且并不准确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因此，需要添加一个麦克风，在不同长度的位置拨动钢尺，用麦克风采集音频并进行傅里叶变换，得到对应长度的频率。最终就可以拟合出一个高精度的频率-步进(step)曲线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>既然为了调音增加了麦克风硬件，那为什么不物尽其用呢？
+esp32s3开发板刚好有usb接口，可以集成一个usb麦克风，连接电脑用来录音，获得更好的录音音质。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>还有一个问题，就是，乐谱的存储与传输
+原型机的谱子格式是自定义的：
+比如，("5#.", 1)：即表示高音升Sol，时长为一拍，用串口发送一个音符演奏一个音符
+这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:19-10:32 https://www.bilibili.com/video/BV187411r7hp/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>midi图示
+nokia tune播放视频
+5针、usb、RTS等物理接口
+麦克风--&gt;开发板-(usb线)-&gt;mic--&gt;电脑
+                                    -&gt;midi--&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哎！不知道你有没有听过一种技术叫MIDI，它即可以传输音符，又可以存储乐谱。
+功能机时代的诺基亚铃声，你一定听过
+它就是midi
+midi可以使用多种接口进行传输，比如usb接口。而刚好我们的开发板上就有usb接口。使用usb midi就是最好的选择了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发板乱糟糟的连线
+人+影视飓风的扭转特效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最后，使用面包板，各种连线实在太乱了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>画一个电路板，把它们整合起来</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>为了更方便复刻，都是使用的成品模块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>几个焊接特写：焊接排母、安装元件（插入卡点）
+成品效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>组装过程特写（按照装机区的那种风格）
+以安装器件，拧螺丝为主</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果没有midi键盘，也可用手机的虚拟MIDI键盘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手机midi键盘演示：do re mi fa。。。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同力度弹奏midi键盘演示强弱
+原声--&gt;效果器（片头cyberpunk 2077 预告BGM演奏）
+口播出镜（拿着读最后一句台词）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（可以先用记号笔标注一下钢尺上音的位置）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>先试试最简单的小星星
+这是《小星星》？我自己都要听不出来了？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO：这里应该对比人手弹奏时的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>todo：测试哆啦A梦的演奏效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我：我一个程序员，让我弹钢尺，我能弹么？
+范志毅：“弹不了！没那个能力知道吧！”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过渡到:
+Cyberuler 2025</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么办呢？那就…上！科！技！
+“自动演奏的钢尺”
+让我们开始吧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加加鸽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO:需要制作片头</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我先设计了一个原型机验证可行性
+模仿大佬演奏的动作，使用丝杆步进电机来精确控制钢尺移动、
+使用一个舵机压住钢尺、另一个舵机弹拨钢尺</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -542,111 +626,83 @@
         <charset val="134"/>
       </rPr>
       <t>，最多只能取其二，其中：
-sg90舵机，力量大、体积小、速度慢
-无刷电机，速度快、体积小，力量小
-3D打印机常用的42步进电机，速度快、力量大、体积大</t>
+sg90舵机，力量大、体积小、但速度慢↓
+小无刷电机，速度快、体积小，但力量小↓
+3D打印机常用的42步进电机，速度快、力量大、但体积大↓</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO：需要实测一下瀑布图，看看频率变化</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>我：那怎么办呢？
 刘华强：那，吸铁石
-我：谁说一定要用舵机呢！钢尺嘛，可以用电磁铁来吸住他
+我：对呀！谁说一定要用舵机呢。钢尺嘛，可以用电磁铁来吸住它
 我：看！还挺牢固的</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>解决了速度问题，下一个要解决的就是音不准的问题
-偏差有x.x%，如果偏差超过3%（50音分）就是明显跑调了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是因为我们常见的音乐都是使用十二平均律，将一个八度平均分成十二份,一份就是一个半音，一个半音音程等于100音分。假设我弹奏一个do，如果偏差小于50音分，它更接近do，可能有些不准但还可以听出来是do。但如果偏差超过50音分，那它就更接近升do了，也就是跑调了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>如何提高音准呢？
-此前调音是在桌面拨动钢尺，用手机测出几个基准长度的音高，而后拟合出频率-长度函数。演奏的时候通过目标频率换算出具体长度。但这样人工测量非常耗时，而且并不准确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>因此，需要添加一个麦克风，在不同长度的位置拨动钢尺，用麦克风采集音频并进行傅里叶变换，得到对应长度的频率。最终就可以拟合出一个高精度的频率-步进(step)曲线</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>既然为了调音增加了麦克风硬件，那为什么不物尽其用呢？
-esp32s3开发板刚好有usb接口，可以集成一个usb麦克风，连接电脑用来录音，获得更好的录音音质。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>还有一个问题，就是，乐谱的存储与传输
-原型机的谱子格式是自定义的：
-比如，("5#.", 1)：即表示高音升Sol，时长为一拍，用串口发送一个音符演奏一个音符
-这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:19-10:32 https://www.bilibili.com/video/BV187411r7hp/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>midi图示
-nokia tune播放视频
-5针、usb、RTS等物理接口
-麦克风--&gt;开发板-(usb线)-&gt;mic--&gt;电脑
-                                    -&gt;midi--&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哎！不知道你有没有听过一种技术叫MIDI，它即可以传输音符，又可以存储乐谱。
-功能机时代的诺基亚铃声，你一定听过
-它就是midi
-midi可以使用多种接口进行传输，比如usb接口。而刚好我们的开发板上就有usb接口。使用usb midi就是最好的选择了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>开发板乱糟糟的连线
-人+影视飓风的扭转特效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最后，使用面包板，各种连线实在太乱了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>画一个电路板，把它们整合起来</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>为了更方便复刻，都是使用的成品模块</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>几个焊接特写：焊接排母、安装元件（插入卡点）
-成品效果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>组装过程特写（按照装机区的那种风格）
-以安装器件，拧螺丝为主</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>取出模型--&gt;拿到工作台--&gt;掰下来</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果没有midi键盘，也可用手机的虚拟MIDI键盘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>手机midi键盘演示：do re mi fa。。。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不同力度弹奏midi键盘演示强弱
-原声--&gt;效果器（片头cyberpunk 2077 预告BGM演奏）
-口播出镜（拿着读最后一句台词）</t>
+    <t>口播出镜
+《华强买瓜》——吸铁石
+电磁铁吸住钢尺特写（尝试拨动，如果不行就静态展示）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO:删除</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>引子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢尺君</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯鸽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一根钢尺的艺术之旅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>up主</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>作品名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>佚名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>千本樱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大钢尺我的家乡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>only my railgun</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取出模型--&gt;拿到工作台--&gt;掰下来 / 一个响指出现在桌面</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -721,7 +777,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -742,7 +798,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -837,7 +911,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -889,12 +963,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -925,6 +993,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -943,7 +1014,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="45" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="45" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="45" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="45" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1221,32 +1313,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FBFDF2-C68F-43FE-8FE4-06F462270704}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="22" t="s">
-        <v>47</v>
+      <c r="A1" s="20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="22" t="s">
-        <v>49</v>
+      <c r="A5" s="20" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1261,7 +1358,7 @@
   <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="8.25" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="27" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="25" customWidth="1"/>
     <col min="4" max="5" width="62.83203125" style="6" customWidth="1"/>
     <col min="6" max="6" width="26.25" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" style="6" customWidth="1"/>
@@ -1270,13 +1367,13 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1292,927 +1389,936 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="49.5">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B2" s="5">
-        <v>0</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="33">
+      <c r="A3" s="5">
+        <f>A2+B2</f>
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="B3" s="4">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="36">
+        <f>A3+B3</f>
+        <v>1.7361111111111109E-4</v>
+      </c>
+      <c r="B4" s="37">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="33">
+      <c r="A5" s="5">
+        <f>A4+B4</f>
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="36">
+        <f>A5+B5</f>
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="B6" s="37">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="33">
-      <c r="A3" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="B3" s="5">
-        <f>B2+A2</f>
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="B4" s="5">
-        <f>B3+A3</f>
-        <v>1.7361111111111109E-4</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="33">
-      <c r="A5" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="B5" s="5">
-        <f t="shared" ref="B5:B56" si="0">B4+A4</f>
-        <v>2.8935185185185184E-4</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="B6" s="5">
-        <f t="shared" si="0"/>
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33">
-      <c r="A7" s="4">
+      <c r="A7" s="35">
+        <f>A6+B6</f>
+        <v>4.1666666666666664E-4</v>
+      </c>
+      <c r="B7" s="34">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="B7" s="5">
-        <f t="shared" si="0"/>
-        <v>4.1666666666666664E-4</v>
-      </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="28" t="s">
-        <v>98</v>
+      <c r="C7" s="29"/>
+      <c r="D7" s="26" t="s">
+        <v>89</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33">
-      <c r="A8" s="4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="49.5">
+      <c r="A8" s="35">
+        <f>A7+B7</f>
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="B8" s="34">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="B8" s="5">
-        <f t="shared" si="0"/>
-        <v>5.0925925925925921E-4</v>
-      </c>
-      <c r="C8" s="31"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="9" customFormat="1" ht="49.5">
-      <c r="A9" s="4">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="5">
+        <f>A8+B8</f>
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="B9" s="4">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="9" customFormat="1" ht="49.5">
+      <c r="A10" s="5">
+        <f>A8+B8</f>
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="B10" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="B9" s="5">
-        <f>B8+A8</f>
-        <v>5.5555555555555556E-4</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7" s="18" customFormat="1" ht="33">
-      <c r="A10" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="B10" s="5">
-        <f t="shared" si="0"/>
+      <c r="C10" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="33">
+      <c r="A11" s="5">
+        <f>A9+B9</f>
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="33">
+      <c r="A12" s="5">
+        <f>A10+B10</f>
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="17" t="s">
+      <c r="B12" s="4">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C12" s="30"/>
+      <c r="D12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="G10" s="17"/>
-    </row>
-    <row r="11" spans="1:7" ht="33">
-      <c r="A11" s="4">
-        <v>1.3888888888888889E-4</v>
-      </c>
-      <c r="B11" s="5">
-        <f>B10+A10</f>
-        <v>8.1018518518518516E-4</v>
-      </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:7" ht="33">
-      <c r="A12" s="4">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="B12" s="5">
-        <f t="shared" si="0"/>
-        <v>9.4907407407407408E-4</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>101</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" s="16" customFormat="1" ht="49.5">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
+        <f>A11+B11</f>
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="B13" s="4">
         <v>1.8518518518518518E-4</v>
       </c>
-      <c r="B13" s="5">
-        <f t="shared" si="0"/>
-        <v>1.0185185185185184E-3</v>
-      </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="31" t="s">
+        <v>50</v>
+      </c>
       <c r="D13" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>42</v>
+        <v>54</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="G13" s="14"/>
     </row>
     <row r="14" spans="1:7" s="16" customFormat="1" ht="49.5">
-      <c r="A14" s="4">
+      <c r="A14" s="5">
+        <f>A12+B12</f>
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="B14" s="4">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="B14" s="5">
-        <f t="shared" si="0"/>
-        <v>1.2037037037037036E-3</v>
-      </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
     </row>
     <row r="15" spans="1:7" s="16" customFormat="1" ht="115.5">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
+        <f>A13+B13</f>
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="B15" s="4">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="B15" s="5">
-        <f t="shared" si="0"/>
-        <v>1.435185185185185E-3</v>
-      </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:7" s="16" customFormat="1" ht="66">
-      <c r="A16" s="4">
+      <c r="A16" s="5">
+        <f>A14+B14</f>
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="B16" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B16" s="5">
-        <f t="shared" si="0"/>
-        <v>1.7824074074074072E-3</v>
-      </c>
-      <c r="C16" s="34"/>
+      <c r="C16" s="33"/>
       <c r="D16" s="13" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A17" s="4">
+      <c r="A17" s="5">
+        <f>A15+B15</f>
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="B17" s="4">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="B17" s="5">
-        <f t="shared" si="0"/>
-        <v>1.8981481481481479E-3</v>
-      </c>
-      <c r="C17" s="34"/>
+      <c r="C17" s="33"/>
       <c r="D17" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
     </row>
     <row r="18" spans="1:7" s="16" customFormat="1">
-      <c r="A18" s="4">
+      <c r="A18" s="5">
+        <f>A16+B16</f>
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="B18" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="B18" s="5">
-        <f t="shared" ref="B18:B22" si="1">B17+A17</f>
-        <v>1.9907407407407404E-3</v>
-      </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="24"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="22"/>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:7" ht="33">
-      <c r="A19" s="4">
+      <c r="A19" s="5">
+        <f>A17+B17</f>
+        <v>1.3773148148148149E-3</v>
+      </c>
+      <c r="B19" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B19" s="5">
-        <f t="shared" si="0"/>
-        <v>2.0023148148148144E-3</v>
-      </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="33"/>
       <c r="D19" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" ht="66">
-      <c r="A20" s="4">
+      <c r="A20" s="5">
+        <f>A18+B18</f>
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="B20" s="4">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="B20" s="5">
-        <f t="shared" si="1"/>
-        <v>2.1180555555555553E-3</v>
-      </c>
-      <c r="C20" s="34"/>
+      <c r="C20" s="33"/>
       <c r="D20" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="G20" s="8" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="66">
-      <c r="A21" s="4">
+      <c r="A21" s="5">
+        <f>A19+B19</f>
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="B21" s="4">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="B21" s="5">
-        <f t="shared" si="0"/>
-        <v>2.5231481481481481E-3</v>
-      </c>
-      <c r="C21" s="34"/>
+      <c r="C21" s="33"/>
       <c r="D21" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="49.5">
-      <c r="A22" s="4">
+      <c r="A22" s="5">
+        <f>A20+B20</f>
+        <v>1.5277777777777776E-3</v>
+      </c>
+      <c r="B22" s="4">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="B22" s="5">
-        <f t="shared" si="1"/>
-        <v>2.8124999999999999E-3</v>
-      </c>
-      <c r="C22" s="34"/>
+      <c r="C22" s="33"/>
       <c r="D22" s="10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="34"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="33"/>
       <c r="D23" s="11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" spans="1:7" s="19" customFormat="1" ht="49.5">
-      <c r="A24" s="4">
+    <row r="24" spans="1:7" s="17" customFormat="1" ht="49.5">
+      <c r="A24" s="5">
+        <f>A22+B22</f>
+        <v>1.8171296296296295E-3</v>
+      </c>
+      <c r="B24" s="4">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="B24" s="5">
-        <f>B22+A22</f>
-        <v>3.1018518518518517E-3</v>
-      </c>
-      <c r="C24" s="34"/>
+      <c r="C24" s="33"/>
       <c r="D24" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
     </row>
-    <row r="25" spans="1:7" s="19" customFormat="1">
-      <c r="A25" s="4">
+    <row r="25" spans="1:7" s="17" customFormat="1">
+      <c r="A25" s="5">
+        <f>A24+B24</f>
+        <v>1.9907407407407404E-3</v>
+      </c>
+      <c r="B25" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="B25" s="5">
-        <f t="shared" si="0"/>
-        <v>3.2754629629629627E-3</v>
-      </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="24"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="22"/>
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
     </row>
     <row r="26" spans="1:7" ht="82.5">
-      <c r="A26" s="4">
+      <c r="A26" s="5">
+        <f>A25+B25</f>
+        <v>2.0023148148148144E-3</v>
+      </c>
+      <c r="B26" s="4">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="B26" s="5">
-        <f t="shared" si="0"/>
-        <v>3.2870370370370367E-3</v>
-      </c>
-      <c r="C26" s="34"/>
+      <c r="C26" s="33"/>
       <c r="D26" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" ht="99">
-      <c r="A27" s="4">
+      <c r="A27" s="5">
+        <f>A26+B26</f>
+        <v>2.2337962962962958E-3</v>
+      </c>
+      <c r="B27" s="4">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="B27" s="5">
-        <f t="shared" si="0"/>
-        <v>3.518518518518518E-3</v>
-      </c>
-      <c r="C27" s="34"/>
+      <c r="C27" s="33"/>
       <c r="D27" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="4">
+      <c r="A28" s="5">
+        <f>A27+B27</f>
+        <v>2.6967592592592586E-3</v>
+      </c>
+      <c r="B28" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="B28" s="5">
-        <f t="shared" si="0"/>
-        <v>3.9814814814814808E-3</v>
-      </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="21" t="s">
-        <v>82</v>
+      <c r="C28" s="33"/>
+      <c r="D28" s="19" t="s">
+        <v>78</v>
       </c>
       <c r="E28" s="12"/>
     </row>
     <row r="29" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A29" s="4">
+      <c r="A29" s="5">
+        <f>A28+B28</f>
+        <v>2.7083333333333326E-3</v>
+      </c>
+      <c r="B29" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B29" s="5">
-        <f t="shared" si="0"/>
-        <v>3.9930555555555552E-3</v>
-      </c>
-      <c r="C29" s="34"/>
+      <c r="C29" s="33"/>
       <c r="D29" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>115</v>
+        <v>101</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
     </row>
     <row r="30" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A30" s="4">
+      <c r="A30" s="5">
+        <f>A29+B29</f>
+        <v>2.8240740740740735E-3</v>
+      </c>
+      <c r="B30" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="B30" s="5">
-        <f t="shared" si="0"/>
-        <v>4.1087962962962962E-3</v>
-      </c>
-      <c r="C30" s="33"/>
+      <c r="C30" s="32"/>
       <c r="D30" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="5">
+        <f>A30+B30</f>
+        <v>2.8819444444444439E-3</v>
+      </c>
+      <c r="B31" s="4">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="36">
+        <f>A31+B31</f>
+        <v>2.9398148148148144E-3</v>
+      </c>
+      <c r="B32" s="37">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C32" s="33"/>
+      <c r="D32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="5">
+        <f>A32+B32</f>
+        <v>3.0555555555555553E-3</v>
+      </c>
+      <c r="B33" s="4">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="D33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="33">
+      <c r="A34" s="36">
+        <f>A33+B33</f>
+        <v>3.1134259259259257E-3</v>
+      </c>
+      <c r="B34" s="37">
+        <v>5.7870370370370378E-4</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="36">
+        <f>A34+B34</f>
+        <v>3.6921296296296294E-3</v>
+      </c>
+      <c r="B35" s="37">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="C35" s="33"/>
+      <c r="D35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="36">
+        <f>A35+B35</f>
+        <v>3.8310185185185183E-3</v>
+      </c>
+      <c r="B36" s="37">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C36" s="33"/>
+      <c r="D36" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="38">
+        <f>A36+B36</f>
+        <v>3.8888888888888888E-3</v>
+      </c>
+      <c r="B37" s="39">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C37" s="33"/>
+      <c r="D37" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="33">
+      <c r="A38" s="40">
+        <f>A37+B37</f>
+        <v>3.9467592592592592E-3</v>
+      </c>
+      <c r="B38" s="41">
+        <v>5.7870370370370378E-4</v>
+      </c>
+      <c r="C38" s="33"/>
+      <c r="D38" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="5">
+        <f>A38+B38</f>
+        <v>4.5254629629629629E-3</v>
+      </c>
+      <c r="B39" s="4">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C39" s="33"/>
+      <c r="D39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="4">
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="5">
+        <f>A39+B39</f>
+        <v>4.5833333333333334E-3</v>
+      </c>
+      <c r="B40" s="4">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="C40" s="33"/>
+      <c r="D40" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="5">
+        <f>A40+B40</f>
+        <v>4.6180555555555558E-3</v>
+      </c>
+      <c r="B41" s="4">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="C41" s="32"/>
+      <c r="D41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="66">
+      <c r="A42" s="5">
+        <f>A41+B41</f>
+        <v>4.6643518518518518E-3</v>
+      </c>
+      <c r="B42" s="4">
+        <v>4.6296296296296293E-4</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="5">
+        <f>A42+B42</f>
+        <v>5.1273148148148146E-3</v>
+      </c>
+      <c r="B43" s="4">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="C43" s="33"/>
+      <c r="D43" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="82.5">
+      <c r="A44" s="5">
+        <f>A43+B43</f>
+        <v>5.1504629629629626E-3</v>
+      </c>
+      <c r="B44" s="4">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="C44" s="33"/>
+      <c r="D44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="5">
+        <f>A44+B44</f>
+        <v>5.5555555555555549E-3</v>
+      </c>
+      <c r="B45" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C45" s="33"/>
+      <c r="D45" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="5"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G46" s="7"/>
+    </row>
+    <row r="47" spans="1:7" ht="66">
+      <c r="A47" s="5">
+        <f>A45+B45</f>
+        <v>5.5671296296296293E-3</v>
+      </c>
+      <c r="B47" s="4">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="C47" s="32"/>
+      <c r="D47" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="5">
+        <f>A47+B47</f>
+        <v>5.9722222222222216E-3</v>
+      </c>
+      <c r="B48" s="4">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="5">
+        <f>A48+B48</f>
+        <v>6.0069444444444441E-3</v>
+      </c>
+      <c r="B49" s="4">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="C49" s="33"/>
+      <c r="D49" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="5">
+        <f>A49+B49</f>
+        <v>6.0532407407407401E-3</v>
+      </c>
+      <c r="B50" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="B31" s="5">
-        <f t="shared" si="0"/>
-        <v>4.1666666666666666E-3</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="4">
+      <c r="C50" s="33"/>
+      <c r="D50" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="33">
+      <c r="A51" s="5">
+        <f>A50+B50</f>
+        <v>6.1111111111111106E-3</v>
+      </c>
+      <c r="B51" s="4">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="B32" s="5">
-        <f t="shared" si="0"/>
-        <v>4.2245370370370371E-3</v>
-      </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="6" t="s">
+      <c r="C51" s="33"/>
+      <c r="D51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="5">
+        <f>A51+B51</f>
+        <v>6.1805555555555546E-3</v>
+      </c>
+      <c r="B52" s="4">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C52" s="32"/>
+      <c r="D52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="49.5">
+      <c r="A53" s="5">
+        <f>A52+B52</f>
+        <v>6.2499999999999986E-3</v>
+      </c>
+      <c r="B53" s="4">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C53" s="21"/>
+      <c r="D53" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="B33" s="5">
-        <f t="shared" si="0"/>
-        <v>4.2939814814814811E-3</v>
-      </c>
-      <c r="C33" s="34"/>
-      <c r="D33" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="6" t="s">
+    </row>
+    <row r="54" spans="1:7" ht="33">
+      <c r="A54" s="5">
+        <f>A53+B53</f>
+        <v>6.3657407407407395E-3</v>
+      </c>
+      <c r="B54" s="4">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C54" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="132">
+      <c r="A55" s="5">
+        <f>A54+B54</f>
+        <v>6.4814814814814804E-3</v>
+      </c>
+      <c r="B55" s="4">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="C55" s="32"/>
+      <c r="D55" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G55" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="33">
-      <c r="A34" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="B34" s="5">
-        <f t="shared" si="0"/>
-        <v>4.3518518518518515E-3</v>
-      </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="B35" s="5">
-        <f t="shared" si="0"/>
-        <v>4.4675925925925924E-3</v>
-      </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="B36" s="5">
-        <f t="shared" si="0"/>
-        <v>4.5254629629629629E-3</v>
-      </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="B37" s="5">
-        <f t="shared" si="0"/>
-        <v>4.5833333333333334E-3</v>
-      </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:7" ht="33">
-      <c r="A38" s="4">
-        <v>1.7361111111111112E-4</v>
-      </c>
-      <c r="B38" s="5">
-        <f t="shared" si="0"/>
-        <v>4.6412037037037038E-3</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="B39" s="5">
-        <f t="shared" si="0"/>
-        <v>4.8148148148148152E-3</v>
-      </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="4">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="B40" s="5">
-        <f t="shared" si="0"/>
-        <v>4.8726851851851856E-3</v>
-      </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="4">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="B41" s="5">
-        <f t="shared" si="0"/>
-        <v>4.9074074074074081E-3</v>
-      </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="66">
-      <c r="A42" s="4">
-        <v>4.6296296296296293E-4</v>
-      </c>
-      <c r="B42" s="5">
-        <f t="shared" si="0"/>
-        <v>4.9537037037037041E-3</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="4">
-        <v>2.3148148148148147E-5</v>
-      </c>
-      <c r="B43" s="5">
-        <f t="shared" si="0"/>
-        <v>5.4166666666666669E-3</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="82.5">
-      <c r="A44" s="4">
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="B44" s="5">
-        <f t="shared" si="0"/>
-        <v>5.4398148148148149E-3</v>
-      </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="B45" s="5">
-        <f t="shared" si="0"/>
-        <v>5.8449074074074072E-3</v>
-      </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="21" t="s">
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="5">
+        <f>A55+B55</f>
+        <v>7.9861111111111105E-3</v>
+      </c>
+      <c r="C56" s="25" t="s">
         <v>82</v>
-      </c>
-      <c r="G45" s="7"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G46" s="7"/>
-    </row>
-    <row r="47" spans="1:7" ht="66">
-      <c r="A47" s="4">
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="B47" s="5">
-        <f>B45+A45</f>
-        <v>5.8564814814814816E-3</v>
-      </c>
-      <c r="C47" s="33"/>
-      <c r="D47" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="4">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="B48" s="5">
-        <f>B47+A47</f>
-        <v>6.2615740740740739E-3</v>
-      </c>
-      <c r="C48" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="4">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="B49" s="5">
-        <f t="shared" si="0"/>
-        <v>6.2962962962962964E-3</v>
-      </c>
-      <c r="C49" s="34"/>
-      <c r="D49" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="B50" s="5">
-        <f t="shared" si="0"/>
-        <v>6.3425925925925924E-3</v>
-      </c>
-      <c r="C50" s="34"/>
-      <c r="D50" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="33">
-      <c r="A51" s="4">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="B51" s="5">
-        <f t="shared" si="0"/>
-        <v>6.4004629629629628E-3</v>
-      </c>
-      <c r="C51" s="34"/>
-      <c r="D51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="4">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="B52" s="5">
-        <f t="shared" si="0"/>
-        <v>6.4699074074074069E-3</v>
-      </c>
-      <c r="C52" s="33"/>
-      <c r="D52" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="49.5">
-      <c r="A53" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="B53" s="5">
-        <f t="shared" si="0"/>
-        <v>6.5393518518518509E-3</v>
-      </c>
-      <c r="C53" s="23"/>
-      <c r="E53" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="33">
-      <c r="A54" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="B54" s="5">
-        <f t="shared" si="0"/>
-        <v>6.6550925925925918E-3</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="132">
-      <c r="A55" s="4">
-        <v>1.5046296296296294E-3</v>
-      </c>
-      <c r="B55" s="5">
-        <f t="shared" si="0"/>
-        <v>6.7708333333333327E-3</v>
-      </c>
-      <c r="C55" s="33"/>
-      <c r="D55" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="B56" s="5">
-        <f t="shared" si="0"/>
-        <v>8.2754629629629619E-3</v>
-      </c>
-      <c r="C56" s="27" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2221,9 +2327,9 @@
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="C42:C47"/>
     <mergeCell ref="C31:C41"/>
-    <mergeCell ref="C12:C30"/>
-    <mergeCell ref="C9:C11"/>
     <mergeCell ref="C48:C52"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C13:C30"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2238,4 +2344,66 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D36613-7CBA-4B03-8002-86AF23254340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B928CA9-3714-458F-9477-6C58C5B77891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-130" yWindow="-130" windowWidth="25860" windowHeight="13940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封标" sheetId="4" r:id="rId1"/>
-    <sheet name="完整版" sheetId="1" r:id="rId2"/>
-    <sheet name="简洁版" sheetId="3" r:id="rId3"/>
-    <sheet name="素材引用" sheetId="5" r:id="rId4"/>
+    <sheet name="剧本" sheetId="1" r:id="rId2"/>
+    <sheet name="素材引用" sheetId="5" r:id="rId3"/>
+    <sheet name="雷达图制作" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="143">
   <si>
     <t>​​画面描述 (分镜)​​</t>
   </si>
@@ -81,10 +81,6 @@
   </si>
   <si>
     <t xml:space="preserve">​​时间戳 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>此前录制的慢放视频（使用类似进度条的东西，显示每部分时间占用）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -184,14 +180,6 @@
   <si>
     <t>哆啦A梦掏出：钢尺</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>手绘设计图展示
-每个器件特写气泡（根据口播节奏依次出现）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>演奏《哆啦A梦》</t>
   </si>
   <si>
     <t>（华强买瓜语音）</t>
@@ -270,16 +258,6 @@
   </si>
   <si>
     <t>口播出镜
-弹奏一个音+手机fft，浮现文字：误差xxx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
-麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
 展示一个串口谱子</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -290,11 +268,6 @@
   </si>
   <si>
     <t>演奏前：来看看效果吧！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
-演奏《哆啦A梦》</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -309,20 +282,6 @@
     <t>首先就是演奏速度比较慢
 慢速演奏完：这样已经是极限了
 如果调快速度就变成这样了！！这限制了它演奏很多快节奏的曲目</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢尺琴插入电源、插入数据线，按调音键调音（如果时间长就快进）
-mid键盘插入数据线
-打开宿主软件（先配置好，最小化），选择xxx设备
-使用MIDI键盘弹奏一小段音乐《欢乐颂》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>夺舍钢尺
-口播出镜
-废弃的3d打印件
-100多个commit屏幕滚动</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -365,13 +324,6 @@
   </si>
   <si>
     <t>夺舍BGM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>夺舍（使用伤心欲茄声音AI合成）：斯你麻赛，nice什么呀！修改了多少个版本才有现在的效果的呀？你是nice了，我的刻度线都磨没了，八嘎压路！
-我：这不是考虑到观众老爷的观看体验，将中间的调试过程压缩了么
-我：结构上迭代设计了很多版
-我：代码也是改了很多次，这里有100多个commit</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -487,13 +439,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>还有一个问题，就是，乐谱的存储与传输
-原型机的谱子格式是自定义的：
-比如，("5#.", 1)：即表示高音升Sol，时长为一拍，用串口发送一个音符演奏一个音符
-这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>10:19-10:32 https://www.bilibili.com/video/BV187411r7hp/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -567,20 +512,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>todo：测试哆啦A梦的演奏效果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>我：我一个程序员，让我弹钢尺，我能弹么？
-范志毅：“弹不了！没那个能力知道吧！”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>过渡到:
-Cyberuler 2025</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>怎么办呢？那就…上！科！技！
 “自动演奏的钢尺”
 让我们开始吧</t>
@@ -588,16 +519,6 @@
   </si>
   <si>
     <t>加加鸽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TODO:需要制作片头</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>我先设计了一个原型机验证可行性
-模仿大佬演奏的动作，使用丝杆步进电机来精确控制钢尺移动、
-使用一个舵机压住钢尺、另一个舵机弹拨钢尺</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -705,12 +626,171 @@
     <t>取出模型--&gt;拿到工作台--&gt;掰下来 / 一个响指出现在桌面</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>sg90舵机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>42步进电机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小无刷电机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应快</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体积小</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>扭力大</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>演奏《小星星》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">夺舍（使用伤心欲茄声音AI合成）：斯你麻赛，nice什么呀！修改了多少个版本才有现在的效果的呀？你是nice了，我的刻度线都磨没了，八嘎压路！
+我：这不是考虑到观众老爷的观看体验，将中间的调试过程压缩了么
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我：结构上迭代设计了很多版，看，盒子里有好多
+我：代码也是改了很多次，这里有100多个commit</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夺舍钢尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+口播出镜
+废弃的3d打印件
+100多个commit屏幕滚动</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我：我一个程序员，让我弹钢尺，我能弹么？弹不了！
+范志毅：“没这个能力知道吧！”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过渡到:
+Cyberuler 2025，添加文本特效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口播出镜
+原型机演奏《小星星》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口播出镜
+自动弹奏一个音+手机fft，浮现文字：误差xxx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>演奏一个音符的慢放视频（使用类似进度条的东西，显示每部分时间占用）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我先设计了一个原型机验证可行性
+模仿演奏的动作，使用丝杆步进电机来精确控制钢尺移动、
+使用一个舵机压住钢尺、另一个舵机弹拨钢尺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>手绘设计图展示</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（舵机、丝杆步进电机）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+每个器件特写气泡（根据口播节奏依次出现）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口播出镜
+麦克风--&gt;开发板-(usb线)-&gt;mic--电脑
+添加一个DRI Mic的在音频设备中的截图</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>还有一个问题，就是，乐谱的存储与传输
+原型机的谱子格式是自定义的：
+比如，("5", 1)：即表示Sol，时长为一拍，用串口发送一个音符演奏一个音符
+这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="等线"/>
@@ -776,6 +856,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -810,13 +897,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -911,7 +998,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -993,7 +1080,22 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="45" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="45" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1014,28 +1116,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="45" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="21" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="45" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="45" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="45" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="45" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1053,6 +1158,1040 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.44070841380676479"/>
+          <c:y val="0.16961546837213035"/>
+          <c:w val="0.5827211133492034"/>
+          <c:h val="0.7869142968699161"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>雷达图制作!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>sg90舵机</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>雷达图制作!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>响应快</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>体积小</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>扭力大</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>雷达图制作!$B$2:$D$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B37B-435F-A1A5-5285699195E0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>雷达图制作!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>小无刷电机</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>雷达图制作!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>响应快</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>体积小</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>扭力大</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>雷达图制作!$B$3:$D$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B37B-435F-A1A5-5285699195E0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>雷达图制作!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>42步进电机</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>雷达图制作!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>响应快</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>体积小</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>扭力大</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>雷达图制作!$B$4:$D$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B37B-435F-A1A5-5285699195E0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="173882544"/>
+        <c:axId val="173883984"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="173882544"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="173883984"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="173883984"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="173882544"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.28782548407864111"/>
+          <c:y val="3.7845705967976713E-2"/>
+          <c:w val="0.38580779900267165"/>
+          <c:h val="4.7691427432033286E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>176212</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>100013</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>133349</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19E40572-40B7-3FA3-1CE0-D8AB9EBEB94E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1318,32 +2457,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1373,7 +2512,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1389,392 +2528,387 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="49.5">
-      <c r="A2" s="5">
+      <c r="A2" s="28">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="27">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C2" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="33">
+      <c r="A3" s="28">
+        <f t="shared" ref="A3:A9" si="0">A2+B2</f>
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="B3" s="27">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="29">
+        <f t="shared" si="0"/>
+        <v>1.7361111111111109E-4</v>
+      </c>
+      <c r="B4" s="30">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="33">
+      <c r="A5" s="28">
+        <f t="shared" si="0"/>
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="B5" s="27">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="33">
-      <c r="A3" s="5">
-        <f>A2+B2</f>
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="B3" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="36">
-        <f>A3+B3</f>
-        <v>1.7361111111111109E-4</v>
-      </c>
-      <c r="B4" s="37">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="E5" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="29">
+        <f t="shared" si="0"/>
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="B6" s="30">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="6" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="33">
-      <c r="A5" s="5">
-        <f>A4+B4</f>
-        <v>2.8935185185185184E-4</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="36">
-        <f>A5+B5</f>
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="B6" s="37">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="33">
+      <c r="A7" s="28">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666664E-4</v>
+      </c>
+      <c r="B7" s="27">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="49.5">
+      <c r="A8" s="28">
+        <f t="shared" si="0"/>
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="B8" s="27">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="33">
-      <c r="A7" s="35">
-        <f>A6+B6</f>
-        <v>4.1666666666666664E-4</v>
-      </c>
-      <c r="B7" s="34">
-        <v>9.2592592592592588E-5</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="49.5">
-      <c r="A8" s="35">
-        <f>A7+B7</f>
-        <v>5.0925925925925921E-4</v>
-      </c>
-      <c r="B8" s="34">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="5">
-        <f>A8+B8</f>
+      <c r="A9" s="28">
+        <f t="shared" si="0"/>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="27">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="9" customFormat="1" ht="49.5">
-      <c r="A10" s="5">
-        <f>A8+B8</f>
+      <c r="A10" s="39">
+        <f t="shared" ref="A10:A22" si="1">A8+B8</f>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="40">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>38</v>
+      <c r="C10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>139</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="33">
-      <c r="A11" s="5">
-        <f>A9+B9</f>
+      <c r="A11" s="28">
+        <f t="shared" si="1"/>
         <v>6.134259259259259E-4</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="27">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="6" t="s">
-        <v>60</v>
+      <c r="C11" s="34"/>
+      <c r="D11" s="41" t="s">
+        <v>135</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F11" s="10"/>
-      <c r="G11" s="11" t="s">
-        <v>113</v>
-      </c>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="33">
       <c r="A12" s="5">
-        <f>A10+B10</f>
+        <f t="shared" si="1"/>
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="B12" s="4">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C12" s="30"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" s="16" customFormat="1" ht="49.5">
       <c r="A13" s="5">
-        <f>A11+B11</f>
+        <f t="shared" si="1"/>
         <v>7.5231481481481482E-4</v>
       </c>
       <c r="B13" s="4">
         <v>1.8518518518518518E-4</v>
       </c>
-      <c r="C13" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>54</v>
+      <c r="C13" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="G13" s="14"/>
     </row>
     <row r="14" spans="1:7" s="16" customFormat="1" ht="49.5">
-      <c r="A14" s="5">
-        <f>A12+B12</f>
+      <c r="A14" s="28">
+        <f t="shared" si="1"/>
         <v>7.6388888888888893E-4</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="27">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="C14" s="33"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="14" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
     </row>
     <row r="15" spans="1:7" s="16" customFormat="1" ht="115.5">
-      <c r="A15" s="5">
-        <f>A13+B13</f>
+      <c r="A15" s="28">
+        <f t="shared" si="1"/>
         <v>9.3749999999999997E-4</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="27">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C15" s="33"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:7" s="16" customFormat="1" ht="66">
-      <c r="A16" s="5">
-        <f>A14+B14</f>
+      <c r="A16" s="28">
+        <f t="shared" si="1"/>
         <v>9.9537037037037042E-4</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="27">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C16" s="33"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="13" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A17" s="5">
-        <f>A15+B15</f>
+      <c r="A17" s="28">
+        <f t="shared" si="1"/>
         <v>1.2847222222222223E-3</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="27">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="13" t="s">
-        <v>41</v>
+      <c r="C17" s="38"/>
+      <c r="D17" s="32" t="s">
+        <v>38</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
     </row>
     <row r="18" spans="1:7" s="16" customFormat="1">
       <c r="A18" s="5">
-        <f>A16+B16</f>
+        <f t="shared" si="1"/>
         <v>1.1111111111111111E-3</v>
       </c>
       <c r="B18" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C18" s="33"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="19" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:7" ht="33">
-      <c r="A19" s="5">
-        <f>A17+B17</f>
+      <c r="A19" s="39">
+        <f t="shared" si="1"/>
         <v>1.3773148148148149E-3</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="40">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="6" t="s">
-        <v>55</v>
+      <c r="C19" s="38"/>
+      <c r="D19" s="32" t="s">
+        <v>136</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:7" ht="66">
-      <c r="A20" s="5">
-        <f>A18+B18</f>
+    <row r="20" spans="1:7" s="47" customFormat="1" ht="66">
+      <c r="A20" s="42">
+        <f t="shared" si="1"/>
         <v>1.1226851851851851E-3</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="43">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8" t="s">
-        <v>121</v>
+      <c r="C20" s="38"/>
+      <c r="D20" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="66">
-      <c r="A21" s="5">
-        <f>A19+B19</f>
+      <c r="A21" s="39">
+        <f t="shared" si="1"/>
         <v>1.4930555555555556E-3</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="40">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="6" t="s">
-        <v>47</v>
+      <c r="C21" s="38"/>
+      <c r="D21" s="32" t="s">
+        <v>44</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="49.5">
-      <c r="A22" s="5">
-        <f>A20+B20</f>
+      <c r="A22" s="28">
+        <f t="shared" si="1"/>
         <v>1.5277777777777776E-3</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="27">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C22" s="33"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="5"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="33"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="11" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E23" s="10"/>
     </row>
@@ -1786,197 +2920,197 @@
       <c r="B24" s="4">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="13" t="s">
-        <v>56</v>
+      <c r="C24" s="38"/>
+      <c r="D24" s="32" t="s">
+        <v>140</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:7" s="17" customFormat="1">
       <c r="A25" s="5">
-        <f>A24+B24</f>
+        <f t="shared" ref="A25:A47" si="2">A24+B24</f>
         <v>1.9907407407407404E-3</v>
       </c>
       <c r="B25" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C25" s="33"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="19" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" ht="82.5">
+    <row r="26" spans="1:7" ht="66">
       <c r="A26" s="5">
-        <f>A25+B25</f>
+        <f t="shared" si="2"/>
         <v>2.0023148148148144E-3</v>
       </c>
       <c r="B26" s="4">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="C26" s="33"/>
+      <c r="C26" s="38"/>
       <c r="D26" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" ht="99">
       <c r="A27" s="5">
-        <f>A26+B26</f>
+        <f t="shared" si="2"/>
         <v>2.2337962962962958E-3</v>
       </c>
       <c r="B27" s="4">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="C27" s="33"/>
+      <c r="C27" s="38"/>
       <c r="D27" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="5">
-        <f>A27+B27</f>
+        <f t="shared" si="2"/>
         <v>2.6967592592592586E-3</v>
       </c>
       <c r="B28" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C28" s="33"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="19" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E28" s="12"/>
     </row>
     <row r="29" spans="1:7" s="16" customFormat="1" ht="33">
       <c r="A29" s="5">
-        <f>A28+B28</f>
+        <f t="shared" si="2"/>
         <v>2.7083333333333326E-3</v>
       </c>
       <c r="B29" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="13" t="s">
-        <v>101</v>
+      <c r="C29" s="38"/>
+      <c r="D29" s="32" t="s">
+        <v>91</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
     </row>
     <row r="30" spans="1:7" s="16" customFormat="1" ht="33">
       <c r="A30" s="5">
-        <f>A29+B29</f>
+        <f t="shared" si="2"/>
         <v>2.8240740740740735E-3</v>
       </c>
       <c r="B30" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C30" s="32"/>
+      <c r="C30" s="37"/>
       <c r="D30" s="13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="5">
-        <f>A30+B30</f>
+        <f t="shared" si="2"/>
         <v>2.8819444444444439E-3</v>
       </c>
       <c r="B31" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C31" s="31" t="s">
-        <v>29</v>
+      <c r="C31" s="36" t="s">
+        <v>28</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="36">
-        <f>A31+B31</f>
+      <c r="A32" s="29">
+        <f t="shared" si="2"/>
         <v>2.9398148148148144E-3</v>
       </c>
-      <c r="B32" s="37">
+      <c r="B32" s="30">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C32" s="33"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="5">
-        <f>A32+B32</f>
+        <f t="shared" si="2"/>
         <v>3.0555555555555553E-3</v>
       </c>
       <c r="B33" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C33" s="33"/>
+      <c r="C33" s="38"/>
       <c r="D33" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="33">
-      <c r="A34" s="36">
-        <f>A33+B33</f>
+      <c r="A34" s="29">
+        <f t="shared" si="2"/>
         <v>3.1134259259259257E-3</v>
       </c>
-      <c r="B34" s="37">
+      <c r="B34" s="30">
         <v>5.7870370370370378E-4</v>
       </c>
-      <c r="C34" s="33"/>
+      <c r="C34" s="38"/>
       <c r="D34" s="6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="36">
-        <f>A34+B34</f>
+      <c r="A35" s="29">
+        <f t="shared" si="2"/>
         <v>3.6921296296296294E-3</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="30">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C35" s="33"/>
+      <c r="C35" s="38"/>
       <c r="D35" s="6" t="s">
         <v>7</v>
       </c>
@@ -1986,339 +3120,344 @@
       <c r="F35" s="7"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="36">
-        <f>A35+B35</f>
+      <c r="A36" s="29">
+        <f t="shared" si="2"/>
         <v>3.8310185185185183E-3</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="30">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C36" s="33"/>
+      <c r="C36" s="38"/>
       <c r="D36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="7"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="38">
-        <f>A36+B36</f>
+      <c r="A37" s="29">
+        <f t="shared" si="2"/>
         <v>3.8888888888888888E-3</v>
       </c>
-      <c r="B37" s="39">
+      <c r="B37" s="30">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C37" s="33"/>
+      <c r="C37" s="38"/>
       <c r="D37" s="6" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F37" s="7"/>
     </row>
     <row r="38" spans="1:7" ht="33">
-      <c r="A38" s="40">
-        <f>A37+B37</f>
+      <c r="A38" s="29">
+        <f t="shared" si="2"/>
         <v>3.9467592592592592E-3</v>
       </c>
-      <c r="B38" s="41">
+      <c r="B38" s="30">
         <v>5.7870370370370378E-4</v>
       </c>
-      <c r="C38" s="33"/>
+      <c r="C38" s="38"/>
       <c r="D38" s="6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F38" s="7"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="5">
-        <f>A38+B38</f>
+        <f t="shared" si="2"/>
         <v>4.5254629629629629E-3</v>
       </c>
       <c r="B39" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C39" s="33"/>
-      <c r="D39" s="6" t="s">
+      <c r="C39" s="38"/>
+      <c r="D39" s="32" t="s">
         <v>9</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="5">
-        <f>A39+B39</f>
+        <f t="shared" si="2"/>
         <v>4.5833333333333334E-3</v>
       </c>
       <c r="B40" s="4">
         <v>3.4722222222222222E-5</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="6" t="s">
-        <v>72</v>
+      <c r="C40" s="38"/>
+      <c r="D40" s="32" t="s">
+        <v>64</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F40" s="7"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="5">
-        <f>A40+B40</f>
+      <c r="A41" s="28">
+        <f t="shared" si="2"/>
         <v>4.6180555555555558E-3</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="27">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C41" s="32"/>
+      <c r="C41" s="37"/>
       <c r="D41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="66">
-      <c r="A42" s="5">
-        <f>A41+B41</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="33">
+      <c r="A42" s="28">
+        <f t="shared" si="2"/>
         <v>4.6643518518518518E-3</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="27">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="C42" s="31" t="s">
-        <v>28</v>
+      <c r="C42" s="36" t="s">
+        <v>27</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="5">
-        <f>A42+B42</f>
+        <f t="shared" si="2"/>
         <v>5.1273148148148146E-3</v>
       </c>
       <c r="B43" s="4">
         <v>2.3148148148148147E-5</v>
       </c>
-      <c r="C43" s="33"/>
+      <c r="C43" s="38"/>
       <c r="D43" s="6" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="82.5">
       <c r="A44" s="5">
-        <f>A43+B43</f>
+        <f t="shared" si="2"/>
         <v>5.1504629629629626E-3</v>
       </c>
       <c r="B44" s="4">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C44" s="33"/>
+      <c r="C44" s="38"/>
       <c r="D44" s="6" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="5">
-        <f>A44+B44</f>
+        <f t="shared" si="2"/>
         <v>5.5555555555555549E-3</v>
       </c>
       <c r="B45" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C45" s="33"/>
+      <c r="C45" s="38"/>
       <c r="D45" s="19" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="5"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="27" t="s">
-        <v>108</v>
+      <c r="A46" s="5">
+        <f t="shared" si="2"/>
+        <v>5.5671296296296293E-3</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C46" s="38"/>
+      <c r="D46" s="31" t="s">
+        <v>98</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:7" ht="66">
       <c r="A47" s="5">
-        <f>A45+B45</f>
-        <v>5.5671296296296293E-3</v>
+        <f t="shared" si="2"/>
+        <v>5.6828703703703702E-3</v>
       </c>
       <c r="B47" s="4">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="6" t="s">
-        <v>109</v>
+      <c r="C47" s="37"/>
+      <c r="D47" s="32" t="s">
+        <v>99</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="5">
-        <f>A47+B47</f>
-        <v>5.9722222222222216E-3</v>
+        <f t="shared" ref="A48:A56" si="3">A47+B47</f>
+        <v>6.0879629629629626E-3</v>
       </c>
       <c r="B48" s="4">
         <v>3.4722222222222222E-5</v>
       </c>
-      <c r="C48" s="31" t="s">
-        <v>27</v>
+      <c r="C48" s="36" t="s">
+        <v>26</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="5">
-        <f>A48+B48</f>
-        <v>6.0069444444444441E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.122685185185185E-3</v>
       </c>
       <c r="B49" s="4">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C49" s="33"/>
-      <c r="D49" s="6" t="s">
-        <v>19</v>
+      <c r="C49" s="38"/>
+      <c r="D49" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="5">
-        <f>A49+B49</f>
-        <v>6.0532407407407401E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.168981481481481E-3</v>
       </c>
       <c r="B50" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C50" s="33"/>
-      <c r="D50" s="6" t="s">
+      <c r="C50" s="38"/>
+      <c r="D50" s="32" t="s">
         <v>11</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="33">
       <c r="A51" s="5">
-        <f>A50+B50</f>
-        <v>6.1111111111111106E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.2268518518518515E-3</v>
       </c>
       <c r="B51" s="4">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C51" s="33"/>
-      <c r="D51" s="6" t="s">
+      <c r="C51" s="38"/>
+      <c r="D51" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="5">
-        <f>A51+B51</f>
-        <v>6.1805555555555546E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.2962962962962955E-3</v>
       </c>
       <c r="B52" s="4">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="6" t="s">
-        <v>23</v>
+      <c r="C52" s="37"/>
+      <c r="D52" s="32" t="s">
+        <v>22</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="49.5">
       <c r="A53" s="5">
-        <f>A52+B52</f>
-        <v>6.2499999999999986E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.3657407407407395E-3</v>
       </c>
       <c r="B53" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C53" s="21"/>
       <c r="D53" s="6" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="33">
       <c r="A54" s="5">
-        <f>A53+B53</f>
-        <v>6.3657407407407395E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.4814814814814804E-3</v>
       </c>
       <c r="B54" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C54" s="31" t="s">
-        <v>26</v>
+      <c r="C54" s="36" t="s">
+        <v>25</v>
       </c>
       <c r="D54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F54" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="132">
       <c r="A55" s="5">
-        <f>A54+B54</f>
-        <v>6.4814814814814804E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.5972222222222213E-3</v>
       </c>
       <c r="B55" s="4">
         <v>1.5046296296296294E-3</v>
       </c>
-      <c r="C55" s="32"/>
+      <c r="C55" s="37"/>
       <c r="D55" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="5">
-        <f>A55+B55</f>
-        <v>7.9861111111111105E-3</v>
+        <f t="shared" si="3"/>
+        <v>8.1018518518518514E-3</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2337,16 +3476,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{543450A5-C08D-4873-BAC4-1F306BA55BCC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -2357,16 +3486,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2374,10 +3503,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2385,10 +3514,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2396,14 +3525,82 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D1F29C-200F-4BB5-9251-208FEB1786B7}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="B1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B928CA9-3714-458F-9477-6C58C5B77891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4D9E5B-5BC9-4182-838F-078339DDD8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-130" yWindow="-130" windowWidth="25860" windowHeight="13940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封标" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="138">
   <si>
     <t>​​画面描述 (分镜)​​</t>
   </si>
@@ -62,9 +62,6 @@
     <t>响指</t>
   </si>
   <si>
-    <t>重新建模，将主板与钢尺、电机等整合在一起</t>
-  </si>
-  <si>
     <t>模型爆炸图</t>
   </si>
   <si>
@@ -77,18 +74,11 @@
     <t>主要模块的代码展示</t>
   </si>
   <si>
-    <t>笔吹奏演示</t>
-  </si>
-  <si>
     <t xml:space="preserve">​​时间戳 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>在屏幕前打一个响指，PCB出现在桌面</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>按照新的设计，开干！！！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -105,31 +95,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>拨动钢尺演奏示意</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是管乐</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pen beats演示（两次动次打次）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>第二遍跟读：动次打次
-这是打击乐</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>贝斯（钢尺），长笛（笔），架子鼓（笔）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1个钢尺琴--&gt;2个钢尺琴--&gt;3个钢尺琴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>气泡音</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -159,14 +124,6 @@
   </si>
   <si>
     <t>片头</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>手动演奏一个《小星星》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>早年在b站看大佬用钢尺演奏太酷了！我也要！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -188,10 +145,6 @@
   <si>
     <t>当前滑块特写
 光驱内部结构特写</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>连线图待绘制</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -252,26 +205,11 @@
   </si>
   <si>
     <t>口播出镜
-慢速演奏（正常）
-快速（无法压住钢尺，节奏乱掉）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
 展示一个串口谱子</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>连线图
-外面一个框浮现</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>演奏前：来看看效果吧！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>接下来就要注入灵魂，撸代码！！！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -299,14 +237,6 @@
     <t>口播出镜</t>
   </si>
   <si>
-    <t>不过一只钢尺演奏难免有些单调，所以我希望在增加几个乐器</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>怎么样？这个赛博钢尺琴是不是还有点意思？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>赛 博 钢 尺 琴——DIY自动演奏的钢尺</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -323,26 +253,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>夺舍BGM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最后的最后，虽然只有一种乐器，也可以用多个组多声部
-接下来就以一首《卡农》作为结尾</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>一个转场动画</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>钢琴一个八度的排列，12个音
-切换到特写键盘do与升do
-指示&lt;50音分偏差
-指示&gt;50音分偏差</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>原理图--&gt;pcb--&gt;2D渲染图</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -352,10 +266,6 @@
   </si>
   <si>
     <t>结束</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>再加上钢尺作为贝斯，让它们组一个文具乐队！！！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -374,10 +284,6 @@
   </si>
   <si>
     <t>《spoiler》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢尺君演奏片段</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -416,29 +322,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>解决了速度问题，下一个要解决的就是音不准的问题
-偏差有x.x%，如果偏差超过3%（50音分）就是明显跑调了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是因为我们常见的音乐都是使用十二平均律，将一个八度平均分成十二份,一份就是一个半音，一个半音音程等于100音分。假设我弹奏一个do，如果偏差小于50音分，它更接近do，可能有些不准但还可以听出来是do。但如果偏差超过50音分，那它就更接近升do了，也就是跑调了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>如何提高音准呢？
-此前调音是在桌面拨动钢尺，用手机测出几个基准长度的音高，而后拟合出频率-长度函数。演奏的时候通过目标频率换算出具体长度。但这样人工测量非常耗时，而且并不准确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>因此，需要添加一个麦克风，在不同长度的位置拨动钢尺，用麦克风采集音频并进行傅里叶变换，得到对应长度的频率。最终就可以拟合出一个高精度的频率-步进(step)曲线</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>既然为了调音增加了麦克风硬件，那为什么不物尽其用呢？
-esp32s3开发板刚好有usb接口，可以集成一个usb麦克风，连接电脑用来录音，获得更好的录音音质。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>10:19-10:32 https://www.bilibili.com/video/BV187411r7hp/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -451,27 +334,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>哎！不知道你有没有听过一种技术叫MIDI，它即可以传输音符，又可以存储乐谱。
-功能机时代的诺基亚铃声，你一定听过
-它就是midi
-midi可以使用多种接口进行传输，比如usb接口。而刚好我们的开发板上就有usb接口。使用usb midi就是最好的选择了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>开发板乱糟糟的连线
 人+影视飓风的扭转特效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最后，使用面包板，各种连线实在太乱了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>画一个电路板，把它们整合起来</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>为了更方便复刻，都是使用的成品模块</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -499,16 +363,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>（可以先用记号笔标注一下钢尺上音的位置）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>先试试最简单的小星星
 这是《小星星》？我自己都要听不出来了？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TODO：这里应该对比人手弹奏时的动作</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -554,10 +410,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TODO：需要实测一下瀑布图，看看频率变化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>我：那怎么办呢？
 刘华强：那，吸铁石
 我：对呀！谁说一定要用舵机呢。钢尺嘛，可以用电磁铁来吸住它
@@ -571,10 +423,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TODO:删除</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>引子</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -651,37 +499,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>演奏《小星星》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">夺舍（使用伤心欲茄声音AI合成）：斯你麻赛，nice什么呀！修改了多少个版本才有现在的效果的呀？你是nice了，我的刻度线都磨没了，八嘎压路！
-我：这不是考虑到观众老爷的观看体验，将中间的调试过程压缩了么
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我：结构上迭代设计了很多版，看，盒子里有好多
-我：代码也是改了很多次，这里有100多个commit</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -726,24 +544,17 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>口播出镜
-自动弹奏一个音+手机fft，浮现文字：误差xxx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>演奏一个音符的慢放视频（使用类似进度条的东西，显示每部分时间占用）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>我先设计了一个原型机验证可行性
-模仿演奏的动作，使用丝杆步进电机来精确控制钢尺移动、
-使用一个舵机压住钢尺、另一个舵机弹拨钢尺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>手绘设计图展示</t>
-    </r>
+    <t>还有一个问题，就是，乐谱的存储与传输
+原型机的谱子格式是自定义的：
+比如，("5", 1)：即表示Sol，时长为一拍，用串口发送一个音符演奏一个音符
+这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -753,7 +564,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>（舵机、丝杆步进电机）</t>
+      <t>插入电脑</t>
     </r>
     <r>
       <rPr>
@@ -764,25 +575,221 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-每个器件特写气泡（根据口播节奏依次出现）</t>
+设备管理器与音频设备展示</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>最后的最后，就以一首《卡农》二重奏作为结尾吧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>口播出镜
-麦克风--&gt;开发板-(usb线)-&gt;mic--电脑
-添加一个DRI Mic的在音频设备中的截图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>还有一个问题，就是，乐谱的存储与传输
-原型机的谱子格式是自定义的：
-比如，("5", 1)：即表示Sol，时长为一拍，用串口发送一个音符演奏一个音符
-这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>；</t>
+快速演奏（无法压住钢尺，节奏乱掉）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">口播出镜
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自动弹奏一个音+手机fft，浮现文字：误差xxx</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">解决了速度问题，下一个要解决的就是音不准的问题
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏差有x.x%，如果偏差超过3%（50音分）就是明显跑调了</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因此，使用程序控制钢尺在不同长度弹奏，并用麦克风采集音频进行傅里叶变换，得到对应长度的频率。最终就可以拟合出一个高精度的频率-电机步进(step)曲线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口播出镜
+麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>既然有了麦克风硬件和usb，那为什么不物尽其用呢？
+可以再集成一个usb麦克风，连接电脑用来录音，获得更好的录音音质。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哎！不知道你有没有听过一种技术叫MIDI，它即可以传输音符，又可以存储乐谱。
+举个例子，功能机时代的诺基亚铃声，它就是midi
+midi可以使用多种接口进行传输，比如usb接口。而esp32主控就支持usb接口。使用usb midi就是最好的选择了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何提高音准呢？先看一下原型机上的方法：
+调音时，在桌面拨动钢尺，用手机测出几个基准长度的音高，而后拟合出频率-长度函数。
+演奏的，时候通过目标频率换算出具体长度。
+但这样人工测量非常耗时，而且并不准确。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那么，开干！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最后，使用开发板+面包板飞线，实在太乱了。
+需要一个新设计把他们整合起来！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口播出镜
+做出握拳加油的手势</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO：做一下视频增稳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么样？这个赛博钢尺琴是不是还有点意思？
+不过单单一只钢尺演奏难免有些单调，所以我希望再增加几个乐器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先是钢尺，充当类似吉他的角色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其次是第一支笔，充当类似长笛的角色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pen beats演示动次打次三次（缩小并放在右下角，配架子鼓）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拨动钢尺演奏示意（缩小并放在左下角，配吉他）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吹笔奏演示意（缩小并放在上方，配长笛）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二开始遍跟读：动次打次
+这是第二支笔，充当类似架子鼓的角色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>让它们组一个文具乐队！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉他（钢尺），长笛（笔），架子鼓（笔）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先设计一个原型机，验证可行性。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加入一下飞入的音效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>先画一个个手绘示意图
+然后来建模，使用丝杆步进电机来控制钢尺移动、使用一个舵机压住钢尺、另一个舵机弹拨钢尺。最后加上底座就完成啦！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>早年在b站经常能看到大佬用钢尺演奏音乐，比如这个
+（视频播放）
+真是太酷了！我也跃跃欲试，想要自己演奏试试！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口播
+千本樱——佚名
+only my railgun——钢尺君
+大东北我的家乡——杯鸽
+（以相片的方式一次落下堆叠）
+口播</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口播
+手动演奏一个《小星星》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO:文本霓虹灯特效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手绘设计图展示
+建模展示：钢尺+丝杆步进电机+按压舵机+拨弦舵机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先设计PCB，为了更方便复刻，都是使用的成品模块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新建模，将主板与钢尺、电机等器件整合在一起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搞定了硬件，接下来就要注入灵魂，撸代码！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leonierX</t>
+  </si>
+  <si>
+    <t>nokia tune (MIDI)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">夺舍（使用伤心欲茄声音AI合成）：斯你麻赛，nice什么呀！修改了多少个版本才有现在的效果的呀？你是nice了，我的刻度线都磨没了，八嘎压路！
+我：这不是考虑到观众老爷的观看体验，将中间的调试过程压缩了么
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我：当然，制作过程还是有些波折的。看，盒子里都是结构建模迭代的版本。
+我：代码也是改了很多次，这里有100多个commit</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -790,7 +797,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="等线"/>
@@ -859,6 +866,13 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -998,7 +1012,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1092,15 +1106,24 @@
     <xf numFmtId="45" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="21" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="45" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1116,13 +1139,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="45" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1132,12 +1149,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2457,32 +2468,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="20" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="20" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2493,7 +2504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="8.25" style="6" customWidth="1"/>
@@ -2506,13 +2517,13 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -2528,41 +2539,44 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="49.5">
-      <c r="A2" s="28">
+      <c r="A2" s="29">
         <v>0</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="30">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="33">
-      <c r="A3" s="28">
+      <c r="A3" s="29">
         <f t="shared" ref="A3:A9" si="0">A2+B2</f>
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="30">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>57</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="99">
       <c r="A4" s="29">
         <f t="shared" si="0"/>
         <v>1.7361111111111109E-4</v>
@@ -2570,14 +2584,14 @@
       <c r="B4" s="30">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C4" s="33" t="s">
-        <v>110</v>
+      <c r="C4" s="36" t="s">
+        <v>75</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="33">
@@ -2588,15 +2602,12 @@
       <c r="B5" s="27">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C5" s="34"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>100</v>
+        <v>129</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2607,13 +2618,13 @@
       <c r="B6" s="30">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C6" s="34"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33">
@@ -2624,12 +2635,12 @@
       <c r="B7" s="27">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="37"/>
       <c r="D7" s="26" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="49.5">
@@ -2640,12 +2651,12 @@
       <c r="B8" s="27">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C8" s="35"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2657,818 +2668,799 @@
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="9" customFormat="1" ht="49.5">
-      <c r="A10" s="39">
-        <f t="shared" ref="A10:A22" si="1">A8+B8</f>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="9" customFormat="1">
+      <c r="A10" s="32">
+        <f>A7+B7</f>
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="B10" s="33">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="C10" s="35"/>
+      <c r="D10" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" s="9" customFormat="1" ht="49.5">
+      <c r="A11" s="32">
+        <f>A8+B8</f>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="B10" s="40">
+      <c r="B11" s="33">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="33">
-      <c r="A11" s="28">
-        <f t="shared" si="1"/>
+      <c r="C11" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" ht="33">
+      <c r="A12" s="28">
+        <f>A9+B9</f>
         <v>6.134259259259259E-4</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B12" s="27">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:7" ht="33">
-      <c r="A12" s="5">
-        <f t="shared" si="1"/>
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="B12" s="4">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>81</v>
+      <c r="C12" s="37"/>
+      <c r="D12" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" s="16" customFormat="1" ht="49.5">
+    <row r="13" spans="1:7" ht="33">
       <c r="A13" s="5">
-        <f t="shared" si="1"/>
-        <v>7.5231481481481482E-4</v>
+        <f t="shared" ref="A13:A20" si="1">A11+B11</f>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="B13" s="4">
-        <v>1.8518518518518518E-4</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="G13" s="14"/>
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C13" s="38"/>
+      <c r="D13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" s="16" customFormat="1" ht="49.5">
       <c r="A14" s="28">
         <f t="shared" si="1"/>
-        <v>7.6388888888888893E-4</v>
+        <v>7.5231481481481482E-4</v>
       </c>
       <c r="B14" s="27">
-        <v>2.3148148148148146E-4</v>
-      </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="14"/>
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>94</v>
+      </c>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:7" s="16" customFormat="1" ht="115.5">
+    <row r="15" spans="1:7" s="16" customFormat="1" ht="49.5">
       <c r="A15" s="28">
         <f t="shared" si="1"/>
-        <v>9.3749999999999997E-4</v>
+        <v>7.6388888888888893E-4</v>
       </c>
       <c r="B15" s="27">
-        <v>3.4722222222222224E-4</v>
-      </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="1:7" s="16" customFormat="1" ht="66">
+        <v>2.3148148148148146E-4</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="16" customFormat="1" ht="115.5">
       <c r="A16" s="28">
         <f t="shared" si="1"/>
-        <v>9.9537037037037042E-4</v>
+        <v>9.3749999999999997E-4</v>
       </c>
       <c r="B16" s="27">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C16" s="38"/>
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="C16" s="41"/>
       <c r="D16" s="13" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>37</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F16" s="13"/>
       <c r="G16" s="13"/>
     </row>
-    <row r="17" spans="1:7" s="16" customFormat="1" ht="33">
+    <row r="17" spans="1:7" s="16" customFormat="1" ht="66">
       <c r="A17" s="28">
         <f t="shared" si="1"/>
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="B17" s="27">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" spans="1:7" s="16" customFormat="1" ht="33">
+      <c r="A18" s="28">
+        <f t="shared" si="1"/>
         <v>1.2847222222222223E-3</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B18" s="27">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="32" t="s">
+      <c r="C18" s="41"/>
+      <c r="D18" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7" s="16" customFormat="1">
-      <c r="A18" s="5">
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" spans="1:7" s="16" customFormat="1">
+      <c r="A19" s="5">
         <f t="shared" si="1"/>
         <v>1.1111111111111111E-3</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B19" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" spans="1:7" ht="33">
-      <c r="A19" s="39">
+      <c r="C19" s="41"/>
+      <c r="D19" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="22"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" spans="1:7" ht="33">
+      <c r="A20" s="32">
         <f t="shared" si="1"/>
         <v>1.3773148148148149E-3</v>
       </c>
-      <c r="B19" s="40">
+      <c r="B20" s="33">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:7" s="47" customFormat="1" ht="66">
-      <c r="A20" s="42">
-        <f t="shared" si="1"/>
-        <v>1.1226851851851851E-3</v>
-      </c>
-      <c r="B20" s="43">
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="66">
-      <c r="A21" s="39">
-        <f t="shared" si="1"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="1:7" ht="82.5">
+      <c r="A21" s="28">
+        <f>A20+B20</f>
         <v>1.4930555555555556E-3</v>
       </c>
-      <c r="B21" s="40">
+      <c r="B21" s="27">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="32" t="s">
-        <v>44</v>
+      <c r="C21" s="41"/>
+      <c r="D21" s="34" t="s">
+        <v>32</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="49.5">
       <c r="A22" s="28">
-        <f t="shared" si="1"/>
-        <v>1.5277777777777776E-3</v>
+        <f>A21+B21</f>
+        <v>1.7824074074074075E-3</v>
       </c>
       <c r="B22" s="27">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C22" s="38"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="10" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="5"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="38"/>
+      <c r="A23" s="32">
+        <f t="shared" ref="A23:A24" si="2">A22+B22</f>
+        <v>2.0717592592592593E-3</v>
+      </c>
+      <c r="B23" s="33">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C23" s="41"/>
       <c r="D23" s="11" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" spans="1:7" s="17" customFormat="1" ht="49.5">
-      <c r="A24" s="5">
-        <f>A22+B22</f>
-        <v>1.8171296296296295E-3</v>
-      </c>
-      <c r="B24" s="4">
+    <row r="24" spans="1:7" ht="66">
+      <c r="A24" s="28">
+        <f t="shared" si="2"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="B24" s="27">
+        <v>2.3148148148148146E-4</v>
+      </c>
+      <c r="C24" s="41"/>
+      <c r="D24" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" ht="82.5">
+      <c r="A25" s="28">
+        <f t="shared" ref="A25:A46" si="3">A24+B24</f>
+        <v>2.3148148148148147E-3</v>
+      </c>
+      <c r="B25" s="27">
+        <v>4.6296296296296293E-4</v>
+      </c>
+      <c r="C25" s="41"/>
+      <c r="D25" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="5">
+        <f>A25+B25</f>
+        <v>2.7777777777777775E-3</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C26" s="41"/>
+      <c r="D26" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="12"/>
+    </row>
+    <row r="27" spans="1:7" s="17" customFormat="1" ht="33">
+      <c r="A27" s="28">
+        <f>A26+B26</f>
+        <v>2.7893518518518515E-3</v>
+      </c>
+      <c r="B27" s="27">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-    </row>
-    <row r="25" spans="1:7" s="17" customFormat="1">
-      <c r="A25" s="5">
-        <f t="shared" ref="A25:A47" si="2">A24+B24</f>
-        <v>1.9907407407407404E-3</v>
-      </c>
-      <c r="B25" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-    </row>
-    <row r="26" spans="1:7" ht="66">
-      <c r="A26" s="5">
-        <f t="shared" si="2"/>
-        <v>2.0023148148148144E-3</v>
-      </c>
-      <c r="B26" s="4">
-        <v>2.3148148148148146E-4</v>
-      </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:7" ht="99">
-      <c r="A27" s="5">
-        <f t="shared" si="2"/>
-        <v>2.2337962962962958E-3</v>
-      </c>
-      <c r="B27" s="4">
-        <v>4.6296296296296293E-4</v>
-      </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="C27" s="41"/>
+      <c r="D27" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="1:7" s="17" customFormat="1">
       <c r="A28" s="5">
-        <f t="shared" si="2"/>
-        <v>2.6967592592592586E-3</v>
+        <f>A27+B27</f>
+        <v>2.9629629629629624E-3</v>
       </c>
       <c r="B28" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C28" s="38"/>
+      <c r="C28" s="41"/>
       <c r="D28" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="E28" s="22"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A29" s="5">
-        <f t="shared" si="2"/>
-        <v>2.7083333333333326E-3</v>
-      </c>
-      <c r="B29" s="4">
+      <c r="A29" s="28">
+        <f>A28+B28</f>
+        <v>2.9745370370370364E-3</v>
+      </c>
+      <c r="B29" s="27">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C29" s="38"/>
-      <c r="D29" s="32" t="s">
-        <v>91</v>
+      <c r="C29" s="41"/>
+      <c r="D29" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A30" s="5">
-        <f t="shared" si="2"/>
-        <v>2.8240740740740735E-3</v>
+    <row r="30" spans="1:7">
+      <c r="A30" s="32">
+        <f>A29+B29</f>
+        <v>3.0902777777777773E-3</v>
       </c>
       <c r="B30" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="19" t="s">
-        <v>39</v>
+      <c r="C30" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="5">
-        <f t="shared" si="2"/>
-        <v>2.8819444444444439E-3</v>
-      </c>
-      <c r="B31" s="4">
+      <c r="A31" s="29">
+        <f t="shared" si="3"/>
+        <v>3.1481481481481477E-3</v>
+      </c>
+      <c r="B31" s="30">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="D31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="46" customFormat="1">
+      <c r="A32" s="43">
+        <f t="shared" si="3"/>
+        <v>3.2638888888888887E-3</v>
+      </c>
+      <c r="B32" s="44">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="29">
-        <f t="shared" si="2"/>
-        <v>2.9398148148148144E-3</v>
-      </c>
-      <c r="B32" s="30">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="5">
-        <f t="shared" si="2"/>
-        <v>3.0555555555555553E-3</v>
-      </c>
-      <c r="B33" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="C33" s="38"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="45"/>
+    </row>
+    <row r="33" spans="1:7" ht="33">
+      <c r="A33" s="29">
+        <f t="shared" si="3"/>
+        <v>3.3217592592592591E-3</v>
+      </c>
+      <c r="B33" s="30">
+        <v>5.7870370370370378E-4</v>
+      </c>
+      <c r="C33" s="41"/>
       <c r="D33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="33">
+        <v>64</v>
+      </c>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="29">
-        <f t="shared" si="2"/>
-        <v>3.1134259259259257E-3</v>
+        <f t="shared" si="3"/>
+        <v>3.9004629629629628E-3</v>
       </c>
       <c r="B34" s="30">
-        <v>5.7870370370370378E-4</v>
-      </c>
-      <c r="C34" s="38"/>
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="C34" s="41"/>
       <c r="D34" s="6" t="s">
-        <v>95</v>
+        <v>6</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="29">
-        <f t="shared" si="2"/>
-        <v>3.6921296296296294E-3</v>
+        <f t="shared" si="3"/>
+        <v>4.0393518518518513E-3</v>
       </c>
       <c r="B35" s="30">
-        <v>1.3888888888888889E-4</v>
-      </c>
-      <c r="C35" s="38"/>
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C35" s="41"/>
       <c r="D35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>6</v>
-      </c>
       <c r="F35" s="7"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="29">
-        <f t="shared" si="2"/>
-        <v>3.8310185185185183E-3</v>
+        <f t="shared" si="3"/>
+        <v>4.0972222222222217E-3</v>
       </c>
       <c r="B36" s="30">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C36" s="38"/>
+      <c r="C36" s="41"/>
       <c r="D36" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:7" ht="33">
+      <c r="A37" s="29">
+        <f t="shared" si="3"/>
+        <v>4.1550925925925922E-3</v>
+      </c>
+      <c r="B37" s="30">
+        <v>5.7870370370370378E-4</v>
+      </c>
+      <c r="C37" s="41"/>
+      <c r="D37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="29">
+        <f t="shared" si="3"/>
+        <v>4.7337962962962958E-3</v>
+      </c>
+      <c r="B38" s="30">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C38" s="41"/>
+      <c r="D38" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="29">
-        <f t="shared" si="2"/>
-        <v>3.8888888888888888E-3</v>
-      </c>
-      <c r="B37" s="30">
+      <c r="F38" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="28">
+        <f t="shared" si="3"/>
+        <v>4.7916666666666663E-3</v>
+      </c>
+      <c r="B39" s="27">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="C39" s="41"/>
+      <c r="D39" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="28">
+        <f t="shared" si="3"/>
+        <v>4.8263888888888887E-3</v>
+      </c>
+      <c r="B40" s="27">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="C40" s="40"/>
+      <c r="D40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="33">
+      <c r="A41" s="32">
+        <f t="shared" si="3"/>
+        <v>4.8726851851851848E-3</v>
+      </c>
+      <c r="B41" s="33">
+        <v>4.6296296296296293E-4</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="28">
+        <f t="shared" si="3"/>
+        <v>5.3356481481481475E-3</v>
+      </c>
+      <c r="B42" s="27">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="C42" s="41"/>
+      <c r="D42" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="99">
+      <c r="A43" s="28">
+        <f t="shared" si="3"/>
+        <v>5.3587962962962955E-3</v>
+      </c>
+      <c r="B43" s="27">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="C43" s="41"/>
+      <c r="D43" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" s="7"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="5">
+        <f t="shared" si="3"/>
+        <v>5.7638888888888878E-3</v>
+      </c>
+      <c r="B44" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C44" s="41"/>
+      <c r="D44" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="7"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="28">
+        <f t="shared" si="3"/>
+        <v>5.7754629629629623E-3</v>
+      </c>
+      <c r="B45" s="27">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C45" s="41"/>
+      <c r="D45" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7" ht="66">
+      <c r="A46" s="28">
+        <f t="shared" si="3"/>
+        <v>5.8912037037037032E-3</v>
+      </c>
+      <c r="B46" s="27">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="C46" s="40"/>
+      <c r="D46" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="33">
+      <c r="A47" s="5">
+        <f t="shared" ref="A47:A55" si="4">A46+B46</f>
+        <v>6.2962962962962955E-3</v>
+      </c>
+      <c r="B47" s="4">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="28">
+        <f t="shared" si="4"/>
+        <v>6.3310185185185179E-3</v>
+      </c>
+      <c r="B48" s="27">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="C48" s="41"/>
+      <c r="D48" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="28">
+        <f t="shared" si="4"/>
+        <v>6.377314814814814E-3</v>
+      </c>
+      <c r="B49" s="27">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="6" t="s">
+      <c r="C49" s="41"/>
+      <c r="D49" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="33">
+      <c r="A50" s="28">
+        <f t="shared" si="4"/>
+        <v>6.4351851851851844E-3</v>
+      </c>
+      <c r="B50" s="27">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C50" s="41"/>
+      <c r="D50" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="28">
+        <f t="shared" si="4"/>
+        <v>6.5046296296296284E-3</v>
+      </c>
+      <c r="B51" s="27">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C51" s="40"/>
+      <c r="D51" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:7" ht="33">
-      <c r="A38" s="29">
-        <f t="shared" si="2"/>
-        <v>3.9467592592592592E-3</v>
-      </c>
-      <c r="B38" s="30">
-        <v>5.7870370370370378E-4</v>
-      </c>
-      <c r="C38" s="38"/>
-      <c r="D38" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="5">
-        <f t="shared" si="2"/>
-        <v>4.5254629629629629E-3</v>
-      </c>
-      <c r="B39" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="C39" s="38"/>
-      <c r="D39" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="5">
-        <f t="shared" si="2"/>
-        <v>4.5833333333333334E-3</v>
-      </c>
-      <c r="B40" s="4">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="28">
-        <f t="shared" si="2"/>
-        <v>4.6180555555555558E-3</v>
-      </c>
-      <c r="B41" s="27">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="33">
-      <c r="A42" s="28">
-        <f t="shared" si="2"/>
-        <v>4.6643518518518518E-3</v>
-      </c>
-      <c r="B42" s="27">
-        <v>4.6296296296296293E-4</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="5">
-        <f t="shared" si="2"/>
-        <v>5.1273148148148146E-3</v>
-      </c>
-      <c r="B43" s="4">
-        <v>2.3148148148148147E-5</v>
-      </c>
-      <c r="C43" s="38"/>
-      <c r="D43" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="82.5">
-      <c r="A44" s="5">
-        <f t="shared" si="2"/>
-        <v>5.1504629629629626E-3</v>
-      </c>
-      <c r="B44" s="4">
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="C44" s="38"/>
-      <c r="D44" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="5">
-        <f t="shared" si="2"/>
-        <v>5.5555555555555549E-3</v>
-      </c>
-      <c r="B45" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="C45" s="38"/>
-      <c r="D45" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G45" s="7"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="5">
-        <f t="shared" si="2"/>
-        <v>5.5671296296296293E-3</v>
-      </c>
-      <c r="B46" s="4">
+    </row>
+    <row r="52" spans="1:7" ht="49.5">
+      <c r="A52" s="5">
+        <f t="shared" si="4"/>
+        <v>6.5740740740740725E-3</v>
+      </c>
+      <c r="B52" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C46" s="38"/>
-      <c r="D46" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G46" s="7"/>
-    </row>
-    <row r="47" spans="1:7" ht="66">
-      <c r="A47" s="5">
-        <f t="shared" si="2"/>
-        <v>5.6828703703703702E-3</v>
-      </c>
-      <c r="B47" s="4">
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="C47" s="37"/>
-      <c r="D47" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="5">
-        <f t="shared" ref="A48:A56" si="3">A47+B47</f>
-        <v>6.0879629629629626E-3</v>
-      </c>
-      <c r="B48" s="4">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="C48" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="5">
-        <f t="shared" si="3"/>
-        <v>6.122685185185185E-3</v>
-      </c>
-      <c r="B49" s="4">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="5">
-        <f t="shared" si="3"/>
-        <v>6.168981481481481E-3</v>
-      </c>
-      <c r="B50" s="4">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="C50" s="38"/>
-      <c r="D50" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="33">
-      <c r="A51" s="5">
-        <f t="shared" si="3"/>
-        <v>6.2268518518518515E-3</v>
-      </c>
-      <c r="B51" s="4">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="C51" s="38"/>
-      <c r="D51" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="5">
-        <f t="shared" si="3"/>
-        <v>6.2962962962962955E-3</v>
-      </c>
-      <c r="B52" s="4">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="C52" s="37"/>
-      <c r="D52" s="32" t="s">
-        <v>22</v>
+      <c r="C52" s="21"/>
+      <c r="D52" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="49.5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="5">
-        <f t="shared" si="3"/>
-        <v>6.3657407407407395E-3</v>
+        <f t="shared" si="4"/>
+        <v>6.6898148148148134E-3</v>
       </c>
       <c r="B53" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C53" s="21"/>
+      <c r="C53" s="39" t="s">
+        <v>16</v>
+      </c>
       <c r="D53" s="6" t="s">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="33">
+        <v>102</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="132">
       <c r="A54" s="5">
-        <f t="shared" si="3"/>
-        <v>6.4814814814814804E-3</v>
+        <f t="shared" si="4"/>
+        <v>6.8055555555555543E-3</v>
       </c>
       <c r="B54" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C54" s="36" t="s">
-        <v>25</v>
-      </c>
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="C54" s="40"/>
       <c r="D54" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="132">
+        <v>34</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="5">
-        <f t="shared" si="3"/>
-        <v>6.5972222222222213E-3</v>
-      </c>
-      <c r="B55" s="4">
-        <v>1.5046296296296294E-3</v>
-      </c>
-      <c r="C55" s="37"/>
-      <c r="D55" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="5">
-        <f t="shared" si="3"/>
-        <v>8.1018518518518514E-3</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>73</v>
+        <f t="shared" si="4"/>
+        <v>8.3101851851851843E-3</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C42:C47"/>
-    <mergeCell ref="C31:C41"/>
-    <mergeCell ref="C48:C52"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C13:C30"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C41:C46"/>
+    <mergeCell ref="C30:C40"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3477,7 +3469,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -3486,16 +3478,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3503,10 +3495,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3514,10 +3506,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3525,10 +3517,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>120</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3547,18 +3550,18 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -3572,7 +3575,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3586,7 +3589,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="B4">
         <v>6</v>

--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\develop\my_workspace\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4D9E5B-5BC9-4182-838F-078339DDD8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0238C7-0EA4-4C01-A9DD-ECF6E4FC5681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封标" sheetId="4" r:id="rId1"/>
@@ -30,12 +30,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -196,11 +191,6 @@
   <si>
     <t>大舵机图片
 不同的器件 + 雷达图（三个维度）动效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>另外，滑块直接套在丝杆上，阻力比较大，也会影响速度
-光驱中就有导轨的，新设计加上导轨减小阻力也是很必要的</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -548,13 +538,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>还有一个问题，就是，乐谱的存储与传输
-原型机的谱子格式是自定义的：
-比如，("5", 1)：即表示Sol，时长为一拍，用串口发送一个音符演奏一个音符
-这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -623,10 +606,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>因此，使用程序控制钢尺在不同长度弹奏，并用麦克风采集音频进行傅里叶变换，得到对应长度的频率。最终就可以拟合出一个高精度的频率-电机步进(step)曲线</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>口播出镜
 麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -637,25 +616,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>哎！不知道你有没有听过一种技术叫MIDI，它即可以传输音符，又可以存储乐谱。
-举个例子，功能机时代的诺基亚铃声，它就是midi
-midi可以使用多种接口进行传输，比如usb接口。而esp32主控就支持usb接口。使用usb midi就是最好的选择了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>如何提高音准呢？先看一下原型机上的方法：
-调音时，在桌面拨动钢尺，用手机测出几个基准长度的音高，而后拟合出频率-长度函数。
-演奏的，时候通过目标频率换算出具体长度。
-但这样人工测量非常耗时，而且并不准确。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>那么，开干！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最后，使用开发板+面包板飞线，实在太乱了。
-需要一个新设计把他们整合起来！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -716,12 +677,6 @@
   <si>
     <t>先画一个个手绘示意图
 然后来建模，使用丝杆步进电机来控制钢尺移动、使用一个舵机压住钢尺、另一个舵机弹拨钢尺。最后加上底座就完成啦！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>早年在b站经常能看到大佬用钢尺演奏音乐，比如这个
-（视频播放）
-真是太酷了！我也跃跃欲试，想要自己演奏试试！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -752,10 +707,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>重新建模，将主板与钢尺、电机等器件整合在一起</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>搞定了硬件，接下来就要注入灵魂，撸代码！！！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -764,6 +715,46 @@
   </si>
   <si>
     <t>nokia tune (MIDI)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>另外，滑块直接套在丝杆上，阻力比较大，也会影响速度
+参考光驱中的结构，滑块是导轨的。那么给滑块加上导轨减小阻力也是很必要的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何提高音准呢？先看一下原型机上的方法：
+调音时，在桌面拨动钢尺，测出几个基准长度的音高，而后拟合出频率-长度曲线。
+演奏时，候通过目标频率换算出具体的钢尺长度。
+但这样人工测量非常耗时，而且精度不高，导致音不准。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因此，使用程序控制钢尺在不同长度弹奏，并用麦克风采集音频进行傅里叶变换，得到对应长度的频率。最终就可以拟合出一个高精度的频率-电机步进(step)对应曲线，来提高音准。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>还有一个问题，就是，乐谱的记录与传输
+原型机的谱子格式是自定义的：
+比如，("5", 1)：即表示do、re、mi、fa、sol的Sol，时长为一拍，用串口发送一个音符演奏一个音符
+这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哎！不知道你有没有听过一种技术叫MIDI，它即可以传输音符，又可以存储乐谱。
+举个例子，功能机时代的诺基亚铃声，它就是midi，比如这个
+（播放视频）
+midi可以使用多种接口进行传输，比如usb接口。而esp32主控就支持usb接口。使用usb midi就是最好的选择了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最后，使用开发板+面包板飞线，实在太乱了
+嗯~（表情）
+需要一个新设计把他们整合起来！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然也需要重新建模，将新的电路板与钢尺、电机等器件整合在一起</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -787,9 +778,15 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>我：当然，制作过程还是有些波折的。看，盒子里都是结构建模迭代的版本。
-我：代码也是改了很多次，这里有100多个commit</t>
+      <t>我：当然，制作过程还是有些波折的。看，结构模型迭代了很多的版本。
+我：代码也是打磨了很多次，这里有100多个commit</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>早年在b站经常能看到大佬用钢尺演奏音乐，比如这些
+（视频播放）
+真是太酷了！我也跃跃欲试，想要自己演奏试试！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -797,7 +794,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="等线"/>
@@ -878,7 +875,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -918,6 +915,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1012,7 +1015,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1067,9 +1070,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1109,18 +1109,21 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="45" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="21" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="45" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1139,19 +1142,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="45" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1580,6 +1571,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1587,7 +1579,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2464,36 +2455,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FBFDF2-C68F-43FE-8FE4-06F462270704}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" s="19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2505,17 +2496,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="8.25" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="25" customWidth="1"/>
-    <col min="4" max="5" width="62.83203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="26.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.265625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.265625" style="24" customWidth="1"/>
+    <col min="4" max="5" width="62.796875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="26.265625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="9.08203125" style="3"/>
+    <col min="8" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -2538,84 +2529,84 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="49.5">
-      <c r="A2" s="29">
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="A2" s="28">
         <v>0</v>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="29">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="33">
-      <c r="A3" s="29">
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A3" s="28">
         <f t="shared" ref="A3:A9" si="0">A2+B2</f>
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="23" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="99">
-      <c r="A4" s="29">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.4">
+      <c r="A4" s="28">
         <f t="shared" si="0"/>
         <v>1.7361111111111109E-4</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="29">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="33">
-      <c r="A5" s="28">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A5" s="27">
         <f t="shared" si="0"/>
         <v>2.8935185185185184E-4</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C5" s="37"/>
       <c r="D5" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="29">
+        <v>122</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="28">
         <f t="shared" si="0"/>
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>1.1574074074074073E-5</v>
       </c>
       <c r="C6" s="37"/>
@@ -2627,28 +2618,28 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="33">
-      <c r="A7" s="28">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A7" s="27">
         <f t="shared" si="0"/>
         <v>4.1666666666666664E-4</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <v>9.2592592592592588E-5</v>
       </c>
       <c r="C7" s="37"/>
-      <c r="D7" s="26" t="s">
-        <v>58</v>
+      <c r="D7" s="25" t="s">
+        <v>57</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="49.5">
-      <c r="A8" s="28">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="A8" s="27">
         <f t="shared" si="0"/>
         <v>5.0925925925925921E-4</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>4.6296296296296294E-5</v>
       </c>
       <c r="C8" s="38"/>
@@ -2656,83 +2647,83 @@
         <v>25</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="28">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="27">
         <f t="shared" si="0"/>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="9" customFormat="1">
-      <c r="A10" s="32">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="5">
         <f>A7+B7</f>
         <v>5.0925925925925921E-4</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="34" t="s">
+      <c r="C10" s="31"/>
+      <c r="D10" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" s="9" customFormat="1" ht="49.5">
-      <c r="A11" s="32">
+    <row r="11" spans="1:7" s="9" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+      <c r="A11" s="5">
         <f>A8+B8</f>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="34" t="s">
-        <v>131</v>
+      <c r="D11" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" ht="33">
-      <c r="A12" s="28">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A12" s="27">
         <f>A9+B9</f>
         <v>6.134259259259259E-4</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>1.3888888888888889E-4</v>
       </c>
       <c r="C12" s="37"/>
-      <c r="D12" s="34" t="s">
-        <v>98</v>
+      <c r="D12" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="33">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <f t="shared" ref="A13:A20" si="1">A11+B11</f>
         <v>6.9444444444444447E-4</v>
@@ -2744,60 +2735,60 @@
       <c r="D13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>59</v>
+      <c r="E13" s="42" t="s">
+        <v>58</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" s="16" customFormat="1" ht="49.5">
-      <c r="A14" s="28">
+    <row r="14" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+      <c r="A14" s="27">
         <f t="shared" si="1"/>
         <v>7.5231481481481482E-4</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="26">
         <v>1.8518518518518518E-4</v>
       </c>
       <c r="C14" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>94</v>
+      <c r="D14" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>93</v>
       </c>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:7" s="16" customFormat="1" ht="49.5">
-      <c r="A15" s="28">
+    <row r="15" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+      <c r="A15" s="27">
         <f t="shared" si="1"/>
         <v>7.6388888888888893E-4</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>2.3148148148148146E-4</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F15" s="14"/>
-      <c r="G15" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="16" customFormat="1" ht="115.5">
-      <c r="A16" s="28">
+      <c r="G15" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="16" customFormat="1" ht="105.75" x14ac:dyDescent="0.4">
+      <c r="A16" s="27">
         <f t="shared" si="1"/>
         <v>9.3749999999999997E-4</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="26">
         <v>3.4722222222222224E-4</v>
       </c>
       <c r="C16" s="41"/>
@@ -2805,50 +2796,50 @@
         <v>37</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
     </row>
-    <row r="17" spans="1:7" s="16" customFormat="1" ht="66">
-      <c r="A17" s="28">
+    <row r="17" spans="1:7" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+      <c r="A17" s="27">
         <f t="shared" si="1"/>
         <v>9.9537037037037042E-4</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A18" s="28">
+    <row r="18" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+      <c r="A18" s="27">
         <f t="shared" si="1"/>
         <v>1.2847222222222223E-3</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="26">
         <v>9.2592592592592588E-5</v>
       </c>
       <c r="C18" s="41"/>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="6" t="s">
         <v>27</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
     </row>
-    <row r="19" spans="1:7" s="16" customFormat="1">
+    <row r="19" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <f t="shared" si="1"/>
         <v>1.1111111111111111E-3</v>
@@ -2857,53 +2848,53 @@
         <v>1.1574074074074073E-5</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="22"/>
+      <c r="D19" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="21"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="33">
-      <c r="A20" s="32">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A20" s="5">
         <f t="shared" si="1"/>
         <v>1.3773148148148149E-3</v>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C20" s="41"/>
-      <c r="D20" s="34" t="s">
-        <v>104</v>
+      <c r="D20" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" ht="82.5">
-      <c r="A21" s="28">
+    <row r="21" spans="1:7" ht="75" x14ac:dyDescent="0.4">
+      <c r="A21" s="27">
         <f>A20+B20</f>
         <v>1.4930555555555556E-3</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="26">
         <v>2.8935185185185189E-4</v>
       </c>
       <c r="C21" s="41"/>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="49.5">
-      <c r="A22" s="28">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="A22" s="27">
         <f>A21+B21</f>
         <v>1.7824074074074075E-3</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="26">
         <v>2.8935185185185189E-4</v>
       </c>
       <c r="C22" s="41"/>
@@ -2911,61 +2902,61 @@
         <v>33</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="32">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="5">
         <f t="shared" ref="A23:A24" si="2">A22+B22</f>
         <v>2.0717592592592593E-3</v>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
       <c r="C23" s="41"/>
       <c r="D23" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" spans="1:7" ht="66">
-      <c r="A24" s="28">
+    <row r="24" spans="1:7" ht="75" x14ac:dyDescent="0.4">
+      <c r="A24" s="27">
         <f t="shared" si="2"/>
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="26">
         <v>2.3148148148148146E-4</v>
       </c>
       <c r="C24" s="41"/>
-      <c r="D24" s="34" t="s">
-        <v>39</v>
+      <c r="D24" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" ht="82.5">
-      <c r="A25" s="28">
+    <row r="25" spans="1:7" ht="90" x14ac:dyDescent="0.4">
+      <c r="A25" s="27">
         <f t="shared" ref="A25:A46" si="3">A24+B24</f>
         <v>2.3148148148148147E-3</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="26">
         <v>4.6296296296296293E-4</v>
       </c>
       <c r="C25" s="41"/>
-      <c r="D25" s="34" t="s">
-        <v>62</v>
+      <c r="D25" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <f>A25+B25</f>
         <v>2.7777777777777775E-3</v>
@@ -2974,30 +2965,30 @@
         <v>1.1574074074074073E-5</v>
       </c>
       <c r="C26" s="41"/>
-      <c r="D26" s="19" t="s">
-        <v>50</v>
+      <c r="D26" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="E26" s="12"/>
     </row>
-    <row r="27" spans="1:7" s="17" customFormat="1" ht="33">
-      <c r="A27" s="28">
+    <row r="27" spans="1:7" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.4">
+      <c r="A27" s="27">
         <f>A26+B26</f>
         <v>2.7893518518518515E-3</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="26">
         <v>1.7361111111111112E-4</v>
       </c>
       <c r="C27" s="41"/>
-      <c r="D27" s="34" t="s">
-        <v>107</v>
+      <c r="D27" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
     </row>
-    <row r="28" spans="1:7" s="17" customFormat="1">
+    <row r="28" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <f>A27+B27</f>
         <v>2.9629629629629624E-3</v>
@@ -3006,33 +2997,33 @@
         <v>1.1574074074074073E-5</v>
       </c>
       <c r="C28" s="41"/>
-      <c r="D28" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="22"/>
+      <c r="D28" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="21"/>
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
     </row>
-    <row r="29" spans="1:7" s="16" customFormat="1" ht="33">
-      <c r="A29" s="28">
+    <row r="29" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+      <c r="A29" s="27">
         <f>A28+B28</f>
         <v>2.9745370370370364E-3</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C29" s="41"/>
-      <c r="D29" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>112</v>
+      <c r="D29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="32">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="5">
         <f>A29+B29</f>
         <v>3.0902777777777773E-3</v>
       </c>
@@ -3046,65 +3037,65 @@
         <v>36</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="29">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="28">
         <f t="shared" si="3"/>
         <v>3.1481481481481477E-3</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="29">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C31" s="41"/>
       <c r="D31" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="46" customFormat="1">
-      <c r="A32" s="43">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="35" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="32">
         <f t="shared" si="3"/>
         <v>3.2638888888888887E-3</v>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="33">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C32" s="41"/>
-      <c r="D32" s="45" t="s">
+      <c r="D32" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="F32" s="45" t="s">
+      <c r="E32" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="45"/>
-    </row>
-    <row r="33" spans="1:7" ht="33">
-      <c r="A33" s="29">
+      <c r="G32" s="34"/>
+    </row>
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A33" s="28">
         <f t="shared" si="3"/>
         <v>3.3217592592592591E-3</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>5.7870370370370378E-4</v>
       </c>
       <c r="C33" s="41"/>
       <c r="D33" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="29">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="28">
         <f t="shared" si="3"/>
         <v>3.9004629629629628E-3</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>1.3888888888888889E-4</v>
       </c>
       <c r="C34" s="41"/>
@@ -3112,16 +3103,16 @@
         <v>6</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="29">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="28">
         <f t="shared" si="3"/>
         <v>4.0393518518518513E-3</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C35" s="41"/>
@@ -3130,73 +3121,73 @@
       </c>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="29">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="28">
         <f t="shared" si="3"/>
         <v>4.0972222222222217E-3</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C36" s="41"/>
       <c r="D36" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:7" ht="33">
-      <c r="A37" s="29">
+    <row r="37" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A37" s="28">
         <f t="shared" si="3"/>
         <v>4.1550925925925922E-3</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <v>5.7870370370370378E-4</v>
       </c>
       <c r="C37" s="41"/>
       <c r="D37" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="29">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="28">
         <f t="shared" si="3"/>
         <v>4.7337962962962958E-3</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C38" s="41"/>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="28">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="27">
         <f t="shared" si="3"/>
         <v>4.7916666666666663E-3</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="26">
         <v>3.4722222222222222E-5</v>
       </c>
       <c r="C39" s="41"/>
-      <c r="D39" s="34" t="s">
-        <v>47</v>
+      <c r="D39" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="28">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="27">
         <f t="shared" si="3"/>
         <v>4.8263888888888887E-3</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="26">
         <v>4.6296296296296294E-5</v>
       </c>
       <c r="C40" s="40"/>
@@ -3204,64 +3195,64 @@
         <v>9</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="33">
-      <c r="A41" s="32">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30.75" x14ac:dyDescent="0.4">
+      <c r="A41" s="5">
         <f t="shared" si="3"/>
         <v>4.8726851851851848E-3</v>
       </c>
-      <c r="B41" s="33">
+      <c r="B41" s="4">
         <v>4.6296296296296293E-4</v>
       </c>
       <c r="C41" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="31" t="s">
-        <v>101</v>
+      <c r="D41" s="30" t="s">
+        <v>99</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="28">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="27">
         <f t="shared" si="3"/>
         <v>5.3356481481481475E-3</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="26">
         <v>2.3148148148148147E-5</v>
       </c>
       <c r="C42" s="41"/>
       <c r="D42" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="99">
-      <c r="A43" s="28">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="90" x14ac:dyDescent="0.4">
+      <c r="A43" s="27">
         <f t="shared" si="3"/>
         <v>5.3587962962962955E-3</v>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="26">
         <v>4.0509259259259258E-4</v>
       </c>
       <c r="C43" s="41"/>
       <c r="D43" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G43" s="7"/>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
         <f t="shared" si="3"/>
         <v>5.7638888888888878E-3</v>
@@ -3270,45 +3261,45 @@
         <v>1.1574074074074073E-5</v>
       </c>
       <c r="C44" s="41"/>
-      <c r="D44" s="19" t="s">
-        <v>50</v>
+      <c r="D44" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="G44" s="7"/>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="28">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="27">
         <f t="shared" si="3"/>
         <v>5.7754629629629623E-3</v>
       </c>
-      <c r="B45" s="27">
+      <c r="B45" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C45" s="41"/>
-      <c r="D45" s="42" t="s">
-        <v>67</v>
+      <c r="D45" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:7" ht="66">
-      <c r="A46" s="28">
+    <row r="46" spans="1:7" ht="60" x14ac:dyDescent="0.4">
+      <c r="A46" s="27">
         <f t="shared" si="3"/>
         <v>5.8912037037037032E-3</v>
       </c>
-      <c r="B46" s="27">
+      <c r="B46" s="26">
         <v>4.0509259259259258E-4</v>
       </c>
       <c r="C46" s="40"/>
-      <c r="D46" s="34" t="s">
-        <v>68</v>
+      <c r="D46" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="33">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <f t="shared" ref="A47:A55" si="4">A46+B46</f>
         <v>6.2962962962962955E-3</v>
@@ -3320,77 +3311,77 @@
         <v>17</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="28">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="27">
         <f t="shared" si="4"/>
         <v>6.3310185185185179E-3</v>
       </c>
-      <c r="B48" s="27">
+      <c r="B48" s="26">
         <v>4.6296296296296294E-5</v>
       </c>
       <c r="C48" s="41"/>
-      <c r="D48" s="34" t="s">
-        <v>119</v>
+      <c r="D48" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="28">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="27">
         <f t="shared" si="4"/>
         <v>6.377314814814814E-3</v>
       </c>
-      <c r="B49" s="27">
+      <c r="B49" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C49" s="41"/>
-      <c r="D49" s="34" t="s">
-        <v>120</v>
+      <c r="D49" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="33">
-      <c r="A50" s="28">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A50" s="27">
         <f t="shared" si="4"/>
         <v>6.4351851851851844E-3</v>
       </c>
-      <c r="B50" s="27">
+      <c r="B50" s="26">
         <v>6.9444444444444444E-5</v>
       </c>
       <c r="C50" s="41"/>
-      <c r="D50" s="34" t="s">
-        <v>118</v>
+      <c r="D50" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="28">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" s="27">
         <f t="shared" si="4"/>
         <v>6.5046296296296284E-3</v>
       </c>
-      <c r="B51" s="27">
+      <c r="B51" s="26">
         <v>6.9444444444444444E-5</v>
       </c>
       <c r="C51" s="40"/>
-      <c r="D51" s="34" t="s">
-        <v>123</v>
+      <c r="D51" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="49.5">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A52" s="5">
         <f t="shared" si="4"/>
         <v>6.5740740740740725E-3</v>
@@ -3398,15 +3389,15 @@
       <c r="B52" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C52" s="21"/>
+      <c r="C52" s="20"/>
       <c r="D52" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
         <f t="shared" si="4"/>
         <v>6.6898148148148134E-3</v>
@@ -3421,13 +3412,13 @@
         <v>36</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="132">
+    <row r="54" spans="1:7" ht="120" x14ac:dyDescent="0.4">
       <c r="A54" s="5">
         <f t="shared" si="4"/>
         <v>6.8055555555555543E-3</v>
@@ -3440,16 +3431,16 @@
         <v>34</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="5">
         <f t="shared" si="4"/>
         <v>8.3101851851851843E-3</v>
       </c>
-      <c r="C55" s="25" t="s">
-        <v>53</v>
+      <c r="C55" s="24" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3470,68 +3461,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3543,25 +3534,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D1F29C-200F-4BB5-9251-208FEB1786B7}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -3573,9 +3564,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3587,9 +3578,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4">
         <v>6</v>

--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\develop\my_workspace\self_playing_ruler\v1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0238C7-0EA4-4C01-A9DD-ECF6E4FC5681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCC7819-AAB5-4147-A376-B1F49EA1DB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="10050" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封标" sheetId="4" r:id="rId1"/>
     <sheet name="剧本" sheetId="1" r:id="rId2"/>
-    <sheet name="素材引用" sheetId="5" r:id="rId3"/>
-    <sheet name="雷达图制作" sheetId="6" r:id="rId4"/>
+    <sheet name="剧本素材legacy" sheetId="7" r:id="rId3"/>
+    <sheet name="素材引用" sheetId="5" r:id="rId4"/>
+    <sheet name="雷达图制作" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="147">
   <si>
     <t>​​画面描述 (分镜)​​</t>
   </si>
@@ -54,9 +59,6 @@
     <t>时长</t>
   </si>
   <si>
-    <t>响指</t>
-  </si>
-  <si>
     <t>模型爆炸图</t>
   </si>
   <si>
@@ -70,10 +72,6 @@
   </si>
   <si>
     <t xml:space="preserve">​​时间戳 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在屏幕前打一个响指，PCB出现在桌面</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -86,10 +84,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>这个xxx midi设备就是</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>气泡音</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -127,10 +121,6 @@
   </si>
   <si>
     <t>哔~</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哆啦A梦掏出：钢尺</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -159,74 +149,24 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>拨动钢尺，用手机测量频率
-频率-长度表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>麦克风--&gt;正弦信号-(fft)-&gt;频率图
 频率-步进表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>演奏《卡农》
-配上字幕滚动：
-软件开发：加加鸽
-硬件开发：加加鸽
-结构建模：加加鸽
-拍摄：加加鸽
-配音：加加鸽
-后期：加加鸽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现问题
-优化设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>大舵机图片
 不同的器件 + 雷达图（三个维度）动效</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>口播出镜
-展示一个串口谱子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>演奏前：来看看效果吧！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>王刚出菜BGM</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>首先就是演奏速度比较慢
-慢速演奏完：这样已经是极限了
-如果调快速度就变成这样了！！这限制了它演奏很多快节奏的曲目</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>nice哥</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>除了最基本的演奏，由于有mic，还可以对声音进行一些处理：
-比如对强弱的支持
-你还可以添加一些效果器，比如给这首曲子加上过载效果
-甚至于它还可以是一个麦克风</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜</t>
-  </si>
-  <si>
     <t>赛 博 钢 尺 琴——DIY自动演奏的钢尺</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -248,19 +188,6 @@
   </si>
   <si>
     <t>原理图--&gt;pcb--&gt;2D渲染图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>感谢嘉立创免费打样，让我白嫖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>结束</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不过上面的文具乐队还没有实现，如果这类视频观众老爷们喜欢，点个关注！！
-后续UP主会持续更新的！！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -301,31 +228,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>方案可行！！！
-不过这样的效果还差点意思，还有很多问题要解决！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用高速摄影机播放分析一下：
-抬起舵机--&gt;移动钢尺--&gt;舵机按下--&gt;舵机拨动
-这四个步骤中，舵机抬起与落下耗时最多，需要着重优化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>10:19-10:32 https://www.bilibili.com/video/BV187411r7hp/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>midi图示
-nokia tune播放视频
-5针、usb、RTS等物理接口
-麦克风--&gt;开发板-(usb线)-&gt;mic--&gt;电脑
-                                    -&gt;midi--&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>开发板乱糟糟的连线
-人+影视飓风的扭转特效</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -336,31 +239,6 @@
   <si>
     <t>组装过程特写（按照装机区的那种风格）
 以安装器件，拧螺丝为主</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果没有midi键盘，也可用手机的虚拟MIDI键盘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>手机midi键盘演示：do re mi fa。。。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不同力度弹奏midi键盘演示强弱
-原声--&gt;效果器（片头cyberpunk 2077 预告BGM演奏）
-口播出镜（拿着读最后一句台词）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>先试试最简单的小星星
-这是《小星星》？我自己都要听不出来了？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>怎么办呢？那就…上！科！技！
-“自动演奏的钢尺”
-让我们开始吧</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -400,108 +278,483 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>引子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢尺君</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯鸽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一根钢尺的艺术之旅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>up主</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>作品名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>佚名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>千本樱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大钢尺我的家乡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>only my railgun</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取出模型--&gt;拿到工作台--&gt;掰下来 / 一个响指出现在桌面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sg90舵机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>42步进电机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小无刷电机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应快</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体积小</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>扭力大</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>演奏《小星星》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过渡到:
+Cyberuler 2025，添加文本特效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>演奏一个音符的慢放视频（使用类似进度条的东西，显示每部分时间占用）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最后的最后，就以一首《卡农》二重奏作为结尾吧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口播出镜
+麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>既然有了麦克风硬件和usb，那为什么不物尽其用呢？
+可以再集成一个usb麦克风，连接电脑用来录音，获得更好的录音音质。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那么，开干！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO：做一下视频增稳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先是钢尺，充当类似吉他的角色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其次是第一支笔，充当类似长笛的角色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pen beats演示动次打次三次（缩小并放在右下角，配架子鼓）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拨动钢尺演奏示意（缩小并放在左下角，配吉他）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吹笔奏演示意（缩小并放在上方，配长笛）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二开始遍跟读：动次打次
+这是第二支笔，充当类似架子鼓的角色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>让它们组一个文具乐队！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉他（钢尺），长笛（笔），架子鼓（笔）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加入一下飞入的音效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO:文本霓虹灯特效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搞定了硬件，接下来就要注入灵魂，撸代码！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leonierX</t>
+  </si>
+  <si>
+    <t>nokia tune (MIDI)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最后，使用开发板+面包板飞线，实在太乱了
+嗯~（表情）
+需要一个新设计把他们整合起来！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+千本樱——佚名
+only my railgun——钢尺君
+大东北我的家乡——杯鸽
+（以相片的方式一次落下堆叠）
+【口播】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+手动演奏一个《小星星》
+【口播】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>先尝试一下最简单的旋律：do do sol sol la la sol, fa fa mi mi re re do
+对，就是《小星星》
+【视频播放】
+啊~~（捂脸），完全是不忍直视啊，这是小星星吗？要不是自己弹奏的，我都听不出来这是小星星！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我：看来我是没什么音乐天赋了，我一个程序员，让我弹钢尺，我能弹么？弹不了！
+范志毅：“没这个能力知道吧！”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+原型机演奏《小星星》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建模展示：钢尺+丝杆步进电机+按压舵机+拨弦舵机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先参考大佬们演奏的动作，一只手按压并控制钢尺长度，另一只手弹拨。我先手绘草图，设计了一个原型机，验证下方案的可行性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大佬演奏视频慢放
+手绘设计图展示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+然后根据草图来建模。使用丝杆步进电机来控制钢尺移动、使用一个舵机压住钢尺、另一个舵机弹拨钢尺，最后加上底座就完成啦！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+快速演奏（无法压住钢尺，节奏乱掉）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果还可以，方案可行！！！
+那么接下来就是优化打磨，做一个完整的“自动演奏的钢尺琴”。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>来看看效果吧！
+【视频播放】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>另外，滑块直接套在丝杆上阻力比较大，速度快了可能会丢步。
+参考光驱中的结构，滑块是固定在导轨上的。那么给滑块加上导轨减小阻力也是很必要的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用高速摄影机播放分析一下：
+抬起舵机--&gt;移动钢尺--&gt;舵机按下--&gt;舵机拨动
+这四个步骤中，按压钢尺的舵机抬起与落下耗时最多，保守估计至少也要163ms ，占了一大半的时间，因此需要着重优化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那首先想到的就是换一个更快速的舵机或者其他电机。
+但要同是满足速度快、下压力大、体积小这三个条件，还真是不好找。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>我：那怎么办呢？
-刘华强：那，吸铁石
-我：对呀！谁说一定要用舵机呢。钢尺嘛，可以用电磁铁来吸住它
-我：看！还挺牢固的</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
+【视频】刘华强：那，吸铁石
+我：对呀！谁说一定要用舵机呢。钢尺嘛，可以用电磁铁来吸住它，没有机械运动，速度可以做到很快。
+【视频】我：看！还挺牢固的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】（手指在脑袋边转动，表示想事情）
 《华强买瓜》——吸铁石
-电磁铁吸住钢尺特写（尝试拨动，如果不行就静态展示）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>引子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢尺君</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>杯鸽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一根钢尺的艺术之旅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>up主</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>作品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>佚名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>千本樱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>大钢尺我的家乡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>only my railgun</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>取出模型--&gt;拿到工作台--&gt;掰下来 / 一个响指出现在桌面</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sg90舵机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>42步进电机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>小无刷电机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>响应快</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>体积小</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>扭力大</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>演奏《小星星》</t>
+【口播】（睁大眼睛，伸出食指）
+电磁铁吸住钢尺特写</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画展示（钢尺--&gt;四个磁铁飞入画面）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画展示（钢尺+磁铁--&gt;滑块+导轨飞入画面）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化1：速度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化2：音准</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化3：乐谱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化4：录音</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画展示（麦克风飞入特写）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发板乱糟糟的连线
+人+影视飓风的扭转特效
+【口播】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因此，使用程序控制钢尺在不同长度弹奏，并用麦克风采集音频进行傅里叶变换，得到对应长度的频率。
+最终就可以拟合出一个高精度的频率-电机步进(step)对应曲线，来提高钢尺位置的精度，提高音准</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【视频】在桌面拨动钢尺，测出几个基准长度的音高，而后拟合出频率-长度曲线。
+【视频】演奏时，候通过目标频率换算出具体的钢尺长度。
+但这样人工测量精度太低，导致音不准。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拨动钢尺，用手机测量频率
+频率-长度表
+【口播】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解决了速度问题，第2个要优化解决的就是音不准的问题
+那么如何提高音准呢？
+先看一下原型机上是怎么校准的：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第3个优化点就是——乐谱的记录与传输
+原型机的谱子格式是自定义的：
+比如，("5", 1)：即表示do、re、mi、fa、sol的Sol，时长为一拍，用串口发送一个音符演奏一个音符
+这样，虽然设计上简单，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+展示一个串口谱子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+midi图示
+nokia tune播放视频
+5针、usb、RTS等物理接口
+麦克风--&gt;开发板-(usb线)-&gt;mic--&gt;电脑
+                                    -&gt;midi--&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>要怎么来优化呢？哎！不知道你有没有听过一种技术叫MIDI
+它即可以传输音符，又可以存储乐谱。
+举个例子，功能机时代的诺基亚铃声，它就是midi，比如这个
+【播放视频】
+midi可以使用多种接口进行传输，比如usb接口。而esp32主控就支持usb接口。使用usb midi就是最好的选择了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先设计主板PCB，为了更方便复刻，都是使用的成品模块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新建模，将新的电路板与钢尺、电机等器件整合在一起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>白屏过度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+废弃的3d打印件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>演奏《卡农》二重奏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>spoiler（片头cyberpunk 2077 预告BGM演奏）
+原声--&gt;效果器
+加上BGM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>还可以添加一些效果器，比如给这首曲子加上过载效果
+在加上BGM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+手机midi键盘演示：do re mi fa。。。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】（拿着读台词）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>甚至于它还可以是一个麦克风</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+不同力度弹奏midi键盘演示强弱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然，除了使用上位机直接播放MIDI文件，也可以使用midi键盘直接演奏，我们先用这个手机MIDI键盘来试一下</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>除了最基本的演奏，如果接上真正的midi键盘，还能够支持力度感应，你按得越重，声音就越响亮有力，就像这样：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么样？这个赛博钢尺琴是不是还有点意思？
+如果你对这个项目感兴趣，那就快来动手复刻一个吧，全部的软硬件资料已经上传到了我的github仓库。也可以加我的Q群来沟通交流。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+在口播画面叠加：Github主页+QQ群（左手分别指一下左上与右上）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然，制作过程也不是一帆风顺。
+迭代了很多的版本，打印了这么多废弃版本，才得到的最终版本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>别急！
+单单一只钢尺演奏难免有些单调，所以我希望再增加几个乐器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+做出握拳加油的手势</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不过上述的文具乐队还没有实现，如果这类视频观众朋友们喜欢，点个三连+关注！！
+后续UP主会持续更新的！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先要优化的就是演奏速度
+前面演奏小星星的速度太慢了
+如果直接加快速度呢？我们来试一下
+【视频播放】
+直接乱掉了。弹奏小星星都这样了，要是弹个野蜂飞舞不得冒烟了？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>为钢尺琴插上电源线与数据线
+设备管理器与音频设备展示</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个DRI MIDI与DIR MIC设备就是钢尺琴啦！
+让我们用它来演奏一曲！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么办呢？看来只能用程序员的方式——给它加个‘外挂’了
+让我来做一台能够“自动演奏的钢尺”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】（说外挂时，双手比yes并弯曲）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>夺舍钢尺</t>
+      <t>以前在B站，钢尺演奏可是实打实的‘流量密码’。看似简单的却能弹出世界名曲。来，大家感受一下。</t>
     </r>
     <r>
       <rPr>
@@ -512,281 +765,9 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-口播出镜
-废弃的3d打印件
-100多个commit屏幕滚动</t>
+【视频播放】
+喔~~真是太酷了！！！我自己也想要尝试演奏一下！</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>我：我一个程序员，让我弹钢尺，我能弹么？弹不了！
-范志毅：“没这个能力知道吧！”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>过渡到:
-Cyberuler 2025，添加文本特效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
-原型机演奏《小星星》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>演奏一个音符的慢放视频（使用类似进度条的东西，显示每部分时间占用）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>插入电脑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-设备管理器与音频设备展示</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最后的最后，就以一首《卡农》二重奏作为结尾吧</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
-快速演奏（无法压住钢尺，节奏乱掉）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">口播出镜
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0" tint="-0.14999847407452621"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>自动弹奏一个音+手机fft，浮现文字：误差xxx</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">解决了速度问题，下一个要解决的就是音不准的问题
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0" tint="-0.14999847407452621"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏差有x.x%，如果偏差超过3%（50音分）就是明显跑调了</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
-麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>既然有了麦克风硬件和usb，那为什么不物尽其用呢？
-可以再集成一个usb麦克风，连接电脑用来录音，获得更好的录音音质。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>那么，开干！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播出镜
-做出握拳加油的手势</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TODO：做一下视频增稳</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>怎么样？这个赛博钢尺琴是不是还有点意思？
-不过单单一只钢尺演奏难免有些单调，所以我希望再增加几个乐器</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>首先是钢尺，充当类似吉他的角色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>其次是第一支笔，充当类似长笛的角色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pen beats演示动次打次三次（缩小并放在右下角，配架子鼓）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>拨动钢尺演奏示意（缩小并放在左下角，配吉他）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>吹笔奏演示意（缩小并放在上方，配长笛）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>第二开始遍跟读：动次打次
-这是第二支笔，充当类似架子鼓的角色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>让它们组一个文具乐队！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>吉他（钢尺），长笛（笔），架子鼓（笔）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>首先设计一个原型机，验证可行性。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>加入一下飞入的音效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>先画一个个手绘示意图
-然后来建模，使用丝杆步进电机来控制钢尺移动、使用一个舵机压住钢尺、另一个舵机弹拨钢尺。最后加上底座就完成啦！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播
-千本樱——佚名
-only my railgun——钢尺君
-大东北我的家乡——杯鸽
-（以相片的方式一次落下堆叠）
-口播</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>口播
-手动演奏一个《小星星》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TODO:文本霓虹灯特效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>手绘设计图展示
-建模展示：钢尺+丝杆步进电机+按压舵机+拨弦舵机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>首先设计PCB，为了更方便复刻，都是使用的成品模块</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>搞定了硬件，接下来就要注入灵魂，撸代码！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>leonierX</t>
-  </si>
-  <si>
-    <t>nokia tune (MIDI)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>另外，滑块直接套在丝杆上，阻力比较大，也会影响速度
-参考光驱中的结构，滑块是导轨的。那么给滑块加上导轨减小阻力也是很必要的</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>如何提高音准呢？先看一下原型机上的方法：
-调音时，在桌面拨动钢尺，测出几个基准长度的音高，而后拟合出频率-长度曲线。
-演奏时，候通过目标频率换算出具体的钢尺长度。
-但这样人工测量非常耗时，而且精度不高，导致音不准。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>因此，使用程序控制钢尺在不同长度弹奏，并用麦克风采集音频进行傅里叶变换，得到对应长度的频率。最终就可以拟合出一个高精度的频率-电机步进(step)对应曲线，来提高音准。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>还有一个问题，就是，乐谱的记录与传输
-原型机的谱子格式是自定义的：
-比如，("5", 1)：即表示do、re、mi、fa、sol的Sol，时长为一拍，用串口发送一个音符演奏一个音符
-这样，虽然调试方便，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哎！不知道你有没有听过一种技术叫MIDI，它即可以传输音符，又可以存储乐谱。
-举个例子，功能机时代的诺基亚铃声，它就是midi，比如这个
-（播放视频）
-midi可以使用多种接口进行传输，比如usb接口。而esp32主控就支持usb接口。使用usb midi就是最好的选择了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最后，使用开发板+面包板飞线，实在太乱了
-嗯~（表情）
-需要一个新设计把他们整合起来！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>当然也需要重新建模，将新的电路板与钢尺、电机等器件整合在一起</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">夺舍（使用伤心欲茄声音AI合成）：斯你麻赛，nice什么呀！修改了多少个版本才有现在的效果的呀？你是nice了，我的刻度线都磨没了，八嘎压路！
-我：这不是考虑到观众老爷的观看体验，将中间的调试过程压缩了么
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我：当然，制作过程还是有些波折的。看，结构模型迭代了很多的版本。
-我：代码也是打磨了很多次，这里有100多个commit</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>早年在b站经常能看到大佬用钢尺演奏音乐，比如这些
-（视频播放）
-真是太酷了！我也跃跃欲试，想要自己演奏试试！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -794,7 +775,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="等线"/>
@@ -860,22 +841,8 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.14999847407452621"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -909,18 +876,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1015,7 +970,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1109,41 +1064,44 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="45" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1571,7 +1529,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1579,6 +1536,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2455,36 +2413,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FBFDF2-C68F-43FE-8FE4-06F462270704}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1">
       <c r="A1" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" s="19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2495,26 +2453,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="8.265625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.265625" style="24" customWidth="1"/>
-    <col min="4" max="5" width="62.796875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="26.265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.25" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="24" customWidth="1"/>
+    <col min="4" max="5" width="62.83203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="26.25" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="3"/>
+    <col min="8" max="16384" width="9.08203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -2529,7 +2487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="49.5">
       <c r="A2" s="28">
         <v>0</v>
       </c>
@@ -2537,16 +2495,16 @@
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="33">
       <c r="A3" s="28">
         <f t="shared" ref="A3:A9" si="0">A2+B2</f>
         <v>1.1574074074074073E-4</v>
@@ -2555,19 +2513,19 @@
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="99">
       <c r="A4" s="28">
         <f t="shared" si="0"/>
         <v>1.7361111111111109E-4</v>
@@ -2575,17 +2533,17 @@
       <c r="B4" s="29">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>74</v>
+      <c r="C4" s="40" t="s">
+        <v>47</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="82.5">
       <c r="A5" s="27">
         <f t="shared" si="0"/>
         <v>2.8935185185185184E-4</v>
@@ -2593,15 +2551,15 @@
       <c r="B5" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C5" s="37"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="6" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="28">
         <f t="shared" si="0"/>
         <v>4.0509259259259258E-4</v>
@@ -2609,16 +2567,16 @@
       <c r="B6" s="29">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C6" s="37"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="49.5">
       <c r="A7" s="27">
         <f t="shared" si="0"/>
         <v>4.1666666666666664E-4</v>
@@ -2626,15 +2584,15 @@
       <c r="B7" s="26">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C7" s="37"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="25" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="33">
       <c r="A8" s="27">
         <f t="shared" si="0"/>
         <v>5.0925925925925921E-4</v>
@@ -2642,15 +2600,15 @@
       <c r="B8" s="26">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C8" s="38"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="6" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="27">
         <f t="shared" si="0"/>
         <v>5.5555555555555556E-4</v>
@@ -2659,13 +2617,13 @@
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="9" customFormat="1" ht="33">
       <c r="A10" s="5">
         <f>A7+B7</f>
         <v>5.0925925925925921E-4</v>
@@ -2673,17 +2631,19 @@
       <c r="B10" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>118</v>
+      <c r="C10" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>95</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" s="9" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" s="9" customFormat="1" ht="49.5">
       <c r="A11" s="5">
         <f>A8+B8</f>
         <v>5.5555555555555556E-4</v>
@@ -2691,21 +2651,19 @@
       <c r="B11" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>20</v>
-      </c>
+      <c r="C11" s="41"/>
       <c r="D11" s="6" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="33">
       <c r="A12" s="27">
         <f>A9+B9</f>
         <v>6.134259259259259E-4</v>
@@ -2713,35 +2671,35 @@
       <c r="B12" s="26">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C12" s="37"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="33">
       <c r="A13" s="5">
-        <f t="shared" ref="A13:A20" si="1">A11+B11</f>
+        <f t="shared" ref="A13:A17" si="1">A11+B11</f>
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="B13" s="4">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C13" s="38"/>
+      <c r="C13" s="42"/>
       <c r="D13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>58</v>
+        <v>92</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>99</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" s="16" customFormat="1" ht="82.5">
       <c r="A14" s="27">
         <f t="shared" si="1"/>
         <v>7.5231481481481482E-4</v>
@@ -2749,21 +2707,21 @@
       <c r="B14" s="26">
         <v>1.8518518518518518E-4</v>
       </c>
-      <c r="C14" s="39" t="s">
-        <v>35</v>
+      <c r="C14" s="43" t="s">
+        <v>108</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" s="16" customFormat="1" ht="66">
       <c r="A15" s="27">
         <f t="shared" si="1"/>
         <v>7.6388888888888893E-4</v>
@@ -2771,19 +2729,19 @@
       <c r="B15" s="26">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="C15" s="41"/>
+      <c r="C15" s="43"/>
       <c r="D15" s="14" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="16" customFormat="1" ht="105.75" x14ac:dyDescent="0.4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="16" customFormat="1" ht="33">
       <c r="A16" s="27">
         <f t="shared" si="1"/>
         <v>9.3749999999999997E-4</v>
@@ -2791,17 +2749,17 @@
       <c r="B16" s="26">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C16" s="41"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="13" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
     </row>
-    <row r="17" spans="1:7" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" s="16" customFormat="1" ht="82.5">
       <c r="A17" s="27">
         <f t="shared" si="1"/>
         <v>9.9537037037037042E-4</v>
@@ -2809,649 +2767,718 @@
       <c r="B17" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C17" s="41"/>
+      <c r="C17" s="43"/>
       <c r="D17" s="13" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
-      <c r="A18" s="27">
-        <f t="shared" si="1"/>
-        <v>1.2847222222222223E-3</v>
-      </c>
-      <c r="B18" s="26">
-        <v>9.2592592592592588E-5</v>
-      </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>129</v>
-      </c>
+    <row r="18" spans="1:7" s="16" customFormat="1">
+      <c r="A18" s="27"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
     </row>
-    <row r="19" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="5">
-        <f t="shared" si="1"/>
-        <v>1.1111111111111111E-3</v>
-      </c>
-      <c r="B19" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="21"/>
+    <row r="19" spans="1:7" s="16" customFormat="1" ht="49.5">
+      <c r="A19" s="27">
+        <f>A16+B16</f>
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="B19" s="26">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>101</v>
+      </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A20" s="5">
-        <f t="shared" si="1"/>
+    <row r="20" spans="1:7" s="16" customFormat="1">
+      <c r="A20" s="27"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="21"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" spans="1:7" s="16" customFormat="1">
+      <c r="A21" s="5">
+        <f>A17+B17</f>
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="B21" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="22" spans="1:7" ht="49.5">
+      <c r="A22" s="5">
+        <f>A19+B19</f>
         <v>1.3773148148148149E-3</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B22" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:7" ht="75" x14ac:dyDescent="0.4">
-      <c r="A21" s="27">
-        <f>A20+B20</f>
+      <c r="C22" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="1:7" ht="66">
+      <c r="A23" s="27">
+        <f>A22+B22</f>
         <v>1.4930555555555556E-3</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B23" s="26">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.4">
-      <c r="A22" s="27">
-        <f>A21+B21</f>
+      <c r="C23" s="43"/>
+      <c r="D23" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="82.5">
+      <c r="A24" s="27">
+        <f>A23+B23</f>
         <v>1.7824074074074075E-3</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B24" s="26">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" s="5">
-        <f t="shared" ref="A23:A24" si="2">A22+B22</f>
+      <c r="C24" s="43"/>
+      <c r="D24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="27"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="5">
+        <f>A24+B24</f>
         <v>2.0717592592592593E-3</v>
-      </c>
-      <c r="B23" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="1:7" ht="75" x14ac:dyDescent="0.4">
-      <c r="A24" s="27">
-        <f t="shared" si="2"/>
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="B24" s="26">
-        <v>2.3148148148148146E-4</v>
-      </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="1:7" ht="90" x14ac:dyDescent="0.4">
-      <c r="A25" s="27">
-        <f t="shared" ref="A25:A46" si="3">A24+B24</f>
-        <v>2.3148148148148147E-3</v>
-      </c>
-      <c r="B25" s="26">
-        <v>4.6296296296296293E-4</v>
-      </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A26" s="5">
-        <f>A25+B25</f>
-        <v>2.7777777777777775E-3</v>
       </c>
       <c r="B26" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="12"/>
-    </row>
-    <row r="27" spans="1:7" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.4">
+      <c r="C26" s="43"/>
+      <c r="D26" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" ht="82.5">
       <c r="A27" s="27">
-        <f>A26+B26</f>
+        <f t="shared" ref="A27" si="2">A26+B26</f>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="B27" s="26">
+        <v>2.3148148148148146E-4</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+    </row>
+    <row r="28" spans="1:7" ht="99">
+      <c r="A28" s="27">
+        <f t="shared" ref="A28:A52" si="3">A27+B27</f>
+        <v>2.3148148148148147E-3</v>
+      </c>
+      <c r="B28" s="26">
+        <v>4.6296296296296293E-4</v>
+      </c>
+      <c r="C28" s="43"/>
+      <c r="D28" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="5">
+        <f>A28+B28</f>
+        <v>2.7777777777777775E-3</v>
+      </c>
+      <c r="B29" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C29" s="43"/>
+      <c r="D29" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="12"/>
+    </row>
+    <row r="30" spans="1:7" s="17" customFormat="1" ht="33">
+      <c r="A30" s="27">
+        <f>A29+B29</f>
         <v>2.7893518518518515E-3</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B30" s="26">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="5">
-        <f>A27+B27</f>
+      <c r="C30" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="1:7" s="17" customFormat="1">
+      <c r="A31" s="5">
+        <f>A30+B30</f>
         <v>2.9629629629629624E-3</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B31" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-    </row>
-    <row r="29" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
-      <c r="A29" s="27">
-        <f>A28+B28</f>
+      <c r="C31" s="43"/>
+      <c r="D31" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:7" s="16" customFormat="1" ht="49.5">
+      <c r="A32" s="27">
+        <f>A31+B31</f>
         <v>2.9745370370370364E-3</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B32" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A30" s="5">
-        <f>A29+B29</f>
+      <c r="C32" s="34"/>
+      <c r="D32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="5">
+        <f>A32+B32</f>
         <v>3.0902777777777773E-3</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B33" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C30" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A31" s="28">
+      <c r="C33" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="28">
         <f t="shared" si="3"/>
         <v>3.1481481481481477E-3</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B34" s="29">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="35" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="32">
+      <c r="C34" s="38"/>
+      <c r="D34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="33">
+      <c r="A35" s="28">
         <f t="shared" si="3"/>
         <v>3.2638888888888887E-3</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B35" s="29">
+        <v>5.7870370370370378E-4</v>
+      </c>
+      <c r="C35" s="38"/>
+      <c r="D35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="28">
+        <f t="shared" si="3"/>
+        <v>3.8425925925925923E-3</v>
+      </c>
+      <c r="B36" s="29">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="C36" s="38"/>
+      <c r="D36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="28">
+        <f t="shared" si="3"/>
+        <v>3.9814814814814808E-3</v>
+      </c>
+      <c r="B37" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="34"/>
-    </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A33" s="28">
-        <f t="shared" si="3"/>
-        <v>3.3217592592592591E-3</v>
-      </c>
-      <c r="B33" s="29">
-        <v>5.7870370370370378E-4</v>
-      </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="28">
-        <f t="shared" si="3"/>
-        <v>3.9004629629629628E-3</v>
-      </c>
-      <c r="B34" s="29">
-        <v>1.3888888888888889E-4</v>
-      </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="6" t="s">
+      <c r="C37" s="38"/>
+      <c r="D37" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="28">
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="28">
         <f t="shared" si="3"/>
         <v>4.0393518518518513E-3</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B38" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" s="28">
+      <c r="C38" s="38"/>
+      <c r="D38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:7" ht="33">
+      <c r="A39" s="28">
         <f t="shared" si="3"/>
         <v>4.0972222222222217E-3</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B39" s="29">
+        <v>5.7870370370370378E-4</v>
+      </c>
+      <c r="C39" s="38"/>
+      <c r="D39" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="28">
+        <f t="shared" si="3"/>
+        <v>4.6759259259259254E-3</v>
+      </c>
+      <c r="B40" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A37" s="28">
-        <f t="shared" si="3"/>
-        <v>4.1550925925925922E-3</v>
-      </c>
-      <c r="B37" s="29">
-        <v>5.7870370370370378E-4</v>
-      </c>
-      <c r="C37" s="41"/>
-      <c r="D37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A38" s="28">
+      <c r="C40" s="38"/>
+      <c r="D40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="27">
         <f t="shared" si="3"/>
         <v>4.7337962962962958E-3</v>
       </c>
-      <c r="B38" s="29">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A39" s="27">
-        <f t="shared" si="3"/>
-        <v>4.7916666666666663E-3</v>
-      </c>
-      <c r="B39" s="26">
+      <c r="B41" s="26">
         <v>3.4722222222222222E-5</v>
       </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="27">
-        <f t="shared" si="3"/>
-        <v>4.8263888888888887E-3</v>
-      </c>
-      <c r="B40" s="26">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="30.75" x14ac:dyDescent="0.4">
-      <c r="A41" s="5">
-        <f t="shared" si="3"/>
-        <v>4.8726851851851848E-3</v>
-      </c>
-      <c r="B41" s="4">
-        <v>4.6296296296296293E-4</v>
-      </c>
-      <c r="C41" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>99</v>
+      <c r="C41" s="38"/>
+      <c r="D41" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="27">
         <f t="shared" si="3"/>
-        <v>5.3356481481481475E-3</v>
+        <v>4.7685185185185183E-3</v>
       </c>
       <c r="B42" s="26">
-        <v>2.3148148148148147E-5</v>
-      </c>
-      <c r="C42" s="41"/>
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="C42" s="39"/>
       <c r="D42" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="90" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="27">
         <f t="shared" si="3"/>
-        <v>5.3587962962962955E-3</v>
-      </c>
-      <c r="B43" s="26">
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G43" s="7"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A44" s="5">
+        <v>4.8148148148148143E-3</v>
+      </c>
+      <c r="B43" s="26"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" s="30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="33">
+      <c r="A44" s="27">
         <f t="shared" si="3"/>
-        <v>5.7638888888888878E-3</v>
+        <v>4.8148148148148143E-3</v>
       </c>
       <c r="B44" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+        <v>4.6296296296296293E-4</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="49.5">
       <c r="A45" s="27">
         <f t="shared" si="3"/>
-        <v>5.7754629629629623E-3</v>
+        <v>5.2777777777777771E-3</v>
       </c>
       <c r="B45" s="26">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C45" s="41"/>
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="C45" s="38"/>
       <c r="D45" s="8" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:7" ht="60" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" ht="33">
       <c r="A46" s="27">
         <f t="shared" si="3"/>
-        <v>5.8912037037037032E-3</v>
+        <v>5.6249999999999989E-3</v>
       </c>
       <c r="B46" s="26">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C46" s="38"/>
+      <c r="D46" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G46" s="7"/>
+    </row>
+    <row r="47" spans="1:7" ht="33">
+      <c r="A47" s="27">
+        <f t="shared" si="3"/>
+        <v>5.7407407407407398E-3</v>
+      </c>
+      <c r="B47" s="26">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C46" s="40"/>
-      <c r="D46" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A47" s="5">
-        <f t="shared" ref="A47:A55" si="4">A46+B46</f>
-        <v>6.2962962962962955E-3</v>
-      </c>
-      <c r="B47" s="4">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="C47" s="39" t="s">
-        <v>17</v>
-      </c>
+      <c r="C47" s="38"/>
       <c r="D47" s="6" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="27">
-        <f t="shared" si="4"/>
-        <v>6.3310185185185179E-3</v>
-      </c>
-      <c r="B48" s="26">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="C48" s="41"/>
+        <f t="shared" si="3"/>
+        <v>6.1458333333333321E-3</v>
+      </c>
+      <c r="B48" s="26"/>
+      <c r="C48" s="38"/>
       <c r="D48" s="6" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="27">
-        <f t="shared" si="4"/>
-        <v>6.377314814814814E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.1458333333333321E-3</v>
       </c>
       <c r="B49" s="26">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="C49" s="41"/>
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="C49" s="38"/>
       <c r="D49" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="33">
       <c r="A50" s="27">
-        <f t="shared" si="4"/>
-        <v>6.4351851851851844E-3</v>
+        <f t="shared" si="3"/>
+        <v>6.1689814814814802E-3</v>
       </c>
       <c r="B50" s="26">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="C50" s="41"/>
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="C50" s="39"/>
       <c r="D50" s="6" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A51" s="27">
-        <f t="shared" si="4"/>
-        <v>6.5046296296296284E-3</v>
-      </c>
-      <c r="B51" s="26">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="C51" s="40"/>
+        <v>137</v>
+      </c>
+      <c r="G50" s="7"/>
+    </row>
+    <row r="51" spans="1:7" ht="49.5">
+      <c r="A51" s="36">
+        <f t="shared" si="3"/>
+        <v>6.5740740740740725E-3</v>
+      </c>
+      <c r="B51" s="4">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="C51" s="37" t="s">
+        <v>14</v>
+      </c>
       <c r="D51" s="6" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.4">
-      <c r="A52" s="5">
-        <f t="shared" si="4"/>
-        <v>6.5740740740740725E-3</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="33">
+      <c r="A52" s="36">
+        <f t="shared" si="3"/>
+        <v>6.9212962962962943E-3</v>
       </c>
       <c r="B52" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C52" s="20"/>
+      <c r="C52" s="38"/>
       <c r="D52" s="6" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A53" s="5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="27">
+        <f t="shared" ref="A53:A60" si="4">A52+B52</f>
+        <v>7.0370370370370352E-3</v>
+      </c>
+      <c r="B53" s="26">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="C53" s="38"/>
+      <c r="D53" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="27">
         <f t="shared" si="4"/>
-        <v>6.6898148148148134E-3</v>
-      </c>
-      <c r="B53" s="4">
+        <v>7.0833333333333312E-3</v>
+      </c>
+      <c r="B54" s="26">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C54" s="38"/>
+      <c r="D54" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="33">
+      <c r="A55" s="27">
+        <f t="shared" si="4"/>
+        <v>7.1412037037037017E-3</v>
+      </c>
+      <c r="B55" s="26">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C55" s="38"/>
+      <c r="D55" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="27">
+        <f t="shared" si="4"/>
+        <v>7.2106481481481457E-3</v>
+      </c>
+      <c r="B56" s="26">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C56" s="39"/>
+      <c r="D56" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="49.5">
+      <c r="A57" s="5">
+        <f t="shared" si="4"/>
+        <v>7.2800925925925897E-3</v>
+      </c>
+      <c r="B57" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C53" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="120" x14ac:dyDescent="0.4">
-      <c r="A54" s="5">
+      <c r="C57" s="20"/>
+      <c r="D57" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="5">
         <f t="shared" si="4"/>
-        <v>6.8055555555555543E-3</v>
-      </c>
-      <c r="B54" s="4">
+        <v>7.3958333333333307E-3</v>
+      </c>
+      <c r="B58" s="4">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C58" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="5">
+        <f t="shared" si="4"/>
+        <v>7.5115740740740716E-3</v>
+      </c>
+      <c r="B59" s="4">
         <v>1.5046296296296294E-3</v>
       </c>
-      <c r="C54" s="40"/>
-      <c r="D54" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A55" s="5">
+      <c r="C59" s="38"/>
+      <c r="D59" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="5">
         <f t="shared" si="4"/>
-        <v>8.3101851851851843E-3</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>52</v>
+        <v>9.0162037037037016E-3</v>
+      </c>
+      <c r="B60" s="35">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="C60" s="39"/>
+      <c r="D60" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="C51:C56"/>
     <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C41:C46"/>
-    <mergeCell ref="C30:C40"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C29"/>
+    <mergeCell ref="C33:C42"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C14:C21"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C44:C50"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3459,71 +3486,33 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07104DAA-2E56-4B7D-A05C-4806FDF0CFBA}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+    <col min="5" max="5" width="73.6640625" customWidth="1"/>
+    <col min="6" max="11" width="67.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="1" spans="1:7" s="16" customFormat="1" ht="99">
+      <c r="A1" s="27" t="e">
+        <f t="shared" ref="A1" si="0">#REF!+#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B1" s="26">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="C1"/>
+      <c r="D1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3532,27 +3521,100 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D1F29C-200F-4BB5-9251-208FEB1786B7}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -3564,9 +3626,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3578,9 +3640,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>6</v>

--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\develop\my_workspace\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCC7819-AAB5-4147-A376-B1F49EA1DB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AE93FD-5153-48EC-80D1-1458CBD2E7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="10050" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封标" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="雷达图制作" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,15 +33,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="148">
   <si>
     <t>​​画面描述 (分镜)​​</t>
   </si>
@@ -201,30 +197,6 @@
   </si>
   <si>
     <t>《spoiler》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>​</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>弹钢尺的画面不变
-范大将军片段（画中画）</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -371,20 +343,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>口播出镜
-麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>既然有了麦克风硬件和usb，那为什么不物尽其用呢？
-可以再集成一个usb麦克风，连接电脑用来录音，获得更好的录音音质。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>那么，开干！！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TODO：做一下视频增稳</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -487,25 +445,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>首先参考大佬们演奏的动作，一只手按压并控制钢尺长度，另一只手弹拨。我先手绘草图，设计了一个原型机，验证下方案的可行性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>大佬演奏视频慢放
 手绘设计图展示</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">
-然后根据草图来建模。使用丝杆步进电机来控制钢尺移动、使用一个舵机压住钢尺、另一个舵机弹拨钢尺，最后加上底座就完成啦！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>【口播】
-快速演奏（无法压住钢尺，节奏乱掉）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>效果还可以，方案可行！！！
 那么接下来就是优化打磨，做一个完整的“自动演奏的钢尺琴”。</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -513,11 +457,6 @@
   <si>
     <t>来看看效果吧！
 【视频播放】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>另外，滑块直接套在丝杆上阻力比较大，速度快了可能会丢步。
-参考光驱中的结构，滑块是固定在导轨上的。那么给滑块加上导轨减小阻力也是很必要的</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -580,33 +519,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>因此，使用程序控制钢尺在不同长度弹奏，并用麦克风采集音频进行傅里叶变换，得到对应长度的频率。
-最终就可以拟合出一个高精度的频率-电机步进(step)对应曲线，来提高钢尺位置的精度，提高音准</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>【视频】在桌面拨动钢尺，测出几个基准长度的音高，而后拟合出频率-长度曲线。
-【视频】演奏时，候通过目标频率换算出具体的钢尺长度。
-但这样人工测量精度太低，导致音不准。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>拨动钢尺，用手机测量频率
 频率-长度表
 【口播】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>解决了速度问题，第2个要优化解决的就是音不准的问题
-那么如何提高音准呢？
-先看一下原型机上是怎么校准的：</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>第3个优化点就是——乐谱的记录与传输
-原型机的谱子格式是自定义的：
-比如，("5", 1)：即表示do、re、mi、fa、sol的Sol，时长为一拍，用串口发送一个音符演奏一个音符
-这样，虽然设计上简单，但每首歌都要一个音一个音来写，太麻烦了！！！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -624,14 +539,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>要怎么来优化呢？哎！不知道你有没有听过一种技术叫MIDI
-它即可以传输音符，又可以存储乐谱。
-举个例子，功能机时代的诺基亚铃声，它就是midi，比如这个
-【播放视频】
-midi可以使用多种接口进行传输，比如usb接口。而esp32主控就支持usb接口。使用usb midi就是最好的选择了。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>首先设计主板PCB，为了更方便复刻，都是使用的成品模块</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -682,29 +589,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>当然，除了使用上位机直接播放MIDI文件，也可以使用midi键盘直接演奏，我们先用这个手机MIDI键盘来试一下</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>除了最基本的演奏，如果接上真正的midi键盘，还能够支持力度感应，你按得越重，声音就越响亮有力，就像这样：</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>怎么样？这个赛博钢尺琴是不是还有点意思？
-如果你对这个项目感兴趣，那就快来动手复刻一个吧，全部的软硬件资料已经上传到了我的github仓库。也可以加我的Q群来沟通交流。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>【口播】
-在口播画面叠加：Github主页+QQ群（左手分别指一下左上与右上）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>当然，制作过程也不是一帆风顺。
-迭代了很多的版本，打印了这么多废弃版本，才得到的最终版本</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>别急！
 单单一只钢尺演奏难免有些单调，所以我希望再增加几个乐器</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -715,19 +599,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>不过上述的文具乐队还没有实现，如果这类视频观众朋友们喜欢，点个三连+关注！！
-后续UP主会持续更新的！！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>首先要优化的就是演奏速度
-前面演奏小星星的速度太慢了
-如果直接加快速度呢？我们来试一下
-【视频播放】
-直接乱掉了。弹奏小星星都这样了，要是弹个野蜂飞舞不得冒烟了？</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>为钢尺琴插上电源线与数据线
 设备管理器与音频设备展示</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -738,12 +609,84 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>怎么办呢？看来只能用程序员的方式——给它加个‘外挂’了
+    <t>【口播】（说外挂时，双手比yes并弯曲）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>为了实现自动化测量频率，需要增加一个麦克风，而后使用程序控制钢尺移动，并测量钢尺在不同长度下震动的频率。
+最终就可以拟合出一个高精度的频率与电机步进(step)对应曲线，来提高钢尺位置控制的精度，提高音准</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>确认了上述四个优化方向，那么，开干！！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然，制作过程也不是一帆风顺。
+迭代了很多次，打印了这么多废弃版本，才是现在看到的样子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+在口播画面叠加：Github主页+QQ群（左手指右上--&gt;左上）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么样？这个赛博钢尺琴是不是还有点意思？（语调高昂的）
+如果你对这个项目感兴趣，那就快来动手复刻一个吧，全部的软硬件资料已经上传到了我的github仓库。也可以加我的Q群来沟通交流。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>库克one more thing！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不过上述的文具乐队还在开发中，如果这类视频观众朋友们喜欢，麻烦点个三连+关注！！
+后续UP主会持续更新的！！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>但我又觉得很酷！怎么办呢？
+看来只能用程序员的方式——给它加个‘外挂’了
 让我来做一台能够“自动演奏的钢尺”</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>【口播】（说外挂时，双手比yes并弯曲）</t>
+    <t>首先参考大佬们演奏的动作，一只手按压并控制钢尺长度，另一只手弹拨。先手绘草图，设计了个原型机，来验证下方案的可行性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据草图来建模。使用丝杆步进电机来控制钢尺移动、使用一个舵机压住钢尺、另一个舵机弹拨钢尺，最后加上底座就完成啦！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】(手比1)
+快速演奏（无法压住钢尺，节奏乱掉）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一项要优化的就是演奏速度
+前面演奏小星星的速度太慢了
+如果直接调快速度呢？我们来试一下
+【视频播放】
+直接乱掉了。弹奏小星星都这样了，要是弹个野蜂飞舞，不得冒烟了？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>另外，滑块直接套在丝杆上阻力比较大，速度快了可能会导致步进电机丢步。
+参考光驱中的结构，滑块是固定在导轨上的。那么给滑块加上导轨减小阻力也是很必要的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解决了速度问题，第2个要优化解决的就是音不准的问题
+那么如何提高音准呢？
+先看一下原型机的工作原理：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【视频】在桌面拨动钢尺，测出几个基准长度的音高，而后拟合出频率-长度曲线。
+【视频】演奏时，通过要演奏的音高，换算出具体的钢尺长度，而后弹奏。
+但这样人工测量精度太低，会导致音不准。因此需要自动化测量提高精度。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -754,7 +697,79 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>以前在B站，钢尺演奏可是实打实的‘流量密码’。看似简单的却能弹出世界名曲。来，大家感受一下。</t>
+      <t>接下来，第3个优化点是——乐谱的记录与传输</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+原型机的谱子格式是自定义的：
+【视频】比如，这个 ("5", 1)：其中“5”表示do、re、mi、fa、sol的Sol，1表示时长为一拍。而后，用串口发送一个音符演奏一个音符
+这样，虽然设计上简单，但每首曲子都要一个音一个音来写，太麻烦了！！！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>​【口播】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+范大将军片段（画中画）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>要怎么来优化呢？哎！不知道你有没有听过一种技术叫MIDI
+它即可以传输音符，又可以存储乐谱。
+举个例子，功能机时代的诺基亚铃声，它就是midi，比如这个
+【播放视频】
+【视频】midi可以使用多种接口进行传输，比如usb接口。而esp32主控就支持usb。因此，使用usb midi就是最好的选择。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然，除了使用上位机直接播放MIDI文件，也可以使用midi键盘直接演奏，我们先用这个手机MIDI键盘来试一下
+【视频播放】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>除了最基本的演奏，如果接上真正的midi键盘，还能够支持力度感应，你按得越重，声音就越响亮有力，就像这样：
+【视频播放】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>曾几何时，钢尺演奏可是实打实的‘流量密码’。简简单单一根钢尺却能弹出世界名曲。来，大家感受一下。</t>
     </r>
     <r>
       <rPr>
@@ -766,8 +781,14 @@
       </rPr>
       <t xml:space="preserve">
 【视频播放】
-喔~~真是太酷了！！！我自己也想要尝试演奏一下！</t>
+喔~~真是太酷了！！！我自己也想要尝试演奏一下呢！</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>既然前面增加了麦克风硬件和usb接口，那为什么不物尽其用呢？
+【视频】第四个优化点就是
+【视频】集成usb麦克风，连接电脑用来录音，来获得更好的录音品质。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -775,7 +796,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="等线"/>
@@ -970,7 +991,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1064,30 +1085,18 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1102,6 +1111,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1529,6 +1547,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1536,7 +1555,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2413,36 +2431,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FBFDF2-C68F-43FE-8FE4-06F462270704}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2453,18 +2471,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G60"/>
-  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16.5"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="8.25" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="24" customWidth="1"/>
-    <col min="4" max="5" width="62.83203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="26.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.265625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.265625" style="24" customWidth="1"/>
+    <col min="4" max="5" width="62.796875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="26.265625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="9.08203125" style="3"/>
+    <col min="8" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2487,7 +2505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="49.5">
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A2" s="28">
         <v>0</v>
       </c>
@@ -2504,7 +2522,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33">
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A3" s="28">
         <f t="shared" ref="A3:A9" si="0">A2+B2</f>
         <v>1.1574074074074073E-4</v>
@@ -2516,16 +2534,16 @@
         <v>27</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="99">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.4">
       <c r="A4" s="28">
         <f t="shared" si="0"/>
         <v>1.7361111111111109E-4</v>
@@ -2533,17 +2551,17 @@
       <c r="B4" s="29">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C4" s="40" t="s">
-        <v>47</v>
+      <c r="C4" s="36" t="s">
+        <v>46</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="82.5">
+    <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.4">
       <c r="A5" s="27">
         <f t="shared" si="0"/>
         <v>2.8935185185185184E-4</v>
@@ -2551,15 +2569,15 @@
       <c r="B5" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C5" s="41"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>85</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="28">
         <f t="shared" si="0"/>
         <v>4.0509259259259258E-4</v>
@@ -2567,7 +2585,7 @@
       <c r="B6" s="29">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C6" s="41"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="6" t="s">
         <v>20</v>
       </c>
@@ -2576,7 +2594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="49.5">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A7" s="27">
         <f t="shared" si="0"/>
         <v>4.1666666666666664E-4</v>
@@ -2584,15 +2602,15 @@
       <c r="B7" s="26">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C7" s="41"/>
+      <c r="C7" s="37"/>
       <c r="D7" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33">
+        <v>141</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A8" s="27">
         <f t="shared" si="0"/>
         <v>5.0925925925925921E-4</v>
@@ -2600,15 +2618,15 @@
       <c r="B8" s="26">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C8" s="42"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>124</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="27">
         <f t="shared" si="0"/>
         <v>5.5555555555555556E-4</v>
@@ -2620,10 +2638,10 @@
         <v>18</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="9" customFormat="1" ht="33">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <f>A7+B7</f>
         <v>5.0925925925925921E-4</v>
@@ -2631,19 +2649,19 @@
       <c r="B10" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="36" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>95</v>
+        <v>91</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" s="9" customFormat="1" ht="49.5">
+    <row r="11" spans="1:7" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <f>A8+B8</f>
         <v>5.5555555555555556E-4</v>
@@ -2651,19 +2669,19 @@
       <c r="B11" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C11" s="41"/>
+      <c r="C11" s="37"/>
       <c r="D11" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" ht="33">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A12" s="27">
         <f>A9+B9</f>
         <v>6.134259259259259E-4</v>
@@ -2671,17 +2689,17 @@
       <c r="B12" s="26">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C12" s="41"/>
+      <c r="C12" s="37"/>
       <c r="D12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>93</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="33">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <f t="shared" ref="A13:A17" si="1">A11+B11</f>
         <v>6.9444444444444447E-4</v>
@@ -2689,17 +2707,17 @@
       <c r="B13" s="4">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C13" s="42"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="41" t="s">
         <v>92</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>99</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" s="16" customFormat="1" ht="82.5">
+    <row r="14" spans="1:7" s="16" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A14" s="27">
         <f t="shared" si="1"/>
         <v>7.5231481481481482E-4</v>
@@ -2707,21 +2725,21 @@
       <c r="B14" s="26">
         <v>1.8518518518518518E-4</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>108</v>
+      <c r="C14" s="39" t="s">
+        <v>100</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>141</v>
+        <v>135</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>136</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:7" s="16" customFormat="1" ht="66">
+    <row r="15" spans="1:7" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.4">
       <c r="A15" s="27">
         <f t="shared" si="1"/>
         <v>7.6388888888888893E-4</v>
@@ -2729,19 +2747,19 @@
       <c r="B15" s="26">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="C15" s="43"/>
+      <c r="C15" s="39"/>
       <c r="D15" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="16" customFormat="1" ht="33">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.4">
       <c r="A16" s="27">
         <f t="shared" si="1"/>
         <v>9.3749999999999997E-4</v>
@@ -2749,17 +2767,17 @@
       <c r="B16" s="26">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C16" s="43"/>
+      <c r="C16" s="39"/>
       <c r="D16" s="13" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
     </row>
-    <row r="17" spans="1:7" s="16" customFormat="1" ht="82.5">
+    <row r="17" spans="1:7" s="16" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A17" s="27">
         <f t="shared" si="1"/>
         <v>9.9537037037037042E-4</v>
@@ -2767,30 +2785,30 @@
       <c r="B17" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C17" s="43"/>
+      <c r="C17" s="39"/>
       <c r="D17" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>104</v>
+        <v>97</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>96</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="1:7" s="16" customFormat="1">
+    <row r="18" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A18" s="27"/>
       <c r="B18" s="26"/>
-      <c r="C18" s="43"/>
+      <c r="C18" s="39"/>
       <c r="D18" s="13" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
     </row>
-    <row r="19" spans="1:7" s="16" customFormat="1" ht="49.5">
+    <row r="19" spans="1:7" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.4">
       <c r="A19" s="27">
         <f>A16+B16</f>
         <v>1.2847222222222223E-3</v>
@@ -2798,28 +2816,28 @@
       <c r="B19" s="26">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C19" s="43"/>
+      <c r="C19" s="39"/>
       <c r="D19" s="13" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="20" spans="1:7" s="16" customFormat="1">
+    <row r="20" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A20" s="27"/>
       <c r="B20" s="26"/>
-      <c r="C20" s="43"/>
+      <c r="C20" s="39"/>
       <c r="D20" s="13" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
     </row>
-    <row r="21" spans="1:7" s="16" customFormat="1">
+    <row r="21" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <f>A17+B17</f>
         <v>1.1111111111111111E-3</v>
@@ -2827,7 +2845,7 @@
       <c r="B21" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C21" s="43"/>
+      <c r="C21" s="39"/>
       <c r="D21" s="18" t="s">
         <v>36</v>
       </c>
@@ -2835,7 +2853,7 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="22" spans="1:7" ht="49.5">
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <f>A19+B19</f>
         <v>1.3773148148148149E-3</v>
@@ -2843,19 +2861,19 @@
       <c r="B22" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C22" s="43" t="s">
-        <v>109</v>
+      <c r="C22" s="39" t="s">
+        <v>101</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>117</v>
+        <v>88</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>138</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" ht="66">
+    <row r="23" spans="1:7" ht="90" x14ac:dyDescent="0.4">
       <c r="A23" s="27">
         <f>A22+B22</f>
         <v>1.4930555555555556E-3</v>
@@ -2863,15 +2881,15 @@
       <c r="B23" s="26">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C23" s="43"/>
+      <c r="C23" s="39"/>
       <c r="D23" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="82.5">
+        <v>106</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="75" x14ac:dyDescent="0.4">
       <c r="A24" s="27">
         <f>A23+B23</f>
         <v>1.7824074074074075E-3</v>
@@ -2879,24 +2897,24 @@
       <c r="B24" s="26">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C24" s="43"/>
+      <c r="C24" s="39"/>
       <c r="D24" s="10" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="27"/>
       <c r="B25" s="26"/>
-      <c r="C25" s="43"/>
+      <c r="C25" s="39"/>
       <c r="D25" s="10" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E25" s="10"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <f>A24+B24</f>
         <v>2.0717592592592593E-3</v>
@@ -2904,13 +2922,13 @@
       <c r="B26" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C26" s="43"/>
+      <c r="C26" s="39"/>
       <c r="D26" s="11" t="s">
         <v>36</v>
       </c>
       <c r="E26" s="10"/>
     </row>
-    <row r="27" spans="1:7" ht="82.5">
+    <row r="27" spans="1:7" ht="90" x14ac:dyDescent="0.4">
       <c r="A27" s="27">
         <f t="shared" ref="A27" si="2">A26+B26</f>
         <v>2.0833333333333333E-3</v>
@@ -2918,38 +2936,38 @@
       <c r="B27" s="26">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="C27" s="43" t="s">
-        <v>110</v>
+      <c r="C27" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>118</v>
+        <v>107</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>140</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" ht="99">
+    <row r="28" spans="1:7" ht="90" x14ac:dyDescent="0.4">
       <c r="A28" s="27">
-        <f t="shared" ref="A28:A52" si="3">A27+B27</f>
+        <f t="shared" ref="A28:A51" si="3">A27+B27</f>
         <v>2.3148148148148147E-3</v>
       </c>
       <c r="B28" s="26">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="C28" s="43"/>
+      <c r="C28" s="39"/>
       <c r="D28" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>121</v>
+        <v>108</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <f>A28+B28</f>
         <v>2.7777777777777775E-3</v>
@@ -2957,13 +2975,13 @@
       <c r="B29" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C29" s="43"/>
+      <c r="C29" s="39"/>
       <c r="D29" s="18" t="s">
         <v>36</v>
       </c>
       <c r="E29" s="12"/>
     </row>
-    <row r="30" spans="1:7" s="17" customFormat="1" ht="33">
+    <row r="30" spans="1:7" s="17" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="27">
         <f>A29+B29</f>
         <v>2.7893518518518515E-3</v>
@@ -2971,19 +2989,19 @@
       <c r="B30" s="26">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="C30" s="43" t="s">
-        <v>111</v>
+      <c r="C30" s="39" t="s">
+        <v>103</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>71</v>
+        <v>142</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>147</v>
       </c>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:7" s="17" customFormat="1">
+    <row r="31" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <f>A30+B30</f>
         <v>2.9629629629629624E-3</v>
@@ -2991,7 +3009,7 @@
       <c r="B31" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C31" s="43"/>
+      <c r="C31" s="39"/>
       <c r="D31" s="18" t="s">
         <v>36</v>
       </c>
@@ -2999,7 +3017,7 @@
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" s="16" customFormat="1" ht="49.5">
+    <row r="32" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
       <c r="A32" s="27">
         <f>A31+B31</f>
         <v>2.9745370370370364E-3</v>
@@ -3007,17 +3025,17 @@
       <c r="B32" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C32" s="34"/>
+      <c r="C32" s="31"/>
       <c r="D32" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>87</v>
+        <v>105</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>83</v>
       </c>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="5">
         <f>A32+B32</f>
         <v>3.0902777777777773E-3</v>
@@ -3025,17 +3043,17 @@
       <c r="B33" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="33" t="s">
         <v>16</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>88</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="28">
         <f t="shared" si="3"/>
         <v>3.1481481481481477E-3</v>
@@ -3043,15 +3061,15 @@
       <c r="B34" s="29">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C34" s="38"/>
+      <c r="C34" s="34"/>
       <c r="D34" s="6" t="s">
         <v>37</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="33">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A35" s="28">
         <f t="shared" si="3"/>
         <v>3.2638888888888887E-3</v>
@@ -3059,13 +3077,13 @@
       <c r="B35" s="29">
         <v>5.7870370370370378E-4</v>
       </c>
-      <c r="C35" s="38"/>
+      <c r="C35" s="34"/>
       <c r="D35" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="28">
         <f t="shared" si="3"/>
         <v>3.8425925925925923E-3</v>
@@ -3073,16 +3091,16 @@
       <c r="B36" s="29">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C36" s="38"/>
+      <c r="C36" s="34"/>
       <c r="D36" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="28">
         <f t="shared" si="3"/>
         <v>3.9814814814814808E-3</v>
@@ -3090,13 +3108,13 @@
       <c r="B37" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C37" s="38"/>
+      <c r="C37" s="34"/>
       <c r="D37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="28">
         <f t="shared" si="3"/>
         <v>4.0393518518518513E-3</v>
@@ -3104,13 +3122,13 @@
       <c r="B38" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C38" s="38"/>
+      <c r="C38" s="34"/>
       <c r="D38" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:7" ht="33">
+    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A39" s="28">
         <f t="shared" si="3"/>
         <v>4.0972222222222217E-3</v>
@@ -3118,13 +3136,13 @@
       <c r="B39" s="29">
         <v>5.7870370370370378E-4</v>
       </c>
-      <c r="C39" s="38"/>
+      <c r="C39" s="34"/>
       <c r="D39" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="28">
         <f t="shared" si="3"/>
         <v>4.6759259259259254E-3</v>
@@ -3132,7 +3150,7 @@
       <c r="B40" s="29">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C40" s="38"/>
+      <c r="C40" s="34"/>
       <c r="D40" s="6" t="s">
         <v>7</v>
       </c>
@@ -3140,7 +3158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="27">
         <f t="shared" si="3"/>
         <v>4.7337962962962958E-3</v>
@@ -3148,16 +3166,16 @@
       <c r="B41" s="26">
         <v>3.4722222222222222E-5</v>
       </c>
-      <c r="C41" s="38"/>
+      <c r="C41" s="34"/>
       <c r="D41" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="27">
         <f t="shared" si="3"/>
         <v>4.7685185185185183E-3</v>
@@ -3165,7 +3183,7 @@
       <c r="B42" s="26">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C42" s="39"/>
+      <c r="C42" s="35"/>
       <c r="D42" s="6" t="s">
         <v>8</v>
       </c>
@@ -3173,21 +3191,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="27">
         <f t="shared" si="3"/>
         <v>4.8148148148148143E-3</v>
       </c>
       <c r="B43" s="26"/>
-      <c r="C43" s="31"/>
+      <c r="C43" s="20"/>
       <c r="D43" s="30" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="33">
+    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A44" s="27">
         <f t="shared" si="3"/>
         <v>4.8148148148148143E-3</v>
@@ -3195,21 +3213,21 @@
       <c r="B44" s="4">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="C44" s="37" t="s">
+      <c r="C44" s="33" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="49.5">
+    <row r="45" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A45" s="27">
         <f t="shared" si="3"/>
         <v>5.2777777777777771E-3</v>
@@ -3217,16 +3235,16 @@
       <c r="B45" s="26">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C45" s="38"/>
+      <c r="C45" s="34"/>
       <c r="D45" s="8" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:7" ht="33">
+    <row r="46" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A46" s="27">
         <f t="shared" si="3"/>
         <v>5.6249999999999989E-3</v>
@@ -3234,16 +3252,16 @@
       <c r="B46" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C46" s="38"/>
+      <c r="C46" s="34"/>
       <c r="D46" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>133</v>
+        <v>116</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>144</v>
       </c>
       <c r="G46" s="7"/>
     </row>
-    <row r="47" spans="1:7" ht="33">
+    <row r="47" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A47" s="27">
         <f t="shared" si="3"/>
         <v>5.7407407407407398E-3</v>
@@ -3251,29 +3269,29 @@
       <c r="B47" s="26">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C47" s="38"/>
+      <c r="C47" s="34"/>
       <c r="D47" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>119</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="27">
         <f t="shared" si="3"/>
         <v>6.1458333333333321E-3</v>
       </c>
       <c r="B48" s="26"/>
-      <c r="C48" s="38"/>
+      <c r="C48" s="34"/>
       <c r="D48" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>117</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="27">
         <f t="shared" si="3"/>
         <v>6.1458333333333321E-3</v>
@@ -3281,12 +3299,12 @@
       <c r="B49" s="26">
         <v>2.3148148148148147E-5</v>
       </c>
-      <c r="C49" s="38"/>
+      <c r="C49" s="34"/>
       <c r="D49" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="33">
+    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A50" s="27">
         <f t="shared" si="3"/>
         <v>6.1689814814814802E-3</v>
@@ -3294,183 +3312,191 @@
       <c r="B50" s="26">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C50" s="39"/>
+      <c r="C50" s="35"/>
       <c r="D50" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>137</v>
+        <v>112</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="G50" s="7"/>
     </row>
-    <row r="51" spans="1:7" ht="49.5">
-      <c r="A51" s="36">
+    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="A51" s="5">
         <f t="shared" si="3"/>
         <v>6.5740740740740725E-3</v>
       </c>
       <c r="B51" s="4">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C51" s="37" t="s">
+      <c r="C51" s="33" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="33">
-      <c r="A52" s="36">
-        <f t="shared" si="3"/>
+        <v>128</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="5"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A53" s="5">
+        <f>A51+B51</f>
         <v>6.9212962962962943E-3</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B53" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C52" s="38"/>
-      <c r="D52" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="27">
-        <f t="shared" ref="A53:A60" si="4">A52+B52</f>
+      <c r="C53" s="34"/>
+      <c r="D53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="27">
+        <f t="shared" ref="A54:A61" si="4">A53+B53</f>
         <v>7.0370370370370352E-3</v>
       </c>
-      <c r="B53" s="26">
+      <c r="B54" s="26">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C53" s="38"/>
-      <c r="D53" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="27">
+      <c r="C54" s="34"/>
+      <c r="D54" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="27">
         <f t="shared" si="4"/>
         <v>7.0833333333333312E-3</v>
       </c>
-      <c r="B54" s="26">
+      <c r="B55" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C54" s="38"/>
-      <c r="D54" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="33">
-      <c r="A55" s="27">
+      <c r="C55" s="34"/>
+      <c r="D55" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A56" s="27">
         <f t="shared" si="4"/>
         <v>7.1412037037037017E-3</v>
       </c>
-      <c r="B55" s="26">
+      <c r="B56" s="26">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C55" s="38"/>
-      <c r="D55" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="27">
+      <c r="C56" s="34"/>
+      <c r="D56" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" s="27">
         <f t="shared" si="4"/>
         <v>7.2106481481481457E-3</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B57" s="26">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C56" s="39"/>
-      <c r="D56" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="49.5">
-      <c r="A57" s="5">
+      <c r="C57" s="35"/>
+      <c r="D57" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="A58" s="5">
         <f t="shared" si="4"/>
         <v>7.2800925925925897E-3</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B58" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C57" s="20"/>
-      <c r="D57" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="5">
+      <c r="C58" s="20"/>
+      <c r="D58" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A59" s="5">
         <f t="shared" si="4"/>
         <v>7.3958333333333307E-3</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B59" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C58" s="37" t="s">
+      <c r="C59" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58" s="6" t="s">
+      <c r="D59" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="5">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A60" s="5">
         <f t="shared" si="4"/>
         <v>7.5115740740740716E-3</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B60" s="4">
         <v>1.5046296296296294E-3</v>
       </c>
-      <c r="C59" s="38"/>
-      <c r="D59" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G59" s="6" t="s">
+      <c r="C60" s="34"/>
+      <c r="D60" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="5">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A61" s="5">
         <f t="shared" si="4"/>
         <v>9.0162037037037016E-3</v>
       </c>
-      <c r="B60" s="35">
+      <c r="B61" s="32">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="C60" s="39"/>
-      <c r="D60" s="6" t="s">
+      <c r="C61" s="35"/>
+      <c r="D61" s="6" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="C51:C56"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="C51:C57"/>
     <mergeCell ref="C4:C8"/>
     <mergeCell ref="C33:C42"/>
     <mergeCell ref="C10:C13"/>
@@ -3488,15 +3514,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07104DAA-2E56-4B7D-A05C-4806FDF0CFBA}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="4" max="4" width="25.6640625" customWidth="1"/>
     <col min="5" max="5" width="73.6640625" customWidth="1"/>
-    <col min="6" max="11" width="67.1640625" customWidth="1"/>
+    <col min="6" max="11" width="67.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="16" customFormat="1" ht="99">
+    <row r="1" spans="1:7" s="16" customFormat="1" ht="90.75" x14ac:dyDescent="0.4">
       <c r="A1" s="27" t="e">
         <f t="shared" ref="A1" si="0">#REF!+#REF!</f>
         <v>#REF!</v>
@@ -3509,7 +3535,7 @@
         <v>29</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
@@ -3523,68 +3549,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3596,25 +3622,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D1F29C-200F-4BB5-9251-208FEB1786B7}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -3626,9 +3652,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3640,9 +3666,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4">
         <v>6</v>

--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\develop\my_workspace\self_playing_ruler\v1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AE93FD-5153-48EC-80D1-1458CBD2E7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CF7EF1-ADA5-4398-9B07-23A2EF73983E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封标" sheetId="4" r:id="rId1"/>
@@ -33,12 +33,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="149">
   <si>
     <t>​​画面描述 (分镜)​​</t>
   </si>
@@ -560,17 +563,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>spoiler（片头cyberpunk 2077 预告BGM演奏）
-原声--&gt;效果器
-加上BGM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>还可以添加一些效果器，比如给这首曲子加上过载效果
-在加上BGM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>【口播】
 手机midi键盘演示：do re mi fa。。。</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -596,16 +588,6 @@
   <si>
     <t>【口播】
 做出握拳加油的手势</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>为钢尺琴插上电源线与数据线
-设备管理器与音频设备展示</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个DRI MIDI与DIR MIC设备就是钢尺琴啦！
-让我们用它来演奏一曲！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -791,12 +773,58 @@
 【视频】集成usb麦克风，连接电脑用来录音，来获得更好的录音品质。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Unnamed没名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>没名的钢尺找音教程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个DRI MIDI与DIR MIC设备就是钢尺琴啦！
+【视频】
+【视频】
+让我们用它来演奏一曲！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>spoiler（片头cyberpunk 2077 预告BGM演奏）
+原声--&gt;鼓点--&gt;效果器--&gt;BGM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为钢尺琴插上电源线与数据线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+设备管理器展示
+cubase中MIDI设备
+音频设备展示</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="等线"/>
@@ -991,7 +1019,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1028,18 +1056,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1055,9 +1077,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1112,13 +1131,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1547,7 +1578,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1555,6 +1585,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2431,34 +2462,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FBFDF2-C68F-43FE-8FE4-06F462270704}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
@@ -2472,17 +2503,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="8.265625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.265625" style="24" customWidth="1"/>
-    <col min="4" max="5" width="62.796875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="26.265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.25" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="21" customWidth="1"/>
+    <col min="4" max="5" width="62.83203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="26.25" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="3"/>
+    <col min="8" max="16384" width="9.08203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2505,14 +2536,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.4">
-      <c r="A2" s="28">
+    <row r="2" spans="1:7" ht="49.5">
+      <c r="A2" s="25">
         <v>0</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -2522,15 +2553,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A3" s="28">
+    <row r="3" spans="1:7" ht="33">
+      <c r="A3" s="25">
         <f t="shared" ref="A3:A9" si="0">A2+B2</f>
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -2543,105 +2574,106 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.4">
-      <c r="A4" s="28">
+    <row r="4" spans="1:7" ht="99">
+      <c r="A4" s="25">
         <f t="shared" si="0"/>
         <v>1.7361111111111109E-4</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="33" t="s">
         <v>46</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="30" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.4">
-      <c r="A5" s="27">
+      <c r="E4" s="37" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="82.5">
+      <c r="A5" s="24">
         <f t="shared" si="0"/>
         <v>2.8935185185185184E-4</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="23">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C5" s="37"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="37" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" s="28">
+    <row r="6" spans="1:7">
+      <c r="A6" s="25">
         <f t="shared" si="0"/>
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="26">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C6" s="37"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="38"/>
       <c r="F6" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.4">
-      <c r="A7" s="27">
+    <row r="7" spans="1:7" ht="49.5">
+      <c r="A7" s="24">
         <f t="shared" si="0"/>
         <v>4.1666666666666664E-4</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="23">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" s="30" t="s">
+      <c r="C7" s="34"/>
+      <c r="D7" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.4">
-      <c r="A8" s="27">
+    <row r="8" spans="1:7" ht="49.5">
+      <c r="A8" s="24">
         <f t="shared" si="0"/>
         <v>5.0925925925925921E-4</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="23">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C8" s="38"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" s="27">
+        <v>120</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="24">
         <f t="shared" si="0"/>
         <v>5.5555555555555556E-4</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="23">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.4">
+      <c r="E9" s="37"/>
+    </row>
+    <row r="10" spans="1:7" s="9" customFormat="1" ht="33">
       <c r="A10" s="5">
         <f>A7+B7</f>
         <v>5.0925925925925921E-4</v>
@@ -2649,19 +2681,19 @@
       <c r="B10" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>133</v>
+      <c r="E10" s="39" t="s">
+        <v>129</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" s="9" customFormat="1" ht="33">
       <c r="A11" s="5">
         <f>A8+B8</f>
         <v>5.5555555555555556E-4</v>
@@ -2669,37 +2701,37 @@
       <c r="B11" s="4">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C11" s="37"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>134</v>
+      <c r="E11" s="39" t="s">
+        <v>130</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>78</v>
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A12" s="27">
+    <row r="12" spans="1:7" ht="33">
+      <c r="A12" s="24">
         <f>A9+B9</f>
         <v>6.134259259259259E-4</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="23">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C12" s="37"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="39" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="33">
       <c r="A13" s="5">
         <f t="shared" ref="A13:A17" si="1">A11+B11</f>
         <v>6.9444444444444447E-4</v>
@@ -2707,137 +2739,137 @@
       <c r="B13" s="4">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C13" s="38"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="40" t="s">
         <v>92</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" s="16" customFormat="1" ht="75" x14ac:dyDescent="0.4">
-      <c r="A14" s="27">
+    <row r="14" spans="1:7" s="14" customFormat="1" ht="82.5">
+      <c r="A14" s="24">
         <f t="shared" si="1"/>
         <v>7.5231481481481482E-4</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="23">
         <v>1.8518518518518518E-4</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="36" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="F14" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" spans="1:7" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.4">
-      <c r="A15" s="27">
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:7" s="14" customFormat="1" ht="66">
+      <c r="A15" s="24">
         <f t="shared" si="1"/>
         <v>7.6388888888888893E-4</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="23">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="18" t="s">
+      <c r="F15" s="13"/>
+      <c r="G15" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.4">
-      <c r="A16" s="27">
+    <row r="16" spans="1:7" s="14" customFormat="1" ht="33">
+      <c r="A16" s="24">
         <f t="shared" si="1"/>
         <v>9.3749999999999997E-4</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="23">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-    </row>
-    <row r="17" spans="1:7" s="16" customFormat="1" ht="75" x14ac:dyDescent="0.4">
-      <c r="A17" s="27">
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:7" s="14" customFormat="1" ht="82.5">
+      <c r="A17" s="24">
         <f t="shared" si="1"/>
         <v>9.9537037037037042E-4</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="23">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="13" t="s">
+      <c r="C17" s="36"/>
+      <c r="D17" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="27"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="13" t="s">
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7" s="14" customFormat="1">
+      <c r="A18" s="24"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" spans="1:7" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.4">
-      <c r="A19" s="27">
+      <c r="E18" s="37"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7" s="14" customFormat="1" ht="66">
+      <c r="A19" s="24">
         <f>A16+B16</f>
         <v>1.2847222222222223E-3</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="23">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="13" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="13" t="s">
+      <c r="E19" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:7" s="14" customFormat="1">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E20" s="41"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="1:7" s="14" customFormat="1">
       <c r="A21" s="5">
         <f>A17+B17</f>
         <v>1.1111111111111111E-3</v>
@@ -2845,15 +2877,15 @@
       <c r="B21" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="18" t="s">
+      <c r="C21" s="36"/>
+      <c r="D21" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="21"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="E21" s="41"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:7" ht="49.5">
       <c r="A22" s="5">
         <f>A19+B19</f>
         <v>1.3773148148148149E-3</v>
@@ -2861,60 +2893,60 @@
       <c r="B22" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="36" t="s">
         <v>101</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="42" t="s">
-        <v>138</v>
+      <c r="E22" s="41" t="s">
+        <v>134</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" ht="90" x14ac:dyDescent="0.4">
-      <c r="A23" s="27">
+    <row r="23" spans="1:7" ht="66">
+      <c r="A23" s="24">
         <f>A22+B22</f>
         <v>1.4930555555555556E-3</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="23">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C23" s="39"/>
+      <c r="C23" s="36"/>
       <c r="D23" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E23" s="30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="75" x14ac:dyDescent="0.4">
-      <c r="A24" s="27">
+      <c r="E23" s="37" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="82.5">
+      <c r="A24" s="24">
         <f>A23+B23</f>
         <v>1.7824074074074075E-3</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="23">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C24" s="39"/>
+      <c r="C24" s="36"/>
       <c r="D24" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="39"/>
+      <c r="E24" s="43" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="24"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="36"/>
       <c r="D25" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E25" s="43"/>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="5">
         <f>A24+B24</f>
         <v>2.0717592592592593E-3</v>
@@ -2922,52 +2954,52 @@
       <c r="B26" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C26" s="39"/>
+      <c r="C26" s="36"/>
       <c r="D26" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" spans="1:7" ht="90" x14ac:dyDescent="0.4">
-      <c r="A27" s="27">
+      <c r="E26" s="43"/>
+    </row>
+    <row r="27" spans="1:7" ht="99">
+      <c r="A27" s="24">
         <f t="shared" ref="A27" si="2">A26+B26</f>
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="23">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="36" t="s">
         <v>102</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="42" t="s">
-        <v>140</v>
+      <c r="E27" s="41" t="s">
+        <v>136</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" ht="90" x14ac:dyDescent="0.4">
-      <c r="A28" s="27">
+    <row r="28" spans="1:7" ht="99">
+      <c r="A28" s="24">
         <f t="shared" ref="A28:A51" si="3">A27+B27</f>
         <v>2.3148148148148147E-3</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="23">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="C28" s="39"/>
+      <c r="C28" s="36"/>
       <c r="D28" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="30" t="s">
-        <v>143</v>
+      <c r="E28" s="37" t="s">
+        <v>139</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7">
       <c r="A29" s="5">
         <f>A28+B28</f>
         <v>2.7777777777777775E-3</v>
@@ -2975,33 +3007,33 @@
       <c r="B29" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="18" t="s">
+      <c r="C29" s="36"/>
+      <c r="D29" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="12"/>
-    </row>
-    <row r="30" spans="1:7" s="17" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="27">
+      <c r="E29" s="41"/>
+    </row>
+    <row r="30" spans="1:7" s="15" customFormat="1" ht="59.25" customHeight="1">
+      <c r="A30" s="24">
         <f>A29+B29</f>
         <v>2.7893518518518515E-3</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="23">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="36" t="s">
         <v>103</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.4">
+        <v>138</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+    </row>
+    <row r="31" spans="1:7" s="15" customFormat="1">
       <c r="A31" s="5">
         <f>A30+B30</f>
         <v>2.9629629629629624E-3</v>
@@ -3009,33 +3041,33 @@
       <c r="B31" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="18" t="s">
+      <c r="C31" s="36"/>
+      <c r="D31" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="21"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" spans="1:7" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.4">
-      <c r="A32" s="27">
+      <c r="E31" s="41"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+    </row>
+    <row r="32" spans="1:7" s="14" customFormat="1" ht="49.5">
+      <c r="A32" s="24">
         <f>A31+B31</f>
         <v>2.9745370370370364E-3</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="23">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C32" s="31"/>
+      <c r="C32" s="28"/>
       <c r="D32" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E32" s="42" t="s">
+      <c r="E32" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="5">
         <f>A32+B32</f>
         <v>3.0902777777777773E-3</v>
@@ -3043,285 +3075,290 @@
       <c r="B33" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="30" t="s">
         <v>16</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="30" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="28">
+      <c r="E33" s="37" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="25">
         <f t="shared" si="3"/>
         <v>3.1481481481481477E-3</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C34" s="34"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="37" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A35" s="28">
+    <row r="35" spans="1:7" ht="33">
+      <c r="A35" s="25">
         <f t="shared" si="3"/>
         <v>3.2638888888888887E-3</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="26">
         <v>5.7870370370370378E-4</v>
       </c>
-      <c r="C35" s="34"/>
+      <c r="C35" s="31"/>
       <c r="D35" s="6" t="s">
         <v>42</v>
       </c>
+      <c r="E35" s="37"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" s="28">
+    <row r="36" spans="1:7">
+      <c r="A36" s="25">
         <f t="shared" si="3"/>
         <v>3.8425925925925923E-3</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="26">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C36" s="34"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="37" t="s">
         <v>110</v>
       </c>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A37" s="28">
+    <row r="37" spans="1:7">
+      <c r="A37" s="25">
         <f t="shared" si="3"/>
         <v>3.9814814814814808E-3</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C37" s="34"/>
+      <c r="C37" s="31"/>
       <c r="D37" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="E37" s="37"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A38" s="28">
+    <row r="38" spans="1:7">
+      <c r="A38" s="25">
         <f t="shared" si="3"/>
         <v>4.0393518518518513E-3</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C38" s="34"/>
+      <c r="C38" s="31"/>
       <c r="D38" s="6" t="s">
         <v>58</v>
       </c>
+      <c r="E38" s="37"/>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A39" s="28">
+    <row r="39" spans="1:7" ht="33">
+      <c r="A39" s="25">
         <f t="shared" si="3"/>
         <v>4.0972222222222217E-3</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="26">
         <v>5.7870370370370378E-4</v>
       </c>
-      <c r="C39" s="34"/>
+      <c r="C39" s="31"/>
       <c r="D39" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="E39" s="37"/>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="28">
+    <row r="40" spans="1:7">
+      <c r="A40" s="25">
         <f t="shared" si="3"/>
         <v>4.6759259259259254E-3</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C40" s="34"/>
+      <c r="C40" s="31"/>
       <c r="D40" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="E40" s="37"/>
       <c r="F40" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A41" s="27">
+    <row r="41" spans="1:7">
+      <c r="A41" s="24">
         <f t="shared" si="3"/>
         <v>4.7337962962962958E-3</v>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="23">
         <v>3.4722222222222222E-5</v>
       </c>
-      <c r="C41" s="34"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="37" t="s">
         <v>80</v>
       </c>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A42" s="27">
+    <row r="42" spans="1:7">
+      <c r="A42" s="24">
         <f t="shared" si="3"/>
         <v>4.7685185185185183E-3</v>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="23">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C42" s="35"/>
+      <c r="C42" s="32"/>
       <c r="D42" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A43" s="27">
+    <row r="43" spans="1:7">
+      <c r="A43" s="24">
         <f t="shared" si="3"/>
         <v>4.8148148148148143E-3</v>
       </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="30" t="s">
+      <c r="B43" s="23"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="F43" s="30" t="s">
+      <c r="E43" s="37"/>
+      <c r="F43" s="27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A44" s="27">
+    <row r="44" spans="1:7" ht="66">
+      <c r="A44" s="24">
         <f t="shared" si="3"/>
         <v>4.8148148148148143E-3</v>
       </c>
       <c r="B44" s="4">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="C44" s="33" t="s">
+      <c r="C44" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>123</v>
+      <c r="D44" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>146</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="45" x14ac:dyDescent="0.4">
-      <c r="A45" s="27">
+    <row r="45" spans="1:7" ht="33">
+      <c r="A45" s="24">
         <f t="shared" si="3"/>
         <v>5.2777777777777771E-3</v>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="23">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C45" s="34"/>
+      <c r="C45" s="31"/>
       <c r="D45" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>115</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="E45" s="37"/>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:7" ht="45" x14ac:dyDescent="0.4">
-      <c r="A46" s="27">
+    <row r="46" spans="1:7" ht="49.5">
+      <c r="A46" s="24">
         <f t="shared" si="3"/>
         <v>5.6249999999999989E-3</v>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="23">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C46" s="34"/>
+      <c r="C46" s="31"/>
       <c r="D46" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>144</v>
+        <v>114</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>140</v>
       </c>
       <c r="G46" s="7"/>
     </row>
-    <row r="47" spans="1:7" ht="45" x14ac:dyDescent="0.4">
-      <c r="A47" s="27">
+    <row r="47" spans="1:7" ht="49.5">
+      <c r="A47" s="24">
         <f t="shared" si="3"/>
         <v>5.7407407407407398E-3</v>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="23">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C47" s="34"/>
+      <c r="C47" s="31"/>
       <c r="D47" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E47" s="30" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A48" s="27">
+        <v>117</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="24">
         <f t="shared" si="3"/>
         <v>6.1458333333333321E-3</v>
       </c>
-      <c r="B48" s="26"/>
-      <c r="C48" s="34"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="31"/>
       <c r="D48" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A49" s="27">
+        <v>115</v>
+      </c>
+      <c r="E48" s="37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="24">
         <f t="shared" si="3"/>
         <v>6.1458333333333321E-3</v>
       </c>
-      <c r="B49" s="26">
+      <c r="B49" s="23">
         <v>2.3148148148148147E-5</v>
       </c>
-      <c r="C49" s="34"/>
+      <c r="C49" s="31"/>
       <c r="D49" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A50" s="27">
+      <c r="E49" s="37"/>
+    </row>
+    <row r="50" spans="1:7" ht="33">
+      <c r="A50" s="24">
         <f t="shared" si="3"/>
         <v>6.1689814814814802E-3</v>
       </c>
-      <c r="B50" s="26">
+      <c r="B50" s="23">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C50" s="35"/>
+      <c r="C50" s="32"/>
       <c r="D50" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E50" s="30" t="s">
-        <v>127</v>
+      <c r="E50" s="37" t="s">
+        <v>123</v>
       </c>
       <c r="G50" s="7"/>
     </row>
-    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" ht="49.5">
       <c r="A51" s="5">
         <f t="shared" si="3"/>
         <v>6.5740740740740725E-3</v>
@@ -3329,25 +3366,26 @@
       <c r="B51" s="4">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C51" s="33" t="s">
+      <c r="C51" s="30" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E51" s="30" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+        <v>124</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="5"/>
       <c r="B52" s="4"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="C52" s="31"/>
+      <c r="D52" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52" s="37"/>
+    </row>
+    <row r="53" spans="1:7" ht="33">
       <c r="A53" s="5">
         <f>A51+B51</f>
         <v>6.9212962962962943E-3</v>
@@ -3355,79 +3393,79 @@
       <c r="B53" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C53" s="34"/>
+      <c r="C53" s="31"/>
       <c r="D53" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E53" s="30" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A54" s="27">
+      <c r="E53" s="37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="24">
         <f t="shared" ref="A54:A61" si="4">A53+B53</f>
         <v>7.0370370370370352E-3</v>
       </c>
-      <c r="B54" s="26">
+      <c r="B54" s="23">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C54" s="34"/>
+      <c r="C54" s="31"/>
       <c r="D54" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="37" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A55" s="27">
+    <row r="55" spans="1:7">
+      <c r="A55" s="24">
         <f t="shared" si="4"/>
         <v>7.0833333333333312E-3</v>
       </c>
-      <c r="B55" s="26">
+      <c r="B55" s="23">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C55" s="34"/>
+      <c r="C55" s="31"/>
       <c r="D55" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="37" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="30" x14ac:dyDescent="0.4">
-      <c r="A56" s="27">
+    <row r="56" spans="1:7" ht="33">
+      <c r="A56" s="24">
         <f t="shared" si="4"/>
         <v>7.1412037037037017E-3</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="23">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C56" s="34"/>
+      <c r="C56" s="31"/>
       <c r="D56" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A57" s="27">
+    <row r="57" spans="1:7">
+      <c r="A57" s="24">
         <f t="shared" si="4"/>
         <v>7.2106481481481457E-3</v>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="23">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C57" s="35"/>
+      <c r="C57" s="32"/>
       <c r="D57" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="37" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" ht="49.5">
       <c r="A58" s="5">
         <f t="shared" si="4"/>
         <v>7.2800925925925897E-3</v>
@@ -3435,15 +3473,15 @@
       <c r="B58" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C58" s="20"/>
+      <c r="C58" s="18"/>
       <c r="D58" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E58" s="30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+        <v>119</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="5">
         <f t="shared" si="4"/>
         <v>7.3958333333333307E-3</v>
@@ -3451,20 +3489,20 @@
       <c r="B59" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C59" s="33" t="s">
+      <c r="C59" s="30" t="s">
         <v>13</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E59" s="30" t="s">
+      <c r="E59" s="37" t="s">
         <v>68</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7">
       <c r="A60" s="5">
         <f t="shared" si="4"/>
         <v>7.5115740740740716E-3</v>
@@ -3472,7 +3510,7 @@
       <c r="B60" s="4">
         <v>1.5046296296296294E-3</v>
       </c>
-      <c r="C60" s="34"/>
+      <c r="C60" s="31"/>
       <c r="D60" s="6" t="s">
         <v>113</v>
       </c>
@@ -3480,15 +3518,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7">
       <c r="A61" s="5">
         <f t="shared" si="4"/>
         <v>9.0162037037037016E-3</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="29">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="C61" s="35"/>
+      <c r="C61" s="32"/>
       <c r="D61" s="6" t="s">
         <v>18</v>
       </c>
@@ -3514,31 +3552,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07104DAA-2E56-4B7D-A05C-4806FDF0CFBA}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.796875" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="25.6640625" customWidth="1"/>
     <col min="5" max="5" width="73.6640625" customWidth="1"/>
-    <col min="6" max="11" width="67.1328125" customWidth="1"/>
+    <col min="6" max="11" width="67.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="16" customFormat="1" ht="90.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="27" t="e">
+    <row r="1" spans="1:7" s="14" customFormat="1" ht="99">
+      <c r="A1" s="24" t="e">
         <f t="shared" ref="A1" si="0">#REF!+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="26">
+      <c r="B1" s="23">
         <v>3.4722222222222224E-4</v>
       </c>
       <c r="C1"/>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3548,28 +3586,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3580,7 +3619,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3591,7 +3630,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3602,14 +3641,25 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3622,12 +3672,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D1F29C-200F-4BB5-9251-208FEB1786B7}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
         <v>62</v>
       </c>
@@ -3638,7 +3688,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
@@ -3652,7 +3702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,7 +3716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>60</v>
       </c>

--- a/v1/screenplay_zh.xlsx
+++ b/v1/screenplay_zh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\project\self_playing_ruler\v1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\develop\my_workspace\self_playing_ruler\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CF7EF1-ADA5-4398-9B07-23A2EF73983E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AEB46C-6F58-44B5-BA8C-A94FEAC202C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="封标" sheetId="4" r:id="rId1"/>
@@ -33,15 +33,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="152">
   <si>
     <t>​​画面描述 (分镜)​​</t>
   </si>
@@ -75,11 +72,6 @@
   </si>
   <si>
     <t>章节</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始弹奏后，bgm关掉
-音乐一定要耳熟能详</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -200,10 +192,6 @@
   </si>
   <si>
     <t>《spoiler》</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:19-10:32 https://www.bilibili.com/video/BV187411r7hp/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -370,24 +358,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>第二开始遍跟读：动次打次
-这是第二支笔，充当类似架子鼓的角色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>让它们组一个文具乐队！！！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>吉他（钢尺），长笛（笔），架子鼓（笔）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>加入一下飞入的音效</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TODO:文本霓虹灯特效</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -528,20 +503,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>【口播】
-展示一个串口谱子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>【口播】
-midi图示
-nokia tune播放视频
-5针、usb、RTS等物理接口
-麦克风--&gt;开发板-(usb线)-&gt;mic--&gt;电脑
-                                    -&gt;midi--&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>首先设计主板PCB，为了更方便复刻，都是使用的成品模块</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -568,14 +529,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>【口播】（拿着读台词）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>甚至于它还可以是一个麦克风</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>【口播】
 不同力度弹奏midi键盘演示强弱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -604,22 +557,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>当然，制作过程也不是一帆风顺。
-迭代了很多次，打印了这么多废弃版本，才是现在看到的样子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>【口播】
-在口播画面叠加：Github主页+QQ群（左手指右上--&gt;左上）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>怎么样？这个赛博钢尺琴是不是还有点意思？（语调高昂的）
 如果你对这个项目感兴趣，那就快来动手复刻一个吧，全部的软硬件资料已经上传到了我的github仓库。也可以加我的Q群来沟通交流。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>库克one more thing！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -639,11 +578,6 @@
   </si>
   <si>
     <t>根据草图来建模。使用丝杆步进电机来控制钢尺移动、使用一个舵机压住钢尺、另一个舵机弹拨钢尺，最后加上底座就完成啦！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>【口播】(手比1)
-快速演奏（无法压住钢尺，节奏乱掉）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -697,43 +631,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>​【口播】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-范大将军片段（画中画）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>【口播】
-麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>要怎么来优化呢？哎！不知道你有没有听过一种技术叫MIDI
-它即可以传输音符，又可以存储乐谱。
-举个例子，功能机时代的诺基亚铃声，它就是midi，比如这个
-【播放视频】
-【视频】midi可以使用多种接口进行传输，比如usb接口。而esp32主控就支持usb。因此，使用usb midi就是最好的选择。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>当然，除了使用上位机直接播放MIDI文件，也可以使用midi键盘直接演奏，我们先用这个手机MIDI键盘来试一下
 【视频播放】</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -741,30 +638,6 @@
   <si>
     <t>除了最基本的演奏，如果接上真正的midi键盘，还能够支持力度感应，你按得越重，声音就越响亮有力，就像这样：
 【视频播放】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>曾几何时，钢尺演奏可是实打实的‘流量密码’。简简单单一根钢尺却能弹出世界名曲。来，大家感受一下。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-【视频播放】
-喔~~真是太酷了！！！我自己也想要尝试演奏一下呢！</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -779,13 +652,6 @@
   </si>
   <si>
     <t>没名的钢尺找音教程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个DRI MIDI与DIR MIC设备就是钢尺琴啦！
-【视频】
-【视频】
-让我们用它来演奏一曲！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -814,8 +680,374 @@
       </rPr>
       <t xml:space="preserve">
 设备管理器展示
-cubase中MIDI设备
-音频设备展示</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>cubase中MIDI设备</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+音频设备展示
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">钢尺校准
+</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当然，制作过程也不是一帆风顺的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+迭代了很多次，打印了这么多废弃版本，才是现在看到的样子</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>【口播】
+【口播】（拿着读台词）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one more thing！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【口播】
+在口播画面叠加：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Github主页+QQ群（左手指右上--&gt;左上）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【口播】(手比1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（优化 速度）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+快速演奏（无法压住钢尺，节奏乱掉）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【口播】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（优化 音准）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【口播】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（优化 乐谱）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+展示一个串口谱子</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【口播】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（优化 录音）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+麦克风--&gt;开发板-(usb线)-&gt;mic--电脑</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>​</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【口播】
+范大将军片段（画中画）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO：非线性动画</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO:文本霓虹灯特效+音效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>要怎么来优化呢？哎！不知道你有没有听过一种技术叫MIDI
+它即可以传输音符，又可以存储乐谱。
+举个例子，功能机时代的诺基亚铃声，它就是midi，比如这个
+【播放视频】
+【视频】midi可以使用多种接口进行传输，比如usb接口。
+而esp32主控就支持usb，因此，使用usb midi就是最好的选择。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【口播】
+midi图示
+nokia tune播放视频
+5针、usb、RTS等物理接口
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ESP32支持USB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>麦克风--&gt;开发板-(usb线)-&gt;mic--&gt;电脑
+                                    -&gt;midi--&gt;</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">10:19-10:32 https://www.bilibili.com/video/BV187411r7hp/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TODO：动画加入MIDI浮现效果</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>另外，即使不弹钢尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+它甚至于可以当做一个麦克风来用</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO：bgm渐弱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO：重新录制</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是第二支笔，充当类似架子鼓的角色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾几何时，钢尺演奏可是实打实的‘流量密码’。简简单单一根钢尺却能弹出世界名曲。来来来，大家感受一下。
+【视频播放】
+喔~~真是太酷了！！！我自己也想要尝试演奏一下呢！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【视频】
+这个DRI MIDI与DIR MIC设备就是钢尺琴啦！
+【视频】（在cubase中使用MIDI设备）
+【视频】（在音频设备中是一个麦克风）
+【视频】先来</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一键自动频率校准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来，让我们用它来演奏一曲！</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -824,7 +1056,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="等线"/>
@@ -889,6 +1121,13 @@
       <name val="微软雅黑"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1019,7 +1258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1110,6 +1349,24 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="21" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1130,27 +1387,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1578,6 +1814,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1585,7 +1822,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2461,37 +2697,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FBFDF2-C68F-43FE-8FE4-06F462270704}">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" s="17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.4">
+      <c r="F23" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2502,18 +2743,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16.5"/>
+  <dimension ref="A1:G62"/>
+  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="8.25" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="21" customWidth="1"/>
-    <col min="4" max="5" width="62.83203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="26.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.265625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.265625" style="21" customWidth="1"/>
+    <col min="4" max="5" width="62.796875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="26.265625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="9.08203125" style="3"/>
+    <col min="8" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2536,7 +2777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="49.5">
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A2" s="25">
         <v>0</v>
       </c>
@@ -2544,37 +2785,37 @@
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="33">
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A3" s="25">
-        <f t="shared" ref="A3:A9" si="0">A2+B2</f>
+        <f t="shared" ref="A3:A8" si="0">A2+B2</f>
         <v>1.1574074074074073E-4</v>
       </c>
       <c r="B3" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="99">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.4">
       <c r="A4" s="25">
         <f t="shared" si="0"/>
         <v>1.7361111111111109E-4</v>
@@ -2582,17 +2823,17 @@
       <c r="B4" s="26">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C4" s="33" t="s">
-        <v>46</v>
+      <c r="C4" s="39" t="s">
+        <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="82.5">
+        <v>79</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <f t="shared" si="0"/>
         <v>2.8935185185185184E-4</v>
@@ -2600,15 +2841,15 @@
       <c r="B5" s="23">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C5" s="34"/>
+      <c r="C5" s="40"/>
       <c r="D5" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="37" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="25">
         <f t="shared" si="0"/>
         <v>4.0509259259259258E-4</v>
@@ -2616,16 +2857,16 @@
       <c r="B6" s="26">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C6" s="34"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="49.5">
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <f t="shared" si="0"/>
         <v>4.1666666666666664E-4</v>
@@ -2633,15 +2874,15 @@
       <c r="B7" s="23">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="49.5">
+        <v>139</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <f t="shared" si="0"/>
         <v>5.0925925925925921E-4</v>
@@ -2649,900 +2890,921 @@
       <c r="B8" s="23">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C8" s="35"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>111</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
-        <f t="shared" si="0"/>
+        <f>A8+B8</f>
         <v>5.5555555555555556E-4</v>
       </c>
       <c r="B9" s="23">
         <v>5.7870370370370366E-5</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="37"/>
-    </row>
-    <row r="10" spans="1:7" s="9" customFormat="1" ht="33">
-      <c r="A10" s="5">
-        <f>A7+B7</f>
-        <v>5.0925925925925921E-4</v>
-      </c>
-      <c r="B10" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.4">
+      <c r="A10" s="24">
+        <f t="shared" ref="A10:A18" si="1">A9+B9</f>
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="B10" s="23">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>129</v>
+      <c r="C10" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" s="9" customFormat="1" ht="33">
-      <c r="A11" s="5">
-        <f>A8+B8</f>
-        <v>5.5555555555555556E-4</v>
-      </c>
-      <c r="B11" s="4">
+    <row r="11" spans="1:7" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.4">
+      <c r="A11" s="24">
+        <f t="shared" si="1"/>
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="B11" s="23">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>78</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="8"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" ht="33">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
-        <f>A9+B9</f>
-        <v>6.134259259259259E-4</v>
+        <f t="shared" si="1"/>
+        <v>8.9120370370370373E-4</v>
       </c>
       <c r="B12" s="23">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>93</v>
+        <v>84</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="33">
-      <c r="A13" s="5">
-        <f t="shared" ref="A13:A17" si="1">A11+B11</f>
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="B13" s="4">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A13" s="24">
+        <f t="shared" si="1"/>
+        <v>1.0300925925925926E-3</v>
+      </c>
+      <c r="B13" s="23">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C13" s="35"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>92</v>
+        <v>83</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>87</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" s="14" customFormat="1" ht="82.5">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <f t="shared" si="1"/>
-        <v>7.5231481481481482E-4</v>
+        <v>1.0995370370370371E-3</v>
       </c>
       <c r="B14" s="23">
-        <v>1.8518518518518518E-4</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>100</v>
-      </c>
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C14" s="30"/>
       <c r="D14" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:7" s="14" customFormat="1" ht="66">
+        <v>35</v>
+      </c>
+      <c r="E14" s="31"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:7" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <f t="shared" si="1"/>
-        <v>7.6388888888888893E-4</v>
+        <v>1.1689814814814816E-3</v>
       </c>
       <c r="B15" s="23">
-        <v>2.3148148148148146E-4</v>
-      </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="14" customFormat="1" ht="33">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <f t="shared" si="1"/>
-        <v>9.3749999999999997E-4</v>
+        <v>1.238425925925926E-3</v>
       </c>
       <c r="B16" s="23">
-        <v>3.4722222222222224E-4</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="1:7" s="14" customFormat="1" ht="82.5">
+        <v>2.3148148148148146E-4</v>
+      </c>
+      <c r="C16" s="42"/>
+      <c r="D16" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <f t="shared" si="1"/>
-        <v>9.9537037037037042E-4</v>
+        <v>1.4699074074074074E-3</v>
       </c>
       <c r="B17" s="23">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="C17" s="42"/>
+      <c r="D17" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.4">
+      <c r="A18" s="24">
+        <f t="shared" si="1"/>
+        <v>1.8171296296296297E-3</v>
+      </c>
+      <c r="B18" s="23">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:7" s="14" customFormat="1">
-      <c r="A18" s="24"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="36"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="12"/>
+        <v>92</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="G18" s="12"/>
     </row>
-    <row r="19" spans="1:7" s="14" customFormat="1" ht="66">
+    <row r="19" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A19" s="24">
-        <f>A16+B16</f>
-        <v>1.2847222222222223E-3</v>
+        <f>A18+B18</f>
+        <v>1.9328703703703704E-3</v>
       </c>
       <c r="B19" s="23">
-        <v>9.2592592592592588E-5</v>
-      </c>
-      <c r="C19" s="36"/>
+        <v>0</v>
+      </c>
+      <c r="C19" s="42"/>
       <c r="D19" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>133</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="E19" s="6"/>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="1:7" s="14" customFormat="1">
-      <c r="A20" s="24"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="36"/>
+    <row r="20" spans="1:7" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.4">
+      <c r="A20" s="24">
+        <f>A17+B17</f>
+        <v>1.8171296296296297E-3</v>
+      </c>
+      <c r="B20" s="23">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="C20" s="42"/>
       <c r="D20" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="41"/>
+        <v>22</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>120</v>
+      </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="1:7" s="14" customFormat="1">
-      <c r="A21" s="5">
-        <f>A17+B17</f>
-        <v>1.1111111111111111E-3</v>
-      </c>
-      <c r="B21" s="4">
+    <row r="21" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="24">
+        <f>A18+B18</f>
+        <v>1.9328703703703704E-3</v>
+      </c>
+      <c r="B22" s="23">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:7" ht="49.5">
-      <c r="A22" s="5">
-        <f>A19+B19</f>
-        <v>1.3773148148148149E-3</v>
-      </c>
-      <c r="B22" s="4">
+      <c r="C22" s="42"/>
+      <c r="D22" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="A23" s="24">
+        <f>A20+B20</f>
+        <v>1.9097222222222224E-3</v>
+      </c>
+      <c r="B23" s="23">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C22" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:7" ht="66">
-      <c r="A23" s="24">
-        <f>A22+B22</f>
-        <v>1.4930555555555556E-3</v>
-      </c>
-      <c r="B23" s="23">
-        <v>2.8935185185185189E-4</v>
-      </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="42" t="s">
+        <v>96</v>
+      </c>
       <c r="D23" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="82.5">
+        <v>136</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:7" ht="90" x14ac:dyDescent="0.4">
       <c r="A24" s="24">
         <f>A23+B23</f>
-        <v>1.7824074074074075E-3</v>
+        <v>2.0254629629629633E-3</v>
       </c>
       <c r="B24" s="23">
         <v>2.8935185185185189E-4</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="24"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="36"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="75" x14ac:dyDescent="0.4">
+      <c r="A25" s="24">
+        <f>A24+B24</f>
+        <v>2.3148148148148151E-3</v>
+      </c>
+      <c r="B25" s="23">
+        <v>2.8935185185185189E-4</v>
+      </c>
+      <c r="C25" s="42"/>
       <c r="D25" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="43"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="5">
-        <f>A24+B24</f>
-        <v>2.0717592592592593E-3</v>
-      </c>
-      <c r="B26" s="4">
+        <v>27</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="24"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="24">
+        <f>A25+B25</f>
+        <v>2.604166666666667E-3</v>
+      </c>
+      <c r="B27" s="23">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C26" s="36"/>
-      <c r="D26" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="43"/>
-    </row>
-    <row r="27" spans="1:7" ht="99">
-      <c r="A27" s="24">
-        <f t="shared" ref="A27" si="2">A26+B26</f>
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="B27" s="23">
+      <c r="C27" s="42"/>
+      <c r="D27" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" spans="1:7" ht="90" x14ac:dyDescent="0.4">
+      <c r="A28" s="24">
+        <f t="shared" ref="A28" si="2">A27+B27</f>
+        <v>2.615740740740741E-3</v>
+      </c>
+      <c r="B28" s="23">
         <v>2.3148148148148146E-4</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E27" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:7" ht="99">
-      <c r="A28" s="24">
-        <f t="shared" ref="A28:A51" si="3">A27+B27</f>
-        <v>2.3148148148148147E-3</v>
-      </c>
-      <c r="B28" s="23">
+      <c r="C28" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+    </row>
+    <row r="29" spans="1:7" ht="105" x14ac:dyDescent="0.4">
+      <c r="A29" s="24">
+        <f t="shared" ref="A29:A54" si="3">A28+B28</f>
+        <v>2.8472222222222223E-3</v>
+      </c>
+      <c r="B29" s="23">
         <v>4.6296296296296293E-4</v>
       </c>
-      <c r="C28" s="36"/>
-      <c r="D28" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="5">
-        <f>A28+B28</f>
-        <v>2.7777777777777775E-3</v>
-      </c>
-      <c r="B29" s="4">
+      <c r="C29" s="42"/>
+      <c r="D29" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="5">
+        <f>A29+B29</f>
+        <v>3.3101851851851851E-3</v>
+      </c>
+      <c r="B30" s="4">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C29" s="36"/>
-      <c r="D29" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="41"/>
-    </row>
-    <row r="30" spans="1:7" s="15" customFormat="1" ht="59.25" customHeight="1">
-      <c r="A30" s="24">
-        <f>A29+B29</f>
-        <v>2.7893518518518515E-3</v>
-      </c>
-      <c r="B30" s="23">
+      <c r="C30" s="42"/>
+      <c r="D30" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="32"/>
+    </row>
+    <row r="31" spans="1:7" s="15" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="24">
+        <f>A30+B30</f>
+        <v>3.3217592592592591E-3</v>
+      </c>
+      <c r="B31" s="23">
         <v>1.7361111111111112E-4</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" s="6" t="s">
+      <c r="C31" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E30" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="31" spans="1:7" s="15" customFormat="1">
-      <c r="A31" s="5">
-        <f>A30+B30</f>
-        <v>2.9629629629629624E-3</v>
-      </c>
-      <c r="B31" s="4">
-        <v>1.1574074074074073E-5</v>
-      </c>
-      <c r="C31" s="36"/>
-      <c r="D31" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="41"/>
+      <c r="E31" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
     </row>
-    <row r="32" spans="1:7" s="14" customFormat="1" ht="49.5">
-      <c r="A32" s="24">
+    <row r="32" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="5">
         <f>A31+B31</f>
-        <v>2.9745370370370364E-3</v>
-      </c>
-      <c r="B32" s="23">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" s="41" t="s">
-        <v>83</v>
-      </c>
+        <v>3.49537037037037E-3</v>
+      </c>
+      <c r="B32" s="4">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C32" s="42"/>
+      <c r="D32" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="32"/>
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="5">
+    <row r="33" spans="1:7" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.4">
+      <c r="A33" s="24">
         <f>A32+B32</f>
-        <v>3.0902777777777773E-3</v>
-      </c>
-      <c r="B33" s="4">
+        <v>3.506944444444444E-3</v>
+      </c>
+      <c r="B33" s="23">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="5">
+        <f>A33+B33</f>
+        <v>3.6226851851851849E-3</v>
+      </c>
+      <c r="B34" s="4">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C33" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="25">
-        <f t="shared" si="3"/>
-        <v>3.1481481481481477E-3</v>
-      </c>
-      <c r="B34" s="26">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C34" s="31"/>
+      <c r="C34" s="36" t="s">
+        <v>15</v>
+      </c>
       <c r="D34" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="33">
+        <v>83</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="25">
         <f t="shared" si="3"/>
-        <v>3.2638888888888887E-3</v>
+        <v>3.6805555555555554E-3</v>
       </c>
       <c r="B35" s="26">
-        <v>5.7870370370370378E-4</v>
-      </c>
-      <c r="C35" s="31"/>
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C35" s="37"/>
       <c r="D35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:7">
+        <v>36</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A36" s="25">
         <f t="shared" si="3"/>
-        <v>3.8425925925925923E-3</v>
+        <v>3.7962962962962963E-3</v>
       </c>
       <c r="B36" s="26">
-        <v>1.3888888888888889E-4</v>
-      </c>
-      <c r="C36" s="31"/>
+        <v>5.7870370370370378E-4</v>
+      </c>
+      <c r="C36" s="37"/>
       <c r="D36" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="25">
         <f t="shared" si="3"/>
-        <v>3.9814814814814808E-3</v>
+        <v>4.3750000000000004E-3</v>
       </c>
       <c r="B37" s="26">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="C37" s="31"/>
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="C37" s="37"/>
       <c r="D37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="37"/>
+        <v>5</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="25">
         <f t="shared" si="3"/>
-        <v>4.0393518518518513E-3</v>
+        <v>4.5138888888888893E-3</v>
       </c>
       <c r="B38" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C38" s="31"/>
+      <c r="C38" s="37"/>
       <c r="D38" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" s="37"/>
+        <v>6</v>
+      </c>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:7" ht="33">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="25">
         <f t="shared" si="3"/>
-        <v>4.0972222222222217E-3</v>
+        <v>4.5717592592592598E-3</v>
       </c>
       <c r="B39" s="26">
-        <v>5.7870370370370378E-4</v>
-      </c>
-      <c r="C39" s="31"/>
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C39" s="37"/>
       <c r="D39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E39" s="37"/>
+        <v>56</v>
+      </c>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A40" s="25">
         <f t="shared" si="3"/>
-        <v>4.6759259259259254E-3</v>
+        <v>4.6296296296296302E-3</v>
       </c>
       <c r="B40" s="26">
+        <v>5.7870370370370378E-4</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="25">
+        <f t="shared" si="3"/>
+        <v>5.2083333333333339E-3</v>
+      </c>
+      <c r="B41" s="26">
         <v>5.7870370370370366E-5</v>
       </c>
-      <c r="C40" s="31"/>
-      <c r="D40" s="6" t="s">
+      <c r="C41" s="37"/>
+      <c r="D41" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="37"/>
-      <c r="F40" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="24">
-        <f t="shared" si="3"/>
-        <v>4.7337962962962958E-3</v>
-      </c>
-      <c r="B41" s="23">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="F41" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
         <f t="shared" si="3"/>
-        <v>4.7685185185185183E-3</v>
+        <v>5.2662037037037044E-3</v>
       </c>
       <c r="B42" s="23">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="C42" s="32"/>
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="C42" s="37"/>
       <c r="D42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>32</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
         <f t="shared" si="3"/>
-        <v>4.8148148148148143E-3</v>
-      </c>
-      <c r="B43" s="23"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="E43" s="37"/>
-      <c r="F43" s="27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="66">
+        <v>5.3009259259259268E-3</v>
+      </c>
+      <c r="B43" s="23">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="C43" s="38"/>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="24">
         <f t="shared" si="3"/>
-        <v>4.8148148148148143E-3</v>
-      </c>
-      <c r="B44" s="4">
-        <v>4.6296296296296293E-4</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>15</v>
-      </c>
+        <v>5.3472222222222228E-3</v>
+      </c>
+      <c r="B44" s="23">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="C44" s="18"/>
       <c r="D44" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="33">
+        <v>104</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="90" x14ac:dyDescent="0.4">
       <c r="A45" s="24">
         <f t="shared" si="3"/>
-        <v>5.2777777777777771E-3</v>
-      </c>
-      <c r="B45" s="23">
-        <v>3.4722222222222224E-4</v>
-      </c>
-      <c r="C45" s="31"/>
-      <c r="D45" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E45" s="37"/>
-      <c r="G45" s="7"/>
-    </row>
-    <row r="46" spans="1:7" ht="49.5">
+        <v>5.3587962962962973E-3</v>
+      </c>
+      <c r="B45" s="4">
+        <v>4.6296296296296293E-4</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A46" s="24">
         <f t="shared" si="3"/>
-        <v>5.6249999999999989E-3</v>
+        <v>5.82175925925926E-3</v>
       </c>
       <c r="B46" s="23">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C46" s="31"/>
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="C46" s="37"/>
       <c r="D46" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G46" s="7"/>
     </row>
-    <row r="47" spans="1:7" ht="49.5">
+    <row r="47" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A47" s="24">
         <f t="shared" si="3"/>
-        <v>5.7407407407407398E-3</v>
+        <v>6.1689814814814819E-3</v>
       </c>
       <c r="B47" s="23">
-        <v>4.0509259259259258E-4</v>
-      </c>
-      <c r="C47" s="31"/>
-      <c r="D47" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C47" s="37"/>
+      <c r="D47" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G47" s="7"/>
+    </row>
+    <row r="48" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A48" s="24">
         <f t="shared" si="3"/>
-        <v>6.1458333333333321E-3</v>
-      </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="31"/>
+        <v>6.2847222222222228E-3</v>
+      </c>
+      <c r="B48" s="23">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="C48" s="37"/>
       <c r="D48" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>108</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30" x14ac:dyDescent="0.4">
       <c r="A49" s="24">
         <f t="shared" si="3"/>
-        <v>6.1458333333333321E-3</v>
-      </c>
-      <c r="B49" s="23">
-        <v>2.3148148148148147E-5</v>
-      </c>
-      <c r="C49" s="31"/>
+        <v>6.6898148148148151E-3</v>
+      </c>
+      <c r="B49" s="23"/>
+      <c r="C49" s="37"/>
       <c r="D49" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" s="37"/>
-    </row>
-    <row r="50" spans="1:7" ht="33">
+        <v>132</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" s="24">
         <f t="shared" si="3"/>
-        <v>6.1689814814814802E-3</v>
+        <v>6.6898148148148151E-3</v>
       </c>
       <c r="B50" s="23">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="C50" s="37"/>
+      <c r="D50" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A51" s="24">
+        <f t="shared" si="3"/>
+        <v>6.7129629629629631E-3</v>
+      </c>
+      <c r="B51" s="23">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="C50" s="32"/>
-      <c r="D50" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="G50" s="7"/>
-    </row>
-    <row r="51" spans="1:7" ht="49.5">
-      <c r="A51" s="5">
+      <c r="C51" s="38"/>
+      <c r="D51" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G51" s="7"/>
+    </row>
+    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.4">
+      <c r="A52" s="5">
         <f t="shared" si="3"/>
-        <v>6.5740740740740725E-3</v>
-      </c>
-      <c r="B51" s="4">
+        <v>7.1180555555555554E-3</v>
+      </c>
+      <c r="B52" s="4">
         <v>3.4722222222222224E-4</v>
       </c>
-      <c r="C51" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="5"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E52" s="37"/>
-    </row>
-    <row r="53" spans="1:7" ht="33">
+      <c r="C52" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
-        <f>A51+B51</f>
-        <v>6.9212962962962943E-3</v>
+        <f t="shared" si="3"/>
+        <v>7.4652777777777773E-3</v>
       </c>
       <c r="B53" s="4">
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C53" s="37"/>
+      <c r="D53" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.4">
+      <c r="A54" s="5">
+        <f t="shared" si="3"/>
+        <v>7.5231481481481477E-3</v>
+      </c>
+      <c r="B54" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="24">
-        <f t="shared" ref="A54:A61" si="4">A53+B53</f>
-        <v>7.0370370370370352E-3</v>
-      </c>
-      <c r="B54" s="23">
+      <c r="C54" s="37"/>
+      <c r="D54" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="24">
+        <f t="shared" ref="A55:A62" si="4">A54+B54</f>
+        <v>7.6388888888888886E-3</v>
+      </c>
+      <c r="B55" s="23">
         <v>4.6296296296296294E-5</v>
       </c>
-      <c r="C54" s="31"/>
-      <c r="D54" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="24">
-        <f t="shared" si="4"/>
-        <v>7.0833333333333312E-3</v>
-      </c>
-      <c r="B55" s="23">
-        <v>5.7870370370370366E-5</v>
-      </c>
-      <c r="C55" s="31"/>
+      <c r="C55" s="37"/>
       <c r="D55" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E55" s="37" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="33">
+      <c r="E55" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="24">
         <f t="shared" si="4"/>
-        <v>7.1412037037037017E-3</v>
+        <v>7.6851851851851847E-3</v>
       </c>
       <c r="B56" s="23">
-        <v>6.9444444444444444E-5</v>
-      </c>
-      <c r="C56" s="31"/>
+        <v>5.7870370370370366E-5</v>
+      </c>
+      <c r="C56" s="37"/>
       <c r="D56" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E56" s="37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="E56" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="24">
         <f t="shared" si="4"/>
-        <v>7.2106481481481457E-3</v>
+        <v>7.7430555555555551E-3</v>
       </c>
       <c r="B57" s="23">
         <v>6.9444444444444444E-5</v>
       </c>
-      <c r="C57" s="32"/>
+      <c r="C57" s="37"/>
       <c r="D57" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="49.5">
-      <c r="A58" s="5">
+        <v>70</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" s="24">
         <f t="shared" si="4"/>
-        <v>7.2800925925925897E-3</v>
-      </c>
-      <c r="B58" s="4">
-        <v>1.1574074074074073E-4</v>
-      </c>
-      <c r="C58" s="18"/>
+        <v>7.8124999999999991E-3</v>
+      </c>
+      <c r="B58" s="23">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="C58" s="38"/>
       <c r="D58" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>74</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="45" x14ac:dyDescent="0.4">
       <c r="A59" s="5">
         <f t="shared" si="4"/>
-        <v>7.3958333333333307E-3</v>
+        <v>7.8819444444444432E-3</v>
       </c>
       <c r="B59" s="4">
         <v>1.1574074074074073E-4</v>
       </c>
-      <c r="C59" s="30" t="s">
-        <v>13</v>
-      </c>
+      <c r="C59" s="18"/>
       <c r="D59" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>110</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="5">
         <f t="shared" si="4"/>
-        <v>7.5115740740740716E-3</v>
+        <v>7.9976851851851841E-3</v>
       </c>
       <c r="B60" s="4">
-        <v>1.5046296296296294E-3</v>
-      </c>
-      <c r="C60" s="31"/>
+        <v>1.1574074074074073E-4</v>
+      </c>
+      <c r="C60" s="36" t="s">
+        <v>12</v>
+      </c>
       <c r="D60" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
         <f t="shared" si="4"/>
-        <v>9.0162037037037016E-3</v>
-      </c>
-      <c r="B61" s="29">
+        <v>8.113425925925925E-3</v>
+      </c>
+      <c r="B61" s="4">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="C61" s="37"/>
+      <c r="D61" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A62" s="5">
+        <f t="shared" si="4"/>
+        <v>9.618055555555555E-3</v>
+      </c>
+      <c r="B62" s="29">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="C61" s="32"/>
-      <c r="D61" s="6" t="s">
-        <v>18</v>
+      <c r="C62" s="38"/>
+      <c r="D62" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="C51:C57"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="C52:C58"/>
     <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C33:C42"/>
+    <mergeCell ref="C34:C43"/>
     <mergeCell ref="C10:C13"/>
-    <mergeCell ref="C14:C21"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C44:C50"/>
+    <mergeCell ref="C15:C22"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C45:C51"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3552,15 +3814,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07104DAA-2E56-4B7D-A05C-4806FDF0CFBA}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="4" max="4" width="25.6640625" customWidth="1"/>
     <col min="5" max="5" width="73.6640625" customWidth="1"/>
-    <col min="6" max="11" width="67.1640625" customWidth="1"/>
+    <col min="6" max="11" width="67.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="14" customFormat="1" ht="99">
+    <row r="1" spans="1:7" s="14" customFormat="1" ht="90.75" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="e">
         <f t="shared" ref="A1" si="0">#REF!+#REF!</f>
         <v>#REF!</v>
@@ -3570,10 +3832,10 @@
       </c>
       <c r="C1"/>
       <c r="D1" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
@@ -3587,80 +3849,80 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F25715-BEED-42F5-8F10-9FEA1FF7F5C3}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -3672,25 +3934,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D1F29C-200F-4BB5-9251-208FEB1786B7}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -3702,9 +3964,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -3716,9 +3978,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B4">
         <v>6</v>
